--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -4954,7 +4954,7 @@
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -5396,7 +5396,7 @@
         <v>491</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>460</v>
@@ -5765,7 +5765,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5773,34 +5773,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>6468</v>
+        <v>24085</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -5812,7 +5812,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5820,34 +5820,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>24085</v>
+        <v>457</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5867,34 +5867,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>솔티스</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000234147&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023414702ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>106</v>
+        <v>12307</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -5906,7 +5906,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5914,34 +5914,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>솔티스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000234147&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023414702ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>457</v>
+        <v>106</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -5961,34 +5961,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>17,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563462ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>12307</v>
+        <v>26611</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -6000,7 +6000,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6008,34 +6008,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[올영단독] 정관장 에브리타임 세븐베리/배/한라봉 플레이버 7포 단독기획</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15,600원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225001&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022500124ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>6735</v>
+        <v>15338</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6102,34 +6102,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>[올영단독] 정관장 에브리타임 세븐베리/배/한라봉 플레이버 7포 단독기획</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>15,600원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225001&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022500124ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>6255</v>
+        <v>6735</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -6259,42 +6259,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6316,42 +6316,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>솔티스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>솔티스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>정관장</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
         </is>
       </c>
     </row>
@@ -6373,42 +6373,42 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>[올영단독] 정관장 에브리타임 세븐베리/배/한라봉 플레이버 7포 단독기획</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
     </row>
@@ -6428,16 +6428,16 @@
         <v>4.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.9</v>
@@ -6446,7 +6446,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -6462,28 +6462,28 @@
         <v>8055</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6468</v>
+        <v>24085</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24085</v>
+        <v>457</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>12307</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>457</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>12307</v>
+        <v>26611</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6735</v>
+        <v>15338</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>13672</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6255</v>
+        <v>6735</v>
       </c>
     </row>
     <row r="8">
@@ -6538,42 +6538,42 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>13,950원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>12,900원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>17,400원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>8,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>15,600원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>8,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>26,900원</t>
         </is>
       </c>
     </row>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -6715,7 +6715,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -6737,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6787,7 +6787,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6822,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6853,7 +6853,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6863,10 +6863,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6885,10 +6885,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>

--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -5800,7 +5800,7 @@
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>24085</v>
+        <v>24087</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>12307</v>
+        <v>12309</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -5988,7 +5988,7 @@
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>26611</v>
+        <v>26614</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -6462,19 +6462,19 @@
         <v>8055</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>24085</v>
+        <v>24087</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>457</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12307</v>
+        <v>12309</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>106</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>26611</v>
+        <v>26614</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>15338</v>
@@ -6787,7 +6787,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6822,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -6853,7 +6853,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6863,10 +6863,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6885,10 +6885,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>

--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -2598,10 +2598,26 @@
       <c r="J2" t="n">
         <v>15998</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 체감 — 섭취 시 확실히 피로가 풀리고 컨디션 회복 및 활력 충전에 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>편리한 섭취와 우수한 휴대성 — 액상과 정제가 함께 있어 바쁜 아침에도 챙겨 먹기 편하고 휴대하기 쉽습니다.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 구성 — 패키지가 고급스러워 생일이나 응원 등 특별한 날 선물용으로 인기가 높습니다.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>아쉬운 부직포 포장 재질 — 고급스러운 상자 포장 대신 부직포 재질로 되어 있어 이음새가 벌어지고 활용도가 떨어집니다.</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -2645,9 +2661,21 @@
       <c r="J3" t="n">
         <v>15335</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>거부감 없는 상큼한 맛 — 쓴맛이 없고 망고피치 맛 액상이라 맛있게 섭취할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>간편한 올인원 제형 — 알약 크기가 작고 액상과 같이 들어 있어 물 없이도 편리하게 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>신속한 체력 보충 효과 — 피곤할 때 하나씩 꺼내 먹으면 활력이 충전되고 피로가 풀어집니다.</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2692,9 +2720,21 @@
       <c r="J4" t="n">
         <v>3342</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>뛰어난 활력 증진 효과 — 몸이 나른하고 피곤할 때 섭취하면 활력이 생기고 힘이 납니다.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 패키지 — 패키지가 깔끔하고 고급스러워 소중한 분께 마음을 전하기 좋습니다.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>간편한 휴대성과 섭취 — 언제 어디서나 들고 다니며 피곤할 때 마시기 편합니다.</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2739,10 +2779,26 @@
       <c r="J5" t="n">
         <v>6449</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>맛있는 과일 맛 구미 제형 — 달콤하고 상큼한 과일 맛 젤리 형태라 간식처럼 즐겁게 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>물 필요 없는 편리함 — 알약을 물과 함께 먹는 번거로움 없이 어디서나 씹어서 섭취 가능합니다.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>감각적이고 예쁜 포장 — 제품 디자인과 이벤트 기획 포장이 예뻐서 선물용으로 반응이 좋습니다.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>아쉬운 일일 권장 섭취량 — 맛있어서 더 먹고 싶지만 하루 권장량이 2개로 제한되어 아쉽다는 반응이 있습니다.</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2786,9 +2842,21 @@
       <c r="J6" t="n">
         <v>8687</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>빠른 기력 회복 체감 — 섭취 후 피로가 풀리고 기력이 회복되는 효과가 신속하게 느껴집니다.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>위생적인 개별 포장 — 1회 섭취량씩 개별 포장되어 있어 들고 다니기 편하고 위생적입니다.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>부담 없는 목넘김과 맛 — 알약 크기가 적당하여 목넘김이 원활하고 맛도 좋아 먹기 좋습니다.</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2833,9 +2901,21 @@
       <c r="J7" t="n">
         <v>717</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>부담 없는 맛과 편의성 — 맛이 좋아 거부감이 없으며 섭취 방법이 간단해 꾸준히 먹기 좋습니다.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>휴대하기 좋은 개별 용기 — 개별 병 형태라 가방에 들고 다니며 필요할 때 챙겨 먹기 편합니다.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>체력 보충과 피로 완화 — 몸이 피곤할 때 먹으면 피로감이 풀리고 활력이 생기는 느낌을 받습니다.</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2880,10 +2960,26 @@
       <c r="J8" t="n">
         <v>773</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>뛰어난 컨디션 개선 — 피로감이 심할 때 섭취하면 빠르게 활력이 돌아오고 피로가 감소합니다.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>진한 오렌지 맛과 휴대성 — 진한 오렌지 맛으로 부담 없이 먹을 수 있고 가방에 휴대하기 편합니다.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>높은 선물 만족도 — 고급스러운 패키지 구성 덕분에 선물을 받는 사람의 만족도가 높습니다.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>부담스러운 제품 가격 — 제품 가격이 다소 비싸 직접 구매하기에는 고민이 된다는 의견이 있습니다.</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -2927,9 +3023,21 @@
       <c r="J9" t="n">
         <v>1618</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>재미있는 섞어 마시기 방식 — 버튼을 눌러 분말을 액상에 섞어 먹는 구조가 신선하고 재미있습니다.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>상큼하고 맛있는 풍미 — 건강식품 특유의 쓴맛 없이 음료처럼 상큼하고 맛있게 마실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 디자인 — 디자인과 구성이 알차고 고급스러워 정성 어린 선물로 제격입니다.</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -2974,9 +3082,21 @@
       <c r="J10" t="n">
         <v>2608</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛 풍미 — 쓴맛이나 비린 느낌 없이 상큼한 레몬향이 나 호불호 없이 마시기 좋습니다.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>편리한 올인원 휴대성 — 개별 포장된 한 병에 액상과 정제가 함께 있어 들고 다니며 먹기 편합니다.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>피로 개선 및 활력 증진 — 바쁜 일상이나 체력 소모가 많은 상황에서 덜 지치도록 도움을 줍니다.</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3021,9 +3141,21 @@
       <c r="J11" t="n">
         <v>766</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>성별 맞춤형 영양 옵션 — 남성용과 여성용으로 구분되어 있어 개인의 필요에 맞게 선택 및 선물할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>실용적인 분할 보관 패키지 — 고급스러운 포장에 박스가 나뉘어 있어 깔끔하게 보관하고 꺼내 먹기 편합니다.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>지속적인 피로감 감소 — 꾸준히 섭취 시 활력이 생기고 매일 느끼던 피로함이 줄어듭니다.</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -3115,10 +3247,26 @@
       <c r="J13" t="n">
         <v>49</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>질리지 않는 다양한 맛 — 메뉴가 다양하게 구성되어 있어 식단 관리 중 매일 먹어도 물리지가 않습니다.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 구성 — 합리적인 가격에 알찬 수량으로 구성되어 부담 없이 구매할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>부드러운 식감과 간편 조리 — 닭가슴살 특유의 뻑뻑함이 적고 전자레인지로 간편하게 조리할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>배송 중 해동 문제 — 배송 과정에서 제품이 완전히 녹아서도착하는 경우가 발생했습니다.</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3162,9 +3310,21 @@
       <c r="J14" t="n">
         <v>730</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>고급스러운 가방 포장 — 플리츠백 스타일의 예쁘고 럭셔리한 포장 덕분에 선물용으로 극찬을 받습니다.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>상큼한 오렌지 맛 액상 — 거부감 없는 오렌지 맛 액상 타입이라 손쉽게 마실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>피부 탄력 및 피로 개선 — 복용 후 푸석했던 피부에 탄력이 생기고 피로가 개선되는 느낌을 받습니다.</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -3209,10 +3369,26 @@
       <c r="J15" t="n">
         <v>142</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 육즙이 유지되어 다이어트 중에도 맛있게 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>다채로운 식단 구성 — 닭가슴살 외에도 소시지, 큐브 등 다채로운 형태와 맛으로 구성되어 질리지 않습니다.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>유용한 보냉백 제공 — 함께 제공되는 보냉백 덕분에 도시락용으로 들고 다니기 편리합니다.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>증정품 디자인 불일치 — 라이브 방송에서 안내된 보냉백 디자인과 다른 제품이 배송되어 아쉬움을 남겼습니다.</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -3256,9 +3432,21 @@
       <c r="J16" t="n">
         <v>213</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>우수한 맛과 깔끔한 목넘김 — 단백질 특유의 비린내나 텁텁함이 없고 일반 초코우유처럼 매우 맛있습니다.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>속이 편한 락토프리 제형 — 락토프리 제품이라 빈속이나 운동 후 섭취해도 속이 편안합니다.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>부담 없는 당류와 칼로리 — 제로슈가로 당류 부담 없이 높은 단백질을 효율적으로 충전할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -3303,10 +3491,26 @@
       <c r="J17" t="n">
         <v>1653</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 풍미 — 거부감 있는 효소 향 대신 군고구마 향이 나 맛있게 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>원활한 소화 및 배변 활동 — 과식 후 더부룩함을 누그러뜨리고 화장실을 편하게 가도록 도와줍니다.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>풍성한 사은품과 가성비 — 다양한 추가 사은품과 높은 할인 혜택으로 구매 만족도가 매우 높습니다.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>사은품 기프티콘 누락 — 이벤트 사은품으로 안내된 기프티콘을 받지 못했다는 불만이 있습니다.</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3350,9 +3554,21 @@
       <c r="J18" t="n">
         <v>1894</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>거부감 없는 무색무취 — 특별한 맛이나 냄새가 없고 입자가 고와 물이나 프로틴에 쉽게 타 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>운동 수행 능력 향상 — 운동 전후 섭취 시 근육 펌핑감과 운동 효율을 높여 체력 증진에 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>우수한 가성비와 대용량 — 넉넉한 용량 대비 가격이 합리적이어서 꾸준히 섭취하기 좋습니다.</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3397,9 +3613,21 @@
       <c r="J19" t="n">
         <v>247</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>풍부한 아르기닌 함량 — 1포당 초고함량의 아르기닌이 들어있어 확실한 활력 부스팅 효과를 줍니다.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>상큼하고 맛있는 베리 맛 — 특유의 거북한 맛을 잡고 상큼한 베리 맛을 내어 부담 없이 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>편리한 스틱 포장 — 스틱 형태로 제작되어 바로 짜 먹거나 물에 타서 마시기 편리합니다.</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3444,9 +3672,21 @@
       <c r="J20" t="n">
         <v>38</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>역하지 않은 상큼한 레몬맛 — 특유의 향 없이 상큼한 레몬 맛이 나 영양제를 잘 못 먹는 사람도 쉽게 복용합니다.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>간편한 액상 스틱 형태 — 물 없이 바로 짜 먹을 수 있고 휴대가 용이하여 외출 시에도 챙겨 먹기 편합니다.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 체감 — 높은 함량으로 섭취 후 피로 회복과 운동 활력 충전에 도움을 줍니다.</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3491,7 +3731,11 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 제품 섭취 후 매우 뛰어난 숙취 해소 효과를 체감할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3846,22 +4090,82 @@
         <v>766</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 체감 — 섭취 시 확실히 피로가 풀리고 컨디션 회복 및 활력 충전에 도움을 줍니다.
+편리한 섭취와 우수한 휴대성 — 액상과 정제가 함께 있어 바쁜 아침에도 챙겨 먹기 편하고 휴대하기 쉽습니다.
+고급스러운 선물용 구성 — 패키지가 고급스러워 생일이나 응원 등 특별한 날 선물용으로 인기가 높습니다.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>거부감 없는 상큼한 맛 — 쓴맛이 없고 망고피치 맛 액상이라 맛있게 섭취할 수 있습니다.
+간편한 올인원 제형 — 알약 크기가 작고 액상과 같이 들어 있어 물 없이도 편리하게 먹을 수 있습니다.
+신속한 체력 보충 효과 — 피곤할 때 하나씩 꺼내 먹으면 활력이 충전되고 피로가 풀어집니다.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 활력 증진 효과 — 몸이 나른하고 피곤할 때 섭취하면 활력이 생기고 힘이 납니다.
+고급스러운 선물용 패키지 — 패키지가 깔끔하고 고급스러워 소중한 분께 마음을 전하기 좋습니다.
+간편한 휴대성과 섭취 — 언제 어디서나 들고 다니며 피곤할 때 마시기 편합니다.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 과일 맛 구미 제형 — 달콤하고 상큼한 과일 맛 젤리 형태라 간식처럼 즐겁게 먹을 수 있습니다.
+물 필요 없는 편리함 — 알약을 물과 함께 먹는 번거로움 없이 어디서나 씹어서 섭취 가능합니다.
+감각적이고 예쁜 포장 — 제품 디자인과 이벤트 기획 포장이 예뻐서 선물용으로 반응이 좋습니다.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 기력 회복 체감 — 섭취 후 피로가 풀리고 기력이 회복되는 효과가 신속하게 느껴집니다.
+위생적인 개별 포장 — 1회 섭취량씩 개별 포장되어 있어 들고 다니기 편하고 위생적입니다.
+부담 없는 목넘김과 맛 — 알약 크기가 적당하여 목넘김이 원활하고 맛도 좋아 먹기 좋습니다.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>부담 없는 맛과 편의성 — 맛이 좋아 거부감이 없으며 섭취 방법이 간단해 꾸준히 먹기 좋습니다.
+휴대하기 좋은 개별 용기 — 개별 병 형태라 가방에 들고 다니며 필요할 때 챙겨 먹기 편합니다.
+체력 보충과 피로 완화 — 몸이 피곤할 때 먹으면 피로감이 풀리고 활력이 생기는 느낌을 받습니다.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 컨디션 개선 — 피로감이 심할 때 섭취하면 빠르게 활력이 돌아오고 피로가 감소합니다.
+진한 오렌지 맛과 휴대성 — 진한 오렌지 맛으로 부담 없이 먹을 수 있고 가방에 휴대하기 편합니다.
+높은 선물 만족도 — 고급스러운 패키지 구성 덕분에 선물을 받는 사람의 만족도가 높습니다.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>재미있는 섞어 마시기 방식 — 버튼을 눌러 분말을 액상에 섞어 먹는 구조가 신선하고 재미있습니다.
+상큼하고 맛있는 풍미 — 건강식품 특유의 쓴맛 없이 음료처럼 상큼하고 맛있게 마실 수 있습니다.
+고급스러운 선물용 디자인 — 디자인과 구성이 알차고 고급스러워 정성 어린 선물로 제격입니다.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛 풍미 — 쓴맛이나 비린 느낌 없이 상큼한 레몬향이 나 호불호 없이 마시기 좋습니다.
+편리한 올인원 휴대성 — 개별 포장된 한 병에 액상과 정제가 함께 있어 들고 다니며 먹기 편합니다.
+피로 개선 및 활력 증진 — 바쁜 일상이나 체력 소모가 많은 상황에서 덜 지치도록 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>성별 맞춤형 영양 옵션 — 남성용과 여성용으로 구분되어 있어 개인의 필요에 맞게 선택 및 선물할 수 있습니다.
+실용적인 분할 보관 패키지 — 고급스러운 포장에 박스가 나뉘어 있어 깔끔하게 보관하고 꺼내 먹기 편합니다.
+지속적인 피로감 감소 — 꾸준히 섭취 시 활력이 생기고 매일 느끼던 피로함이 줄어듭니다.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -3869,13 +4173,25 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 부직포 포장 재질 — 고급스러운 상자 포장 대신 부직포 재질로 되어 있어 이음새가 벌어지고 활용도가 떨어집니다.</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 일일 권장 섭취량 — 맛있어서 더 먹고 싶지만 하루 권장량이 2개로 제한되어 아쉽다는 반응이 있습니다.</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 제품 가격 — 제품 가격이 다소 비싸 직접 구매하기에는 고민이 된다는 의견이 있습니다.</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4313,22 +4629,74 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>질리지 않는 다양한 맛 — 메뉴가 다양하게 구성되어 있어 식단 관리 중 매일 먹어도 물리지가 않습니다.
+뛰어난 가성비 구성 — 합리적인 가격에 알찬 수량으로 구성되어 부담 없이 구매할 수 있습니다.
+부드러운 식감과 간편 조리 — 닭가슴살 특유의 뻑뻑함이 적고 전자레인지로 간편하게 조리할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 가방 포장 — 플리츠백 스타일의 예쁘고 럭셔리한 포장 덕분에 선물용으로 극찬을 받습니다.
+상큼한 오렌지 맛 액상 — 거부감 없는 오렌지 맛 액상 타입이라 손쉽게 마실 수 있습니다.
+피부 탄력 및 피로 개선 — 복용 후 푸석했던 피부에 탄력이 생기고 피로가 개선되는 느낌을 받습니다.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 육즙이 유지되어 다이어트 중에도 맛있게 먹을 수 있습니다.
+다채로운 식단 구성 — 닭가슴살 외에도 소시지, 큐브 등 다채로운 형태와 맛으로 구성되어 질리지 않습니다.
+유용한 보냉백 제공 — 함께 제공되는 보냉백 덕분에 도시락용으로 들고 다니기 편리합니다.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>우수한 맛과 깔끔한 목넘김 — 단백질 특유의 비린내나 텁텁함이 없고 일반 초코우유처럼 매우 맛있습니다.
+속이 편한 락토프리 제형 — 락토프리 제품이라 빈속이나 운동 후 섭취해도 속이 편안합니다.
+부담 없는 당류와 칼로리 — 제로슈가로 당류 부담 없이 높은 단백질을 효율적으로 충전할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 풍미 — 거부감 있는 효소 향 대신 군고구마 향이 나 맛있게 먹을 수 있습니다.
+원활한 소화 및 배변 활동 — 과식 후 더부룩함을 누그러뜨리고 화장실을 편하게 가도록 도와줍니다.
+풍성한 사은품과 가성비 — 다양한 추가 사은품과 높은 할인 혜택으로 구매 만족도가 매우 높습니다.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>거부감 없는 무색무취 — 특별한 맛이나 냄새가 없고 입자가 고와 물이나 프로틴에 쉽게 타 먹을 수 있습니다.
+운동 수행 능력 향상 — 운동 전후 섭취 시 근육 펌핑감과 운동 효율을 높여 체력 증진에 도움을 줍니다.
+우수한 가성비와 대용량 — 넉넉한 용량 대비 가격이 합리적이어서 꾸준히 섭취하기 좋습니다.</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>풍부한 아르기닌 함량 — 1포당 초고함량의 아르기닌이 들어있어 확실한 활력 부스팅 효과를 줍니다.
+상큼하고 맛있는 베리 맛 — 특유의 거북한 맛을 잡고 상큼한 베리 맛을 내어 부담 없이 먹을 수 있습니다.
+편리한 스틱 포장 — 스틱 형태로 제작되어 바로 짜 먹거나 물에 타서 마시기 편리합니다.</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>역하지 않은 상큼한 레몬맛 — 특유의 향 없이 상큼한 레몬 맛이 나 영양제를 잘 못 먹는 사람도 쉽게 복용합니다.
+간편한 액상 스틱 형태 — 물 없이 바로 짜 먹을 수 있고 휴대가 용이하여 외출 시에도 챙겨 먹기 편합니다.
+확실한 피로 회복 체감 — 높은 함량으로 섭취 후 피로 회복과 운동 활력 충전에 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 제품 섭취 후 매우 뛰어난 숙취 해소 효과를 체감할 수 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="inlineStr">
@@ -4337,11 +4705,23 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>배송 중 해동 문제 — 배송 과정에서 제품이 완전히 녹아서도착하는 경우가 발생했습니다.</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>증정품 디자인 불일치 — 라이브 방송에서 안내된 보냉백 디자인과 다른 제품이 배송되어 아쉬움을 남겼습니다.</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>사은품 기프티콘 누락 — 이벤트 사은품으로 안내된 기프티콘을 받지 못했다는 불만이 있습니다.</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4625,11 +5005,23 @@
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>5850</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>5851</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>압도적인 가격 경쟁력 — 다이소 판매 제품으로 3,000원이라는 매우 저렴한 가격에 한 달 분량을 구매할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>눈 떨림 및 근육 경련 완화 — 섭취 후 눈 밑 떨림이나 자다 다리에 쥐가 나는 증상이 크게 가라앉습니다.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>숙면 및 긴장 완화 효과 — 자기 전 복용 시 긴장을 풀어주어 깊은 잠을 자는 데 큰 도움을 줍니다.</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -4674,11 +5066,27 @@
       <c r="J3" t="n">
         <v>398</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>시원하고 확실한 배변 작용 — 배가 아프지 않고 자연스럽고 시원하게 묵은 변을 배출해 줍니다.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>부담 없는 합리적 가격 — 편의점 대비 저렴한 2,000원 가격으로 부담 없이 구매할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>불편한 정제 배출 방식 — 상단 정제가 액상 안으로 잘 떨어지지 않아 손으로 직접 꺼내야 하는 불편함이 있습니다.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>기대와 다른 액상 맛 — 일반적인 포도주스 맛을 기대한 소비자는 다소 맛이 아쉽다고 느낄 수 있습니다.</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -4721,10 +5129,22 @@
       <c r="J4" t="n">
         <v>47</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>저렴한 고함량 비타민C — 비타민C 2000mg 고함량 제품을 5,000원이라는 저렴한 가격에 구매할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>위생적인 개별 스틱 포장 — 가루 형태의 개별 스틱 포장으로 되어 있어 휴대하고 챙겨 먹기 편합니다.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>원료 원산지 미표기 — 원산지 정보가 상세히 표기되어 있지 않아 성분을 까다롭게 따지는 경우 아쉬울 수 있습니다.</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -4768,8 +5188,16 @@
       <c r="J5" t="n">
         <v>675</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>운동 전 활력 부스팅 — 운동이나 야외 활동 전에 먹으면 확실히 덜 지치고 에너지가 나는 효과가 있습니다.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>소량 구성과 간편 휴대 — 2일분 소포장 구성으로 여행 시 챙기거나 사전 테스트용으로 부담 없이 구매할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -4815,9 +5243,21 @@
       <c r="J6" t="n">
         <v>3223</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>스틱형의 우수한 휴대성 — 무겁고 깨지기 쉬운 유리병 대신 가벼운 스틱 액상 포장이라 외출 시 휴대하기 편합니다.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>탄산 없는 속 편한 섭취 — 탄산이 들어있지 않아 복용 후 자극이 없고 은은한 멘톨향으로 상쾌합니다.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>신속한 소화 불편 완화 — 과식이나 식후 더부룩할 때 먹으면 속이 빠르게 편안해집니다.</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -4862,9 +5302,21 @@
       <c r="J7" t="n">
         <v>2088</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>편리한 야채 영양 섭취 — 챙겨 먹기 힘든 다양한 채소를 작고 씹어 먹기 편한 미니볼 형태로 섭취할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>새콤달콤한 사탕 맛 — 쓴맛 없이 새콤달콤한 사탕 같아 거부감 없이 간식처럼 맛있게 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>알찬 수량과 가성비 — 15포 들어있는 알찬 구성 대비 가격이 저렴하여 만족도가 높습니다.</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -4909,10 +5361,22 @@
       <c r="J8" t="n">
         <v>491</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>편리한 츄어블 제형 — 물 없이 씹어서 섭취할 수 있어 알약을 삼키기 어려운 아이나 성인 모두 편하게 먹습니다.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>부담 없는 영양과 풍미 — 과도한 고함량 부담이 없으며 은은한 우유 맛이 나 거부감이 적습니다.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>다소 단단한 제형 식감 — 씹어 먹는 츄어블 형태임에도 알약 제형이 다소 딱딱하게 느껴질 수 있습니다.</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -4956,9 +5420,21 @@
       <c r="J9" t="n">
         <v>204</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>눈 피로 개선 체감 — 안구 피로감이나 침침함, 눈꼽 생김 등을 완화하는 데 실질적인 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>목넘김이 쉬운 캡슐 크기 — 알약 크기가 작아 목에 걸리는 느낌 없이 편안하게 삼킬 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 부담 없는 가격으로 눈 건강 영양제를 꾸준히 복용할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -5003,9 +5479,21 @@
       <c r="J10" t="n">
         <v>460</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>원활한 배변 활동 도움 — 마그네슘과 식이섬유가 함께 함유되어 변비 완화 및 쾌변에 유용한 효과를 줍니다.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>상큼한 과일 맛 액상 — 섭취가 쉬운 액상 스틱 제형에 맛있는 포도 맛이 가미되어 먹기 즐겁습니다.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>간편한 짜먹는 스틱 포장 — 1포씩 간편하게 짜 먹을 수 있어 보관과 휴대가 용이합니다.</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5048,11 +5536,23 @@
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3272</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+        <v>3273</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>체계적인 복합 영양 설계 — 칼슘과 마그네슘의 2:1 비율 배합에 비타민D까지 한 번에 챙길 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>저렴하고 착한 가격 — 제약사 브랜드 제품임에도 5,000원의 저렴한 가격으로 구매가 가능합니다.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>간편한 뼈 건강 케어 — 여러 알을 복용할 필요 없이 한 번에 뼈와 관절 건강을 관리할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -5375,7 +5875,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>398</v>
@@ -5402,39 +5902,108 @@
         <v>460</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3272</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>압도적인 가격 경쟁력 — 다이소 판매 제품으로 3,000원이라는 매우 저렴한 가격에 한 달 분량을 구매할 수 있습니다.
+눈 떨림 및 근육 경련 완화 — 섭취 후 눈 밑 떨림이나 자다 다리에 쥐가 나는 증상이 크게 가라앉습니다.
+숙면 및 긴장 완화 효과 — 자기 전 복용 시 긴장을 풀어주어 깊은 잠을 자는 데 큰 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>시원하고 확실한 배변 작용 — 배가 아프지 않고 자연스럽고 시원하게 묵은 변을 배출해 줍니다.
+부담 없는 합리적 가격 — 편의점 대비 저렴한 2,000원 가격으로 부담 없이 구매할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>저렴한 고함량 비타민C — 비타민C 2000mg 고함량 제품을 5,000원이라는 저렴한 가격에 구매할 수 있습니다.
+위생적인 개별 스틱 포장 — 가루 형태의 개별 스틱 포장으로 되어 있어 휴대하고 챙겨 먹기 편합니다.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>운동 전 활력 부스팅 — 운동이나 야외 활동 전에 먹으면 확실히 덜 지치고 에너지가 나는 효과가 있습니다.
+소량 구성과 간편 휴대 — 2일분 소포장 구성으로 여행 시 챙기거나 사전 테스트용으로 부담 없이 구매할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>스틱형의 우수한 휴대성 — 무겁고 깨지기 쉬운 유리병 대신 가벼운 스틱 액상 포장이라 외출 시 휴대하기 편합니다.
+탄산 없는 속 편한 섭취 — 탄산이 들어있지 않아 복용 후 자극이 없고 은은한 멘톨향으로 상쾌합니다.
+신속한 소화 불편 완화 — 과식이나 식후 더부룩할 때 먹으면 속이 빠르게 편안해집니다.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>편리한 야채 영양 섭취 — 챙겨 먹기 힘든 다양한 채소를 작고 씹어 먹기 편한 미니볼 형태로 섭취할 수 있습니다.
+새콤달콤한 사탕 맛 — 쓴맛 없이 새콤달콤한 사탕 같아 거부감 없이 간식처럼 맛있게 먹을 수 있습니다.
+알찬 수량과 가성비 — 15포 들어있는 알찬 구성 대비 가격이 저렴하여 만족도가 높습니다.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>편리한 츄어블 제형 — 물 없이 씹어서 섭취할 수 있어 알약을 삼키기 어려운 아이나 성인 모두 편하게 먹습니다.
+부담 없는 영양과 풍미 — 과도한 고함량 부담이 없으며 은은한 우유 맛이 나 거부감이 적습니다.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>눈 피로 개선 체감 — 안구 피로감이나 침침함, 눈꼽 생김 등을 완화하는 데 실질적인 도움을 줍니다.
+목넘김이 쉬운 캡슐 크기 — 알약 크기가 작아 목에 걸리는 느낌 없이 편안하게 삼킬 수 있습니다.
+뛰어난 가성비 — 부담 없는 가격으로 눈 건강 영양제를 꾸준히 복용할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>원활한 배변 활동 도움 — 마그네슘과 식이섬유가 함께 함유되어 변비 완화 및 쾌변에 유용한 효과를 줍니다.
+상큼한 과일 맛 액상 — 섭취가 쉬운 액상 스틱 제형에 맛있는 포도 맛이 가미되어 먹기 즐겁습니다.
+간편한 짜먹는 스틱 포장 — 1포씩 간편하게 짜 먹을 수 있어 보관과 휴대가 용이합니다.</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>체계적인 복합 영양 설계 — 칼슘과 마그네슘의 2:1 비율 배합에 비타민D까지 한 번에 챙길 수 있습니다.
+저렴하고 착한 가격 — 제약사 브랜드 제품임에도 5,000원의 저렴한 가격으로 구매가 가능합니다.
+간편한 뼈 건강 케어 — 여러 알을 복용할 필요 없이 한 번에 뼈와 관절 건강을 관리할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>불편한 정제 배출 방식 — 상단 정제가 액상 안으로 잘 떨어지지 않아 손으로 직접 꺼내야 하는 불편함이 있습니다.
+기대와 다른 액상 맛 — 일반적인 포도주스 맛을 기대한 소비자는 다소 맛이 아쉽다고 느낄 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>원료 원산지 미표기 — 원산지 정보가 상세히 표기되어 있지 않아 성분을 까다롭게 따지는 경우 아쉬울 수 있습니다.</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>다소 단단한 제형 식감 — 씹어 먹는 츄어블 형태임에도 알약 제형이 다소 딱딱하게 느껴질 수 있습니다.</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
@@ -5708,10 +6277,22 @@
       <c r="J2" t="n">
         <v>14716</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>우수한 숙면 유도 효과 — 섭취 시 뒤척이지 않고 빠르게 깊은 잠에 들도록 도와줍니다.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>맛있는 구미 제형 — 정제 약 대신 달콤하고 맛있는 젤리 형태로 되어 있어 자기 전 부담 없이 먹기 좋습니다.</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>취침 전 재양치 필요성 — 젤리 제형 특성상 취침 전 섭취 후 양치를 다시 해야 하는 번거로움이 있습니다.</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -5755,9 +6336,21 @@
       <c r="J3" t="n">
         <v>8055</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>여성 이너뷰티 종합 케어 — 질유산균 성분으로 아침 공복에 챙겨 먹으며 장과 여성 건강을 한 번에 케어할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>간편한 1일 1캡슐 복용 — 하루 한 알만 챙기면 되는 직관적이고 편한 용법을 가집니다.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>풍성한 기획 세트 구성 — 증정품이 포함된 알찬 세트 구성으로 혜택이 좋습니다.</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -5802,8 +6395,16 @@
       <c r="J4" t="n">
         <v>24087</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 강화 — 꾸준한 섭취를 통해 장내 유익균을 늘리고 면역력을 튼튼하게 유지해 줍니다.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>풍성한 1+1 기획 혜택 — 1+1 구성과 사은품 증정으로 가격 대비 높은 만족감을 제공합니다.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -5849,9 +6450,21 @@
       <c r="J5" t="n">
         <v>457</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>체지방과 장 건강 이중 케어 — 장 유산균 케어와 체지방 관리를 동시에 해결해 주는 합리적인 제품입니다.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>맛있는 요거트 풍미 — 거부감 없는 상큼한 요거트 맛으로 매일 맛있게 섭취할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>속 더부룩함 완화 — 섭취 후 배에 가스가 차거나 더부룩한 증상이 줄어들고 속이 편안해집니다.</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -5896,8 +6509,16 @@
       <c r="J6" t="n">
         <v>12309</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>배 아픔 없는 원활한 배변 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 갈 수 있도록 돕습니다.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>피부와 장의 복합 관리 — 장 건강뿐만 아니라 피부 면역력 유지에도 도움을 주어 이너뷰티를 챙길 수 있습니다.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -5990,10 +6611,22 @@
       <c r="J8" t="n">
         <v>26614</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>체지방 감소 및 붓기 관리 — 디톡스 및 체지방 관리에 유용하며 과식 후 뱃살과 붓기를 정돈하는 데 도움을 줍니다.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>꾸준한 일상 다이어트 케어 — 무리하게 굶지 않고 일상에서 간편하게 보조제로 체중을 관리할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 정제의 크기가 다소 커서 삼킬 때 목넘김이 약간 불편할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -6037,8 +6670,16 @@
       <c r="J9" t="n">
         <v>15338</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>비타민C와 D 올인원 조합 — 면역에 좋은 비타민C와 햇빛이 부족한 실내인을 위한 비타민D를 한 번에 섭취할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>귀여운 증정품 파우치 기획 — 콜라보 캐릭터 파우치 등이 증정되어 구매 만족도를 높여줍니다.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6084,8 +6725,16 @@
       <c r="J10" t="n">
         <v>13672</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>다채롭고 맛있는 과일 맛 — 애플민트, 백도, 타트체리 등 맛있는 과일 맛 구미 형태라 맛있게 챙겨 먹을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>자연스러운 수면 유도 — 취침 전 섭취하면 뒤척임이 줄어들고 편안하게 잠들 수 있게 도와줍니다.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -6486,21 +7135,63 @@
         <v>6735</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>우수한 숙면 유도 효과 — 섭취 시 뒤척이지 않고 빠르게 깊은 잠에 들도록 도와줍니다.
+맛있는 구미 제형 — 정제 약 대신 달콤하고 맛있는 젤리 형태로 되어 있어 자기 전 부담 없이 먹기 좋습니다.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>여성 이너뷰티 종합 케어 — 질유산균 성분으로 아침 공복에 챙겨 먹으며 장과 여성 건강을 한 번에 케어할 수 있습니다.
+간편한 1일 1캡슐 복용 — 하루 한 알만 챙기면 되는 직관적이고 편한 용법을 가집니다.
+풍성한 기획 세트 구성 — 증정품이 포함된 알찬 세트 구성으로 혜택이 좋습니다.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 강화 — 꾸준한 섭취를 통해 장내 유익균을 늘리고 면역력을 튼튼하게 유지해 줍니다.
+풍성한 1+1 기획 혜택 — 1+1 구성과 사은품 증정으로 가격 대비 높은 만족감을 제공합니다.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>체지방과 장 건강 이중 케어 — 장 유산균 케어와 체지방 관리를 동시에 해결해 주는 합리적인 제품입니다.
+맛있는 요거트 풍미 — 거부감 없는 상큼한 요거트 맛으로 매일 맛있게 섭취할 수 있습니다.
+속 더부룩함 완화 — 섭취 후 배에 가스가 차거나 더부룩한 증상이 줄어들고 속이 편안해집니다.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>배 아픔 없는 원활한 배변 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 갈 수 있도록 돕습니다.
+피부와 장의 복합 관리 — 장 건강뿐만 아니라 피부 면역력 유지에도 도움을 주어 이너뷰티를 챙길 수 있습니다.</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>체지방 감소 및 붓기 관리 — 디톡스 및 체지방 관리에 유용하며 과식 후 뱃살과 붓기를 정돈하는 데 도움을 줍니다.
+꾸준한 일상 다이어트 케어 — 무리하게 굶지 않고 일상에서 간편하게 보조제로 체중을 관리할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>비타민C와 D 올인원 조합 — 면역에 좋은 비타민C와 햇빛이 부족한 실내인을 위한 비타민D를 한 번에 섭취할 수 있습니다.
+귀여운 증정품 파우치 기획 — 콜라보 캐릭터 파우치 등이 증정되어 구매 만족도를 높여줍니다.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>다채롭고 맛있는 과일 맛 — 애플민트, 백도, 타트체리 등 맛있는 과일 맛 구미 형태라 맛있게 챙겨 먹을 수 있습니다.
+자연스러운 수면 유도 — 취침 전 섭취하면 뒤척임이 줄어들고 편안하게 잠들 수 있게 도와줍니다.</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
@@ -6509,13 +7200,21 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 재양치 필요성 — 젤리 제형 특성상 취침 전 섭취 후 양치를 다시 해야 하는 번거로움이 있습니다.</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 정제의 크기가 다소 커서 삼킬 때 목넘김이 약간 불편할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
@@ -6787,7 +7486,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6800,16 +7499,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6819,10 +7518,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -6831,7 +7530,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6841,13 +7540,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">

--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -1195,14 +1195,139 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,135 +1342,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1450,157 +1450,157 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 섭취 시 확실히 피로가 풀리고 컨디션 회복 및 활력 충전에 도움을 줍니다.</t>
+          <t>편리한 섭취와 휴대성 — 액상과 정제 조합으로 먹기 쉽고 외출 시 휴대하기 용이함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>편리한 섭취와 우수한 휴대성 — 액상과 정제가 함께 있어 바쁜 아침에도 챙겨 먹기 편하고 휴대하기 쉽습니다.</t>
+          <t>고급스러운 선물 패키지 — 패키지가 고급스러워 지인이나 부모님 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 구성 — 패키지가 고급스러워 생일이나 응원 등 특별한 날 선물용으로 인기가 높습니다.</t>
+          <t>피로 회복 및 활력 증진 — 섭취 후 피로감이 줄어들고 컨디션 유지 및 활력 보충에 도움 됨</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>아쉬운 부직포 포장 재질 — 고급스러운 상자 포장 대신 부직포 재질로 되어 있어 이음새가 벌어지고 활용도가 떨어집니다.</t>
+          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용이나 활용도가 떨어짐</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2663,20 +2663,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>거부감 없는 상큼한 맛 — 쓴맛이 없고 망고피치 맛 액상이라 맛있게 섭취할 수 있습니다.</t>
+          <t>맛있는 망고피치 맛 — 비타민 특유의 쓴맛이나 냄새가 없고 망고피치 맛으로 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 올인원 제형 — 알약 크기가 작고 액상과 같이 들어 있어 물 없이도 편리하게 먹을 수 있습니다.</t>
+          <t>간편한 올인원 제형 — 액상과 정제가 같이 들어 있어 물 없이도 장소 구분 없이 먹기 편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>신속한 체력 보충 효과 — 피곤할 때 하나씩 꺼내 먹으면 활력이 충전되고 피로가 풀어집니다.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>우수한 활력 보충 효과 — 피로할 때 먹으면 에너지가 충전되고 체력 보충에 도움 됨</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>상대적으로 연한 맛과 효과 — 독일산 비타민 제품에 비해 섭취감이 다소 연하고 약하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2722,17 +2726,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 활력 증진 효과 — 몸이 나른하고 피곤할 때 섭취하면 활력이 생기고 힘이 납니다.</t>
+          <t>뛰어난 피로 회복 체감 — 몸이 피곤하거나 나른할 때 섭취하면 빠르게 기운이 나고 효과적임</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 패키지가 깔끔하고 고급스러워 소중한 분께 마음을 전하기 좋습니다.</t>
+          <t>고급스러운 기프트 패키지 — 상자 포장이 묵직하고 깔끔하며 고급스러워 선물용으로 아주 훌륭함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 섭취 — 언제 어디서나 들고 다니며 피곤할 때 마시기 편합니다.</t>
+          <t>편리한 휴대성 및 복용 — 개별 포장되어 갖고 다니기 편하고 피곤할 때 마시기 유용함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2781,22 +2785,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 과일 맛 구미 제형 — 달콤하고 상큼한 과일 맛 젤리 형태라 간식처럼 즐겁게 먹을 수 있습니다.</t>
+          <t>맛있는 과일 맛 젤리 — 쓴맛 없이 달콤한 과일 맛 구미 형태라 간식처럼 즐겁게 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>물 필요 없는 편리함 — 알약을 물과 함께 먹는 번거로움 없이 어디서나 씹어서 섭취 가능합니다.</t>
+          <t>물 필요 없는 편리함 — 물 없이 씹어서 간편하게 복용할 수 있어 영양제 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>감각적이고 예쁜 포장 — 제품 디자인과 이벤트 기획 포장이 예뻐서 선물용으로 반응이 좋습니다.</t>
+          <t>예쁜 선물용 패키지 — 포장 디자인이 예쁘고 알찬 구성이라 연령대 상관없이 선물하기 적합함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>아쉬운 일일 권장 섭취량 — 맛있어서 더 먹고 싶지만 하루 권장량이 2개로 제한되어 아쉽다는 반응이 있습니다.</t>
+          <t>적게 느껴지는 하루 권장량 — 맛에 비해 하루 섭취 권장량이 2개로 제한되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2844,17 +2848,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 기력 회복 체감 — 섭취 후 피로가 풀리고 기력이 회복되는 효과가 신속하게 느껴집니다.</t>
+          <t>빠른 피로 회복 효과 — 섭취 후 피로가 풀어지고 기력 회복 효과가 직관적으로 체감됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>위생적인 개별 포장 — 1회 섭취량씩 개별 포장되어 있어 들고 다니기 편하고 위생적입니다.</t>
+          <t>쉬운 알약 목넘김 — 정제 크기가 크지 않아 목넘김 부담 없이 액상과 함께 섭취 가능함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>부담 없는 목넘김과 맛 — 알약 크기가 적당하여 목넘김이 원활하고 맛도 좋아 먹기 좋습니다.</t>
+          <t>위생적인 개별 포장 — 1회분씩 개별 포장되어 있어 위생적이고 들고 다니기 편함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2903,17 +2907,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 편의성 — 맛이 좋아 거부감이 없으며 섭취 방법이 간단해 꾸준히 먹기 좋습니다.</t>
+          <t>맛있고 쉬운 복용법 — 맛이 좋고 먹기 편해 데일리로 지속해서 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>휴대하기 좋은 개별 용기 — 개별 병 형태라 가방에 들고 다니며 필요할 때 챙겨 먹기 편합니다.</t>
+          <t>간편한 휴대성 — 가방에 넣고 다니기 좋은 사이즈로 외출 시에도 챙기기 용이함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>체력 보충과 피로 완화 — 몸이 피곤할 때 먹으면 피로감이 풀리고 활력이 생기는 느낌을 받습니다.</t>
+          <t>체력 보충 및 피로 해소 — 몸이 피곤하고 체력이 떨어질 때 먹으면 컨디션 관리에 도움 됨</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2962,22 +2966,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>뛰어난 컨디션 개선 — 피로감이 심할 때 섭취하면 빠르게 활력이 돌아오고 피로가 감소합니다.</t>
+          <t>강력한 컨디션 회복 — 체력이 바닥났을 때 먹으면 피로감이 줄고 활력이 돋아남</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>진한 오렌지 맛과 휴대성 — 진한 오렌지 맛으로 부담 없이 먹을 수 있고 가방에 휴대하기 편합니다.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>높은 선물 만족도 — 고급스러운 패키지 구성 덕분에 선물을 받는 사람의 만족도가 높습니다.</t>
-        </is>
-      </c>
+          <t>진하고 상큼한 오렌지맛 — 진한 오렌지 맛 액상과 정제 조합으로 거부감 없이 맛있게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>부담스러운 제품 가격 — 제품 가격이 다소 비싸 직접 구매하기에는 고민이 된다는 의견이 있습니다.</t>
+          <t>부담스러운 가격대 — 제품의 가격이 다소 비싸 직접 상시 구매하기에는 부담이 큼</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>재미있는 섞어 마시기 방식 — 버튼을 눌러 분말을 액상에 섞어 먹는 구조가 신선하고 재미있습니다.</t>
+          <t>신선하고 재미있는 제형 — 버튼을 눌러 분말을 액상에 섞어 마시는 방식으로 섭취 재미가 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 풍미 — 건강식품 특유의 쓴맛 없이 음료처럼 상큼하고 맛있게 마실 수 있습니다.</t>
+          <t>상큼하고 맛있는 음료 맛 — 쓰지 않고 음료수처럼 상큼하고 맛있어 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 디자인 — 디자인과 구성이 알차고 고급스러워 정성 어린 선물로 제격입니다.</t>
+          <t>고급스러운 포장 디자인 — 패키지와 케이스가 예쁘고 알차서 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3084,17 +3084,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛 풍미 — 쓴맛이나 비린 느낌 없이 상큼한 레몬향이 나 호불호 없이 마시기 좋습니다.</t>
+          <t>상큼한 레몬 맛 — 쓴맛이나 비린 맛 없이 상큼한 레몬향으로 호불호 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편리한 올인원 휴대성 — 개별 포장된 한 병에 액상과 정제가 함께 있어 들고 다니며 먹기 편합니다.</t>
+          <t>올인원 일체형 제형 — 한 병에 액상과 정제가 같이 들어 있어 별도의 물 없이 간편하게 먹음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 증진 — 바쁜 일상이나 체력 소모가 많은 상황에서 덜 지치도록 도움을 줍니다.</t>
+          <t>피로 해소 및 활력 증진 — 바쁜 일상이나 피곤할 때 먹으면 덜 지치고 컨디션 유지에 도움 됨</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성별 맞춤형 영양 옵션 — 남성용과 여성용으로 구분되어 있어 개인의 필요에 맞게 선택 및 선물할 수 있습니다.</t>
+          <t>성별 맞춤 옵션 제공 — 남성용과 여성용이 세분화되어 있어 맞춤형 영양 케어가 가능함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>실용적인 분할 보관 패키지 — 고급스러운 포장에 박스가 나뉘어 있어 깔끔하게 보관하고 꺼내 먹기 편합니다.</t>
+          <t>피로감 감소 효과 — 하루 하나씩 섭취 시 피로함이 덜 느껴지고 활력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>지속적인 피로감 감소 — 꾸준히 섭취 시 활력이 생기고 매일 느끼던 피로함이 줄어듭니다.</t>
+          <t>고급스러운 선물용 포장 — 패키지 구성과 박스 포장이 고급스러워 직장 동료 선물로 적합함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3249,22 +3249,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 메뉴가 다양하게 구성되어 있어 식단 관리 중 매일 먹어도 물리지가 않습니다.</t>
+          <t>우수한 가성비 구성 — 저렴한 가격대에 알찬 수량으로 구성되어 경제적임</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 구성 — 합리적인 가격에 알찬 수량으로 구성되어 부담 없이 구매할 수 있습니다.</t>
+          <t>질리지 않는 촉촉함 — 퍽퍽함이 적고 자극적이지 않은 맛과 다양한 메뉴로 질리지 않음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>부드러운 식감과 간편 조리 — 닭가슴살 특유의 뻑뻑함이 적고 전자레인지로 간편하게 조리할 수 있습니다.</t>
+          <t>간편한 조리법 — 전자레인지 조리로 간편하게 데워 먹을 수 있어 식단 관리에 용이함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 중 해동 문제 — 배송 과정에서 제품이 완전히 녹아서도착하는 경우가 발생했습니다.</t>
+          <t>배송 중 해동 상태 — 배송 시 제품이 배송 과정에서 모두 녹아 도착하는 문제가 발생함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3312,17 +3312,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스러운 가방 포장 — 플리츠백 스타일의 예쁘고 럭셔리한 포장 덕분에 선물용으로 극찬을 받습니다.</t>
+          <t>럭셔리한 플리츠백 포장 — 가방 형태의 포장이 매우 예쁘고 활용성이 높아 선물용으로 최고임</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>상큼한 오렌지 맛 액상 — 거부감 없는 오렌지 맛 액상 타입이라 손쉽게 마실 수 있습니다.</t>
+          <t>콜라겐과 비오틴 복합 — 콜라겐과 비오틴을 따로 먹을 필요 없이 한 병으로 해결 가능함</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>피부 탄력 및 피로 개선 — 복용 후 푸석했던 피부에 탄력이 생기고 피로가 개선되는 느낌을 받습니다.</t>
+          <t>상큼한 오렌지맛 액상 — 오렌지 맛 액상 형태라 거부감 없이 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3371,22 +3371,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 육즙이 유지되어 다이어트 중에도 맛있게 먹을 수 있습니다.</t>
+          <t>촉촉하고 부드러운 식감 — 전자레인지 조리 후에도 육즙이 남아 있어 퍽퍽하지 않고 촉촉함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다채로운 식단 구성 — 닭가슴살 외에도 소시지, 큐브 등 다채로운 형태와 맛으로 구성되어 질리지 않습니다.</t>
+          <t>다양한 종류와 구성 — 닭가슴살, 소세지, 큐브 등 구성이 다채로워 식단 시 질리지 않음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>유용한 보냉백 제공 — 함께 제공되는 보냉백 덕분에 도시락용으로 들고 다니기 편리합니다.</t>
+          <t>유용한 보냉백 증정 — 도시락을 싸 다니기 좋은 보냉 파우치가 함께 증정되어 편리함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>증정품 디자인 불일치 — 라이브 방송에서 안내된 보냉백 디자인과 다른 제품이 배송되어 아쉬움을 남겼습니다.</t>
+          <t>증정품 디자인 불일치 — 방송에서 안내된 디자인과 다른 보냉백이 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3434,17 +3434,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>우수한 맛과 깔끔한 목넘김 — 단백질 특유의 비린내나 텁텁함이 없고 일반 초코우유처럼 매우 맛있습니다.</t>
+          <t>비린 맛없는 달콤한 맛 — 단백질 음료 특유의 텁텁함 없이 진한 초코우유처럼 맛이 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>속이 편한 락토프리 제형 — 락토프리 제품이라 빈속이나 운동 후 섭취해도 속이 편안합니다.</t>
+          <t>속 편한 락토프리 성분 — 제로 슈가 및 락토프리 제품으로 빈속에 마셔도 속이 편안함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>부담 없는 당류와 칼로리 — 제로슈가로 당류 부담 없이 높은 단백질을 효율적으로 충전할 수 있습니다.</t>
+          <t>운동 후 단백질 충전 — 운동 직후 단백질을 빠르게 보충하기에 적합하고 간편함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3493,24 +3493,20 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 풍미 — 거부감 있는 효소 향 대신 군고구마 향이 나 맛있게 먹을 수 있습니다.</t>
+          <t>고소한 군고구마 풍미 — 효소 특유의 냄새 없이 군고구마 향이 나 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>원활한 소화 및 배변 활동 — 과식 후 더부룩함을 누그러뜨리고 화장실을 편하게 가도록 도와줍니다.</t>
+          <t>푸짐한 추가 사은품 — 견과류바와 다양한 효소가 사은품으로 푸짐하게 제공됨</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>풍성한 사은품과 가성비 — 다양한 추가 사은품과 높은 할인 혜택으로 구매 만족도가 매우 높습니다.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>사은품 기프티콘 누락 — 이벤트 사은품으로 안내된 기프티콘을 받지 못했다는 불만이 있습니다.</t>
-        </is>
-      </c>
+          <t>속 편한 소화 개선 — 섭취 후 더부룩함이 줄어들고 배변 활동을 원활하게 도와줌</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3556,17 +3552,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>거부감 없는 무색무취 — 특별한 맛이나 냄새가 없고 입자가 고와 물이나 프로틴에 쉽게 타 먹을 수 있습니다.</t>
+          <t>무색·무취·무맛의 편안함 — 특별한 맛이나 향이 없어 입에 털어먹거나 물에 타기 수월함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 운동 전후 섭취 시 근육 펌핑감과 운동 효율을 높여 체력 증진에 도움을 줍니다.</t>
+          <t>고운 입자와 빠른 용해 — 입자가 고와서 물에 잘 녹고 흡수가 빠르게 느껴짐</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>우수한 가성비와 대용량 — 넉넉한 용량 대비 가격이 합리적이어서 꾸준히 섭취하기 좋습니다.</t>
+          <t>운동 퍼포먼스 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 큰 도움을 줌</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3615,17 +3611,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>풍부한 아르기닌 함량 — 1포당 초고함량의 아르기닌이 들어있어 확실한 활력 부스팅 효과를 줍니다.</t>
+          <t>고함량 아르기닌 성분 — 1포당 6,200mg의 고함량 아르기닌이 들어 있어 효과적임</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 베리 맛 — 특유의 거북한 맛을 잡고 상큼한 베리 맛을 내어 부담 없이 먹을 수 있습니다.</t>
+          <t>상큼한 베리 맛스틱 — 상큼한 맛으로 그냥 짜 먹거나 물에 타 마시기 편리함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>편리한 스틱 포장 — 스틱 형태로 제작되어 바로 짜 먹거나 물에 타서 마시기 편리합니다.</t>
+          <t>확실한 활력 개선 체감 — 피로감이 줄어들고 하루를 활기차게 보내는 데 도옴이 됨</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3674,17 +3670,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>역하지 않은 상큼한 레몬맛 — 특유의 향 없이 상큼한 레몬 맛이 나 영양제를 잘 못 먹는 사람도 쉽게 복용합니다.</t>
+          <t>맛있는 레몬 맛 액상 — 역하지 않고 상큼한 레몬 맛이라 영양제를 잘 못 먹는 사람도 쉬움</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 액상 스틱 형태 — 물 없이 바로 짜 먹을 수 있고 휴대가 용이하여 외출 시에도 챙겨 먹기 편합니다.</t>
+          <t>간편한 스틱 포장 — 스틱 형태라 외출 시 챙겨 다니기 쉽고 복용이 편리함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 높은 함량으로 섭취 후 피로 회복과 운동 활력 충전에 도움을 줍니다.</t>
+          <t>피로 회복 지원 — 복용 시 피로 해소에 도움을 주고 운동할 때 힘이 나는 느낌을 줌</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3733,7 +3729,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 제품 섭취 후 매우 뛰어난 숙취 해소 효과를 체감할 수 있습니다.</t>
+          <t>우수한 숙취 해소 — 섭취 시 숙취 해소 효과가 매우 뛰어나 만족스러움</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -4098,72 +4094,71 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 섭취 시 확실히 피로가 풀리고 컨디션 회복 및 활력 충전에 도움을 줍니다.
-편리한 섭취와 우수한 휴대성 — 액상과 정제가 함께 있어 바쁜 아침에도 챙겨 먹기 편하고 휴대하기 쉽습니다.
-고급스러운 선물용 구성 — 패키지가 고급스러워 생일이나 응원 등 특별한 날 선물용으로 인기가 높습니다.</t>
+          <t>편리한 섭취와 휴대성 — 액상과 정제 조합으로 먹기 쉽고 외출 시 휴대하기 용이함
+고급스러운 선물 패키지 — 패키지가 고급스러워 지인이나 부모님 선물용으로 적합함
+피로 회복 및 활력 증진 — 섭취 후 피로감이 줄어들고 컨디션 유지 및 활력 보충에 도움 됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 상큼한 맛 — 쓴맛이 없고 망고피치 맛 액상이라 맛있게 섭취할 수 있습니다.
-간편한 올인원 제형 — 알약 크기가 작고 액상과 같이 들어 있어 물 없이도 편리하게 먹을 수 있습니다.
-신속한 체력 보충 효과 — 피곤할 때 하나씩 꺼내 먹으면 활력이 충전되고 피로가 풀어집니다.</t>
+          <t>맛있는 망고피치 맛 — 비타민 특유의 쓴맛이나 냄새가 없고 망고피치 맛으로 맛있게 섭취 가능함
+간편한 올인원 제형 — 액상과 정제가 같이 들어 있어 물 없이도 장소 구분 없이 먹기 편함
+우수한 활력 보충 효과 — 피로할 때 먹으면 에너지가 충전되고 체력 보충에 도움 됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 활력 증진 효과 — 몸이 나른하고 피곤할 때 섭취하면 활력이 생기고 힘이 납니다.
-고급스러운 선물용 패키지 — 패키지가 깔끔하고 고급스러워 소중한 분께 마음을 전하기 좋습니다.
-간편한 휴대성과 섭취 — 언제 어디서나 들고 다니며 피곤할 때 마시기 편합니다.</t>
+          <t>뛰어난 피로 회복 체감 — 몸이 피곤하거나 나른할 때 섭취하면 빠르게 기운이 나고 효과적임
+고급스러운 기프트 패키지 — 상자 포장이 묵직하고 깔끔하며 고급스러워 선물용으로 아주 훌륭함
+편리한 휴대성 및 복용 — 개별 포장되어 갖고 다니기 편하고 피곤할 때 마시기 유용함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 과일 맛 구미 제형 — 달콤하고 상큼한 과일 맛 젤리 형태라 간식처럼 즐겁게 먹을 수 있습니다.
-물 필요 없는 편리함 — 알약을 물과 함께 먹는 번거로움 없이 어디서나 씹어서 섭취 가능합니다.
-감각적이고 예쁜 포장 — 제품 디자인과 이벤트 기획 포장이 예뻐서 선물용으로 반응이 좋습니다.</t>
+          <t>맛있는 과일 맛 젤리 — 쓴맛 없이 달콤한 과일 맛 구미 형태라 간식처럼 즐겁게 먹기 좋음
+물 필요 없는 편리함 — 물 없이 씹어서 간편하게 복용할 수 있어 영양제 챙겨 먹기 편함
+예쁜 선물용 패키지 — 포장 디자인이 예쁘고 알찬 구성이라 연령대 상관없이 선물하기 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 기력 회복 체감 — 섭취 후 피로가 풀리고 기력이 회복되는 효과가 신속하게 느껴집니다.
-위생적인 개별 포장 — 1회 섭취량씩 개별 포장되어 있어 들고 다니기 편하고 위생적입니다.
-부담 없는 목넘김과 맛 — 알약 크기가 적당하여 목넘김이 원활하고 맛도 좋아 먹기 좋습니다.</t>
+          <t>빠른 피로 회복 효과 — 섭취 후 피로가 풀어지고 기력 회복 효과가 직관적으로 체감됨
+쉬운 알약 목넘김 — 정제 크기가 크지 않아 목넘김 부담 없이 액상과 함께 섭취 가능함
+위생적인 개별 포장 — 1회분씩 개별 포장되어 있어 위생적이고 들고 다니기 편함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 편의성 — 맛이 좋아 거부감이 없으며 섭취 방법이 간단해 꾸준히 먹기 좋습니다.
-휴대하기 좋은 개별 용기 — 개별 병 형태라 가방에 들고 다니며 필요할 때 챙겨 먹기 편합니다.
-체력 보충과 피로 완화 — 몸이 피곤할 때 먹으면 피로감이 풀리고 활력이 생기는 느낌을 받습니다.</t>
+          <t>맛있고 쉬운 복용법 — 맛이 좋고 먹기 편해 데일리로 지속해서 챙겨 먹기 좋음
+간편한 휴대성 — 가방에 넣고 다니기 좋은 사이즈로 외출 시에도 챙기기 용이함
+체력 보충 및 피로 해소 — 몸이 피곤하고 체력이 떨어질 때 먹으면 컨디션 관리에 도움 됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 컨디션 개선 — 피로감이 심할 때 섭취하면 빠르게 활력이 돌아오고 피로가 감소합니다.
-진한 오렌지 맛과 휴대성 — 진한 오렌지 맛으로 부담 없이 먹을 수 있고 가방에 휴대하기 편합니다.
-높은 선물 만족도 — 고급스러운 패키지 구성 덕분에 선물을 받는 사람의 만족도가 높습니다.</t>
+          <t>강력한 컨디션 회복 — 체력이 바닥났을 때 먹으면 피로감이 줄고 활력이 돋아남
+진하고 상큼한 오렌지맛 — 진한 오렌지 맛 액상과 정제 조합으로 거부감 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>재미있는 섞어 마시기 방식 — 버튼을 눌러 분말을 액상에 섞어 먹는 구조가 신선하고 재미있습니다.
-상큼하고 맛있는 풍미 — 건강식품 특유의 쓴맛 없이 음료처럼 상큼하고 맛있게 마실 수 있습니다.
-고급스러운 선물용 디자인 — 디자인과 구성이 알차고 고급스러워 정성 어린 선물로 제격입니다.</t>
+          <t>신선하고 재미있는 제형 — 버튼을 눌러 분말을 액상에 섞어 마시는 방식으로 섭취 재미가 있음
+상큼하고 맛있는 음료 맛 — 쓰지 않고 음료수처럼 상큼하고 맛있어 부담 없이 복용 가능함
+고급스러운 포장 디자인 — 패키지와 케이스가 예쁘고 알차서 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛 풍미 — 쓴맛이나 비린 느낌 없이 상큼한 레몬향이 나 호불호 없이 마시기 좋습니다.
-편리한 올인원 휴대성 — 개별 포장된 한 병에 액상과 정제가 함께 있어 들고 다니며 먹기 편합니다.
-피로 개선 및 활력 증진 — 바쁜 일상이나 체력 소모가 많은 상황에서 덜 지치도록 도움을 줍니다.</t>
+          <t>상큼한 레몬 맛 — 쓴맛이나 비린 맛 없이 상큼한 레몬향으로 호불호 없이 섭취 가능함
+올인원 일체형 제형 — 한 병에 액상과 정제가 같이 들어 있어 별도의 물 없이 간편하게 먹음
+피로 해소 및 활력 증진 — 바쁜 일상이나 피곤할 때 먹으면 덜 지치고 컨디션 유지에 도움 됨</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤형 영양 옵션 — 남성용과 여성용으로 구분되어 있어 개인의 필요에 맞게 선택 및 선물할 수 있습니다.
-실용적인 분할 보관 패키지 — 고급스러운 포장에 박스가 나뉘어 있어 깔끔하게 보관하고 꺼내 먹기 편합니다.
-지속적인 피로감 감소 — 꾸준히 섭취 시 활력이 생기고 매일 느끼던 피로함이 줄어듭니다.</t>
+          <t>성별 맞춤 옵션 제공 — 남성용과 여성용이 세분화되어 있어 맞춤형 영양 케어가 가능함
+피로감 감소 효과 — 하루 하나씩 섭취 시 피로함이 덜 느껴지고 활력 증진에 도움 됨
+고급스러운 선물용 포장 — 패키지 구성과 박스 포장이 고급스러워 직장 동료 선물로 적합함</t>
         </is>
       </c>
     </row>
@@ -4175,21 +4170,25 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 부직포 포장 재질 — 고급스러운 상자 포장 대신 부직포 재질로 되어 있어 이음새가 벌어지고 활용도가 떨어집니다.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용이나 활용도가 떨어짐</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>상대적으로 연한 맛과 효과 — 독일산 비타민 제품에 비해 섭취감이 다소 연하고 약하게 느껴짐</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 일일 권장 섭취량 — 맛있어서 더 먹고 싶지만 하루 권장량이 2개로 제한되어 아쉽다는 반응이 있습니다.</t>
+          <t>적게 느껴지는 하루 권장량 — 맛에 비해 하루 섭취 권장량이 2개로 제한되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 제품 가격 — 제품 가격이 다소 비싸 직접 구매하기에는 고민이 된다는 의견이 있습니다.</t>
+          <t>부담스러운 가격대 — 제품의 가격이 다소 비싸 직접 상시 구매하기에는 부담이 큼</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -4638,63 +4637,63 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 메뉴가 다양하게 구성되어 있어 식단 관리 중 매일 먹어도 물리지가 않습니다.
-뛰어난 가성비 구성 — 합리적인 가격에 알찬 수량으로 구성되어 부담 없이 구매할 수 있습니다.
-부드러운 식감과 간편 조리 — 닭가슴살 특유의 뻑뻑함이 적고 전자레인지로 간편하게 조리할 수 있습니다.</t>
+          <t>우수한 가성비 구성 — 저렴한 가격대에 알찬 수량으로 구성되어 경제적임
+질리지 않는 촉촉함 — 퍽퍽함이 적고 자극적이지 않은 맛과 다양한 메뉴로 질리지 않음
+간편한 조리법 — 전자레인지 조리로 간편하게 데워 먹을 수 있어 식단 관리에 용이함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 가방 포장 — 플리츠백 스타일의 예쁘고 럭셔리한 포장 덕분에 선물용으로 극찬을 받습니다.
-상큼한 오렌지 맛 액상 — 거부감 없는 오렌지 맛 액상 타입이라 손쉽게 마실 수 있습니다.
-피부 탄력 및 피로 개선 — 복용 후 푸석했던 피부에 탄력이 생기고 피로가 개선되는 느낌을 받습니다.</t>
+          <t>럭셔리한 플리츠백 포장 — 가방 형태의 포장이 매우 예쁘고 활용성이 높아 선물용으로 최고임
+콜라겐과 비오틴 복합 — 콜라겐과 비오틴을 따로 먹을 필요 없이 한 병으로 해결 가능함
+상큼한 오렌지맛 액상 — 오렌지 맛 액상 형태라 거부감 없이 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 육즙이 유지되어 다이어트 중에도 맛있게 먹을 수 있습니다.
-다채로운 식단 구성 — 닭가슴살 외에도 소시지, 큐브 등 다채로운 형태와 맛으로 구성되어 질리지 않습니다.
-유용한 보냉백 제공 — 함께 제공되는 보냉백 덕분에 도시락용으로 들고 다니기 편리합니다.</t>
+          <t>촉촉하고 부드러운 식감 — 전자레인지 조리 후에도 육즙이 남아 있어 퍽퍽하지 않고 촉촉함
+다양한 종류와 구성 — 닭가슴살, 소세지, 큐브 등 구성이 다채로워 식단 시 질리지 않음
+유용한 보냉백 증정 — 도시락을 싸 다니기 좋은 보냉 파우치가 함께 증정되어 편리함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>우수한 맛과 깔끔한 목넘김 — 단백질 특유의 비린내나 텁텁함이 없고 일반 초코우유처럼 매우 맛있습니다.
-속이 편한 락토프리 제형 — 락토프리 제품이라 빈속이나 운동 후 섭취해도 속이 편안합니다.
-부담 없는 당류와 칼로리 — 제로슈가로 당류 부담 없이 높은 단백질을 효율적으로 충전할 수 있습니다.</t>
+          <t>비린 맛없는 달콤한 맛 — 단백질 음료 특유의 텁텁함 없이 진한 초코우유처럼 맛이 좋음
+속 편한 락토프리 성분 — 제로 슈가 및 락토프리 제품으로 빈속에 마셔도 속이 편안함
+운동 후 단백질 충전 — 운동 직후 단백질을 빠르게 보충하기에 적합하고 간편함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 풍미 — 거부감 있는 효소 향 대신 군고구마 향이 나 맛있게 먹을 수 있습니다.
-원활한 소화 및 배변 활동 — 과식 후 더부룩함을 누그러뜨리고 화장실을 편하게 가도록 도와줍니다.
-풍성한 사은품과 가성비 — 다양한 추가 사은품과 높은 할인 혜택으로 구매 만족도가 매우 높습니다.</t>
+          <t>고소한 군고구마 풍미 — 효소 특유의 냄새 없이 군고구마 향이 나 맛있게 먹을 수 있음
+푸짐한 추가 사은품 — 견과류바와 다양한 효소가 사은품으로 푸짐하게 제공됨
+속 편한 소화 개선 — 섭취 후 더부룩함이 줄어들고 배변 활동을 원활하게 도와줌</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 무색무취 — 특별한 맛이나 냄새가 없고 입자가 고와 물이나 프로틴에 쉽게 타 먹을 수 있습니다.
-운동 수행 능력 향상 — 운동 전후 섭취 시 근육 펌핑감과 운동 효율을 높여 체력 증진에 도움을 줍니다.
-우수한 가성비와 대용량 — 넉넉한 용량 대비 가격이 합리적이어서 꾸준히 섭취하기 좋습니다.</t>
+          <t>무색·무취·무맛의 편안함 — 특별한 맛이나 향이 없어 입에 털어먹거나 물에 타기 수월함
+고운 입자와 빠른 용해 — 입자가 고와서 물에 잘 녹고 흡수가 빠르게 느껴짐
+운동 퍼포먼스 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 큰 도움을 줌</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>풍부한 아르기닌 함량 — 1포당 초고함량의 아르기닌이 들어있어 확실한 활력 부스팅 효과를 줍니다.
-상큼하고 맛있는 베리 맛 — 특유의 거북한 맛을 잡고 상큼한 베리 맛을 내어 부담 없이 먹을 수 있습니다.
-편리한 스틱 포장 — 스틱 형태로 제작되어 바로 짜 먹거나 물에 타서 마시기 편리합니다.</t>
+          <t>고함량 아르기닌 성분 — 1포당 6,200mg의 고함량 아르기닌이 들어 있어 효과적임
+상큼한 베리 맛스틱 — 상큼한 맛으로 그냥 짜 먹거나 물에 타 마시기 편리함
+확실한 활력 개선 체감 — 피로감이 줄어들고 하루를 활기차게 보내는 데 도옴이 됨</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>역하지 않은 상큼한 레몬맛 — 특유의 향 없이 상큼한 레몬 맛이 나 영양제를 잘 못 먹는 사람도 쉽게 복용합니다.
-간편한 액상 스틱 형태 — 물 없이 바로 짜 먹을 수 있고 휴대가 용이하여 외출 시에도 챙겨 먹기 편합니다.
-확실한 피로 회복 체감 — 높은 함량으로 섭취 후 피로 회복과 운동 활력 충전에 도움을 줍니다.</t>
+          <t>맛있는 레몬 맛 액상 — 역하지 않고 상큼한 레몬 맛이라 영양제를 잘 못 먹는 사람도 쉬움
+간편한 스틱 포장 — 스틱 형태라 외출 시 챙겨 다니기 쉽고 복용이 편리함
+피로 회복 지원 — 복용 시 피로 해소에 도움을 주고 운동할 때 힘이 나는 느낌을 줌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 제품 섭취 후 매우 뛰어난 숙취 해소 효과를 체감할 수 있습니다.</t>
+          <t>우수한 숙취 해소 — 섭취 시 숙취 해소 효과가 매우 뛰어나 만족스러움</t>
         </is>
       </c>
     </row>
@@ -4707,21 +4706,17 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 문제 — 배송 과정에서 제품이 완전히 녹아서도착하는 경우가 발생했습니다.</t>
+          <t>배송 중 해동 상태 — 배송 시 제품이 배송 과정에서 모두 녹아 도착하는 문제가 발생함</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>증정품 디자인 불일치 — 라이브 방송에서 안내된 보냉백 디자인과 다른 제품이 배송되어 아쉬움을 남겼습니다.</t>
+          <t>증정품 디자인 불일치 — 방송에서 안내된 디자인과 다른 보냉백이 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>사은품 기프티콘 누락 — 이벤트 사은품으로 안내된 기프티콘을 받지 못했다는 불만이 있습니다.</t>
-        </is>
-      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4970,7 +4965,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4978,7 +4973,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4988,48 +4983,52 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>5851</v>
+        <v>3324</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>압도적인 가격 경쟁력 — 다이소 판매 제품으로 3,000원이라는 매우 저렴한 가격에 한 달 분량을 구매할 수 있습니다.</t>
+          <t>최고의 가성비 — 5,000원이라는 저렴한 가격으로 한 달 치 비타민을 챙길 수 있음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>눈 떨림 및 근육 경련 완화 — 섭취 후 눈 밑 떨림이나 자다 다리에 쥐가 나는 증상이 크게 가라앉습니다.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>숙면 및 긴장 완화 효과 — 자기 전 복용 시 긴장을 풀어주어 깊은 잠을 자는 데 큰 도움을 줍니다.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>알찬 영양 성분 배합 — 한국인 맞춤형으로 비타민 12종과 미네랄 7종이 포함됨</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>상대적으로 낮은 함량 — 저렴한 가격 특성상 약국 제품에 비해 영양 성분 함량이 적을 수 있음</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>살짝 큰 알약 크기 — 사람에 따라 정제 알약의 크기가 약간 크게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5037,62 +5036,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>398</v>
+        <v>5851</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>시원하고 확실한 배변 작용 — 배가 아프지 않고 자연스럽고 시원하게 묵은 변을 배출해 줍니다.</t>
+          <t>수면 및 근육 완화 체감 — 눈 떨림 및 다리 쥐 증상이 개선되고 숙면을 취하는 데 큰 도움 됨</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>부담 없는 합리적 가격 — 편의점 대비 저렴한 2,000원 가격으로 부담 없이 구매할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>불편한 정제 배출 방식 — 상단 정제가 액상 안으로 잘 떨어지지 않아 손으로 직접 꺼내야 하는 불편함이 있습니다.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>기대와 다른 액상 맛 — 일반적인 포도주스 맛을 기대한 소비자는 다소 맛이 아쉽다고 느낄 수 있습니다.</t>
-        </is>
-      </c>
+          <t>부담 없는 저렴한 가격 — 3,000원에 마그네슘 권장량을 채울 수 있어 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>속 편한 섭취감 — 복용 시 속 쓰림 없이 편안하게 지속해서 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5100,49 +5095,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911092&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260814/qU3FUPerTqzVYxrqf7Lx610911092_00_01qU3FUPerTqzVYxrqf7Lx.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>47</v>
+        <v>4461</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>저렴한 고함량 비타민C — 비타민C 2000mg 고함량 제품을 5,000원이라는 저렴한 가격에 구매할 수 있습니다.</t>
+          <t>작은 정제와 편한 목넘김 — 알약 크기가 작아서 물과 함께 삼키기가 매우 수월함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>위생적인 개별 스틱 포장 — 가루 형태의 개별 스틱 포장으로 되어 있어 휴대하고 챙겨 먹기 편합니다.</t>
+          <t>식전 혈당 관리 용이 — 식전 복용으로 간단하게 혈당 스파이크 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>원료 원산지 미표기 — 원산지 정보가 상세히 표기되어 있지 않아 성분을 까다롭게 따지는 경우 아쉬울 수 있습니다.</t>
+          <t>미흡한 체감 효과 — 개인차에 따라 식후 졸음이나 혈당 조절 측면의 직접 체감이 부족함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -5151,7 +5146,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5159,47 +5154,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>675</v>
+        <v>6137</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>운동 전 활력 부스팅 — 운동이나 야외 활동 전에 먹으면 확실히 덜 지치고 에너지가 나는 효과가 있습니다.</t>
+          <t>고함량 대비 뛰어난 가성비 — 하루 권장량 100mg을 저렴한 가격으로 챙길 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>소량 구성과 간편 휴대 — 2일분 소포장 구성으로 여행 시 챙기거나 사전 테스트용으로 부담 없이 구매할 수 있습니다.</t>
+          <t>활력 및 피로 개선 — 꾸준한 복용 시 몸이 가벼워지고 일상 활력 증진에 도옴을 줌</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>저녁 복용 시 수면 영향 — 저녁 식후에 복용할 경우 사람에 따라 잠들기 어려울 수 있음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -5214,50 +5213,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3223</v>
+        <v>3422</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>스틱형의 우수한 휴대성 — 무겁고 깨지기 쉬운 유리병 대신 가벼운 스틱 액상 포장이라 외출 시 휴대하기 편합니다.</t>
+          <t>동일 성분 대비 갓성비 — 유명 브랜드 제품과 동일한 함량을 5,000원에 구매 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>탄산 없는 속 편한 섭취 — 탄산이 들어있지 않아 복용 후 자극이 없고 은은한 멘톨향으로 상쾌합니다.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>신속한 소화 불편 완화 — 과식이나 식후 더부룩할 때 먹으면 속이 빠르게 편안해집니다.</t>
-        </is>
-      </c>
+          <t>체지방 관리 및 부담 해소 — 기름진 음식이나 탄수화물 섭취 후 부담을 줄여주는 데 유용함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -5265,7 +5260,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5273,48 +5268,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2088</v>
+        <v>3273</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>편리한 야채 영양 섭취 — 챙겨 먹기 힘든 다양한 채소를 작고 씹어 먹기 편한 미니볼 형태로 섭취할 수 있습니다.</t>
+          <t>칼마디 황금 비율 조합 — 칼슘과 마그네슘의 2:1 비율 및 비타민D 복합 구성으로 흡수에 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>새콤달콤한 사탕 맛 — 쓴맛 없이 새콤달콤한 사탕 같아 거부감 없이 간식처럼 맛있게 먹을 수 있습니다.</t>
+          <t>3종 결합 가성비 — 뼈 건강 필수 영양소 3가지를 5천원에 한 번에 먹을 수 있음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>알찬 수량과 가성비 — 15포 들어있는 알찬 구성 대비 가격이 저렴하여 만족도가 높습니다.</t>
+          <t>간편한 뼈 관절 관리 — 여러 개를 따로 챙길 필요 없이 한 알로 해결되어 용이함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -5324,7 +5319,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5332,49 +5327,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 어린이 칼슘 마그네슘D 츄어블 60정 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000143&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/mx3ripII7mLHu95jzlBA600000143_00_00mx3ripII7mLHu95jzlBA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>491</v>
+        <v>2396</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>편리한 츄어블 제형 — 물 없이 씹어서 섭취할 수 있어 알약을 삼키기 어려운 아이나 성인 모두 편하게 먹습니다.</t>
+          <t>우수한 배변 활동 지원 — 마신 후 화장실을 잘 가게 되어 속이 가벼워지고 편안해짐</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>부담 없는 영양과 풍미 — 과도한 고함량 부담이 없으며 은은한 우유 맛이 나 거부감이 적습니다.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>커피 대용으로 적합 — 찬물에 잘 녹고 아메리카노와 유사하여 부담 없이 마시기 좋음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>편리한 스틱 포장 — 개별 스틱 포장이라 외출이나 회사에서 챙겨 마시기 편함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>다소 단단한 제형 식감 — 씹어 먹는 츄어블 형태임에도 알약 제형이 다소 딱딱하게 느껴질 수 있습니다.</t>
+          <t>소용량 및 씁쓸한 맛 — 1포 용량이 적어 2포를 타야 진해지며 사람에 따라 다소 씁쓸함</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5383,7 +5382,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5391,12 +5390,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 눈피로엔 아이포커스 미니 20캡슐</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5406,33 +5405,33 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982832&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/eUpKnXlsDmWUTHaFdSd5611982832_00_00eUpKnXlsDmWUTHaFdSd5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>204</v>
+        <v>5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>눈 피로 개선 체감 — 안구 피로감이나 침침함, 눈꼽 생김 등을 완화하는 데 실질적인 도움을 줍니다.</t>
+          <t>고급스러운 기프트 포장 — 패키지가 고급스러워 명절이나 부모님 선물용으로 추천할 만함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>목넘김이 쉬운 캡슐 크기 — 알약 크기가 작아 목에 걸리는 느낌 없이 편안하게 삼킬 수 있습니다.</t>
+          <t>부담 없는 쓴맛 — 홍삼 특유의 강한 쓴맛이 적어 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 부담 없는 가격으로 눈 건강 영양제를 꾸준히 복용할 수 있습니다.</t>
+          <t>휴대성 및 복용 편의 — 개별 환 포장으로 들고 다니기 좋고 복용이 간편함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -5442,7 +5441,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5450,58 +5449,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/wJCESiflDyulw8oZ8pW1601618642_00_00wJCESiflDyulw8oZ8pW1.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>460</v>
+        <v>6059</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 마그네슘과 식이섬유가 함께 함유되어 변비 완화 및 쾌변에 유용한 효과를 줍니다.</t>
+          <t>비린내 없는 깔끔함 — 섭취 후 생선 비린내가 오르지 않아 거부감 없이 복용 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>상큼한 과일 맛 액상 — 섭취가 쉬운 액상 스틱 제형에 맛있는 포도 맛이 가미되어 먹기 즐겁습니다.</t>
+          <t>안구 건조 개선 효과 — 꾸준히 복용 시 눈의 뻑뻑함과 건조함 완화에 도움이 됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>간편한 짜먹는 스틱 포장 — 1포씩 간편하게 짜 먹을 수 있어 보관과 휴대가 용이합니다.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>rTG 오메가3 가성비 — rTG 형태 오메가3를 5,000원에 부담 없이 지속 구매 가능함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 및 잦은 품절 — 캡슐 크기가 커 삼키기 어려울 수 있으며 품절이 자주 발생함</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5509,7 +5512,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5524,33 +5527,33 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3273</v>
+        <v>3564</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>체계적인 복합 영양 설계 — 칼슘과 마그네슘의 2:1 비율 배합에 비타민D까지 한 번에 챙길 수 있습니다.</t>
+          <t>속 더부룩함 없는 복용감 — 타사 제품 대비 섭취 후 속 더부룩함이나 불편함이 적음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>저렴하고 착한 가격 — 제약사 브랜드 제품임에도 5,000원의 저렴한 가격으로 구매가 가능합니다.</t>
+          <t>간 피로 개선 체감 — 꾸준히 복용 시 피로감이 줄어들고 컨디션 유지에 도움 됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>간편한 뼈 건강 케어 — 여러 알을 복용할 필요 없이 한 번에 뼈와 관절 건강을 관리할 수 있습니다.</t>
+          <t>비타민B 복합 가성비 — 밀크씨슬과 비타민B군을 저렴한 가격으로 한 번에 보충함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -5668,52 +5671,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -5730,42 +5733,42 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5782,52 +5785,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 어린이 칼슘 마그네슘D 츄어블 60정 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 눈피로엔 아이포커스 미니 20캡슐</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5844,10 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5853,7 +5856,7 @@
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.7</v>
@@ -5862,7 +5865,7 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5875,34 +5878,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>3324</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>5851</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>398</v>
-      </c>
       <c r="E7" s="3" t="n">
-        <v>47</v>
+        <v>4461</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>675</v>
+        <v>6137</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3223</v>
+        <v>3422</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2088</v>
+        <v>3273</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>491</v>
+        <v>2396</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>204</v>
+        <v>5</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>460</v>
+        <v>6059</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3273</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5913,68 +5916,68 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가격 경쟁력 — 다이소 판매 제품으로 3,000원이라는 매우 저렴한 가격에 한 달 분량을 구매할 수 있습니다.
-눈 떨림 및 근육 경련 완화 — 섭취 후 눈 밑 떨림이나 자다 다리에 쥐가 나는 증상이 크게 가라앉습니다.
-숙면 및 긴장 완화 효과 — 자기 전 복용 시 긴장을 풀어주어 깊은 잠을 자는 데 큰 도움을 줍니다.</t>
+          <t>최고의 가성비 — 5,000원이라는 저렴한 가격으로 한 달 치 비타민을 챙길 수 있음
+알찬 영양 성분 배합 — 한국인 맞춤형으로 비타민 12종과 미네랄 7종이 포함됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>시원하고 확실한 배변 작용 — 배가 아프지 않고 자연스럽고 시원하게 묵은 변을 배출해 줍니다.
-부담 없는 합리적 가격 — 편의점 대비 저렴한 2,000원 가격으로 부담 없이 구매할 수 있습니다.</t>
+          <t>수면 및 근육 완화 체감 — 눈 떨림 및 다리 쥐 증상이 개선되고 숙면을 취하는 데 큰 도움 됨
+부담 없는 저렴한 가격 — 3,000원에 마그네슘 권장량을 채울 수 있어 가성비가 훌륭함
+속 편한 섭취감 — 복용 시 속 쓰림 없이 편안하게 지속해서 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 고함량 비타민C — 비타민C 2000mg 고함량 제품을 5,000원이라는 저렴한 가격에 구매할 수 있습니다.
-위생적인 개별 스틱 포장 — 가루 형태의 개별 스틱 포장으로 되어 있어 휴대하고 챙겨 먹기 편합니다.</t>
+          <t>작은 정제와 편한 목넘김 — 알약 크기가 작아서 물과 함께 삼키기가 매우 수월함
+식전 혈당 관리 용이 — 식전 복용으로 간단하게 혈당 스파이크 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>운동 전 활력 부스팅 — 운동이나 야외 활동 전에 먹으면 확실히 덜 지치고 에너지가 나는 효과가 있습니다.
-소량 구성과 간편 휴대 — 2일분 소포장 구성으로 여행 시 챙기거나 사전 테스트용으로 부담 없이 구매할 수 있습니다.</t>
+          <t>고함량 대비 뛰어난 가성비 — 하루 권장량 100mg을 저렴한 가격으로 챙길 수 있어 만족스러움
+활력 및 피로 개선 — 꾸준한 복용 시 몸이 가벼워지고 일상 활력 증진에 도옴을 줌</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>스틱형의 우수한 휴대성 — 무겁고 깨지기 쉬운 유리병 대신 가벼운 스틱 액상 포장이라 외출 시 휴대하기 편합니다.
-탄산 없는 속 편한 섭취 — 탄산이 들어있지 않아 복용 후 자극이 없고 은은한 멘톨향으로 상쾌합니다.
-신속한 소화 불편 완화 — 과식이나 식후 더부룩할 때 먹으면 속이 빠르게 편안해집니다.</t>
+          <t>동일 성분 대비 갓성비 — 유명 브랜드 제품과 동일한 함량을 5,000원에 구매 가능함
+체지방 관리 및 부담 해소 — 기름진 음식이나 탄수화물 섭취 후 부담을 줄여주는 데 유용함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>편리한 야채 영양 섭취 — 챙겨 먹기 힘든 다양한 채소를 작고 씹어 먹기 편한 미니볼 형태로 섭취할 수 있습니다.
-새콤달콤한 사탕 맛 — 쓴맛 없이 새콤달콤한 사탕 같아 거부감 없이 간식처럼 맛있게 먹을 수 있습니다.
-알찬 수량과 가성비 — 15포 들어있는 알찬 구성 대비 가격이 저렴하여 만족도가 높습니다.</t>
+          <t>칼마디 황금 비율 조합 — 칼슘과 마그네슘의 2:1 비율 및 비타민D 복합 구성으로 흡수에 좋음
+3종 결합 가성비 — 뼈 건강 필수 영양소 3가지를 5천원에 한 번에 먹을 수 있음
+간편한 뼈 관절 관리 — 여러 개를 따로 챙길 필요 없이 한 알로 해결되어 용이함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>편리한 츄어블 제형 — 물 없이 씹어서 섭취할 수 있어 알약을 삼키기 어려운 아이나 성인 모두 편하게 먹습니다.
-부담 없는 영양과 풍미 — 과도한 고함량 부담이 없으며 은은한 우유 맛이 나 거부감이 적습니다.</t>
+          <t>우수한 배변 활동 지원 — 마신 후 화장실을 잘 가게 되어 속이 가벼워지고 편안해짐
+커피 대용으로 적합 — 찬물에 잘 녹고 아메리카노와 유사하여 부담 없이 마시기 좋음
+편리한 스틱 포장 — 개별 스틱 포장이라 외출이나 회사에서 챙겨 마시기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>눈 피로 개선 체감 — 안구 피로감이나 침침함, 눈꼽 생김 등을 완화하는 데 실질적인 도움을 줍니다.
-목넘김이 쉬운 캡슐 크기 — 알약 크기가 작아 목에 걸리는 느낌 없이 편안하게 삼킬 수 있습니다.
-뛰어난 가성비 — 부담 없는 가격으로 눈 건강 영양제를 꾸준히 복용할 수 있습니다.</t>
+          <t>고급스러운 기프트 포장 — 패키지가 고급스러워 명절이나 부모님 선물용으로 추천할 만함
+부담 없는 쓴맛 — 홍삼 특유의 강한 쓴맛이 적어 부담 없이 먹을 수 있음
+휴대성 및 복용 편의 — 개별 환 포장으로 들고 다니기 좋고 복용이 간편함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 마그네슘과 식이섬유가 함께 함유되어 변비 완화 및 쾌변에 유용한 효과를 줍니다.
-상큼한 과일 맛 액상 — 섭취가 쉬운 액상 스틱 제형에 맛있는 포도 맛이 가미되어 먹기 즐겁습니다.
-간편한 짜먹는 스틱 포장 — 1포씩 간편하게 짜 먹을 수 있어 보관과 휴대가 용이합니다.</t>
+          <t>비린내 없는 깔끔함 — 섭취 후 생선 비린내가 오르지 않아 거부감 없이 복용 가능함
+안구 건조 개선 효과 — 꾸준히 복용 시 눈의 뻑뻑함과 건조함 완화에 도움이 됨
+rTG 오메가3 가성비 — rTG 형태 오메가3를 5,000원에 부담 없이 지속 구매 가능함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>체계적인 복합 영양 설계 — 칼슘과 마그네슘의 2:1 비율 배합에 비타민D까지 한 번에 챙길 수 있습니다.
-저렴하고 착한 가격 — 제약사 브랜드 제품임에도 5,000원의 저렴한 가격으로 구매가 가능합니다.
-간편한 뼈 건강 케어 — 여러 알을 복용할 필요 없이 한 번에 뼈와 관절 건강을 관리할 수 있습니다.</t>
+          <t>속 더부룩함 없는 복용감 — 타사 제품 대비 섭취 후 속 더부룩함이나 불편함이 적음
+간 피로 개선 체감 — 꾸준히 복용 시 피로감이 줄어들고 컨디션 유지에 도움 됨
+비타민B 복합 가성비 — 밀크씨슬과 비타민B군을 저렴한 가격으로 한 번에 보충함</t>
         </is>
       </c>
     </row>
@@ -5984,28 +5987,36 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>불편한 정제 배출 방식 — 상단 정제가 액상 안으로 잘 떨어지지 않아 손으로 직접 꺼내야 하는 불편함이 있습니다.
-기대와 다른 액상 맛 — 일반적인 포도주스 맛을 기대한 소비자는 다소 맛이 아쉽다고 느낄 수 있습니다.</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>상대적으로 낮은 함량 — 저렴한 가격 특성상 약국 제품에 비해 영양 성분 함량이 적을 수 있음
+살짝 큰 알약 크기 — 사람에 따라 정제 알약의 크기가 약간 크게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>원료 원산지 미표기 — 원산지 정보가 상세히 표기되어 있지 않아 성분을 까다롭게 따지는 경우 아쉬울 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
+          <t>미흡한 체감 효과 — 개인차에 따라 식후 졸음이나 혈당 조절 측면의 직접 체감이 부족함</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>저녁 복용 시 수면 영향 — 저녁 식후에 복용할 경우 사람에 따라 잠들기 어려울 수 있음</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>다소 단단한 제형 식감 — 씹어 먹는 츄어블 형태임에도 알약 제형이 다소 딱딱하게 느껴질 수 있습니다.</t>
+          <t>소용량 및 씁쓸한 맛 — 1포 용량이 적어 2포를 타야 진해지며 사람에 따라 다소 씁쓸함</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 및 잦은 품절 — 캡슐 크기가 커 삼키기 어려울 수 있으며 품절이 자주 발생함</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6016,47 +6027,47 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1,500원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6275,24 +6286,20 @@
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>14716</v>
+        <v>14719</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 숙면 유도 효과 — 섭취 시 뒤척이지 않고 빠르게 깊은 잠에 들도록 도와줍니다.</t>
+          <t>맛있는 젤리 형태 — 알약이 아닌 달콤한 구미 타입이라 섭취 부담이 없음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형 — 정제 약 대신 달콤하고 맛있는 젤리 형태로 되어 있어 자기 전 부담 없이 먹기 좋습니다.</t>
+          <t>빠르고 깊은 수면 유도 — 취침 전 복용 시 잠에 금방 들고 푹 자는 데 효과적임</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>취침 전 재양치 필요성 — 젤리 제형 특성상 취침 전 섭취 후 양치를 다시 해야 하는 번거로움이 있습니다.</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -6338,19 +6345,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>여성 이너뷰티 종합 케어 — 질유산균 성분으로 아침 공복에 챙겨 먹으며 장과 여성 건강을 한 번에 케어할 수 있습니다.</t>
+          <t>하루 한 알 간편 케어 — 아침 공복에 1캡슐로 여성 건강과 장 건강을 관리함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 1일 1캡슐 복용 — 하루 한 알만 챙기면 되는 직관적이고 편한 용법을 가집니다.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>풍성한 기획 세트 구성 — 증정품이 포함된 알찬 세트 구성으로 혜택이 좋습니다.</t>
-        </is>
-      </c>
+          <t>넉넉한 더블 기획 구성 — 2개월 분량의 알찬 구성으로 넉넉하게 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6397,12 +6400,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>장 건강 및 면역력 강화 — 꾸준한 섭취를 통해 장내 유익균을 늘리고 면역력을 튼튼하게 유지해 줍니다.</t>
+          <t>장 건강 및 면역 케어 — 꾸준히 먹으면 장이 편안해지고 면역 유지에 도움을 줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>풍성한 1+1 기획 혜택 — 1+1 구성과 사은품 증정으로 가격 대비 높은 만족감을 제공합니다.</t>
+          <t>혜자스러운 1+1 기획 — 1+1 더블 구성과 증정품을 함께 얻을 수 있어 가성비 높음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -6452,17 +6455,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 이중 케어 — 장 유산균 케어와 체지방 관리를 동시에 해결해 주는 합리적인 제품입니다.</t>
+          <t>장과 체지방 동시 관리 — 체지방 감소와 장 건강을 함께 챙기는 이중 기능성 제품임</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>맛있는 요거트 풍미 — 거부감 없는 상큼한 요거트 맛으로 매일 맛있게 섭취할 수 있습니다.</t>
+          <t>상큼한 요거트 맛 — 상큼한 요거트 맛이라 하루 한 포씩 맛있게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>속 더부룩함 완화 — 섭취 후 배에 가스가 차거나 더부룩한 증상이 줄어들고 속이 편안해집니다.</t>
+          <t>속 편한 뱃살 케어 — 복용 시 아랫배가 가벼워지고 더부룩한 속이 한결 편안해짐</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -6511,12 +6514,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>배 아픔 없는 원활한 배변 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 갈 수 있도록 돕습니다.</t>
+          <t>속 편한 배변 활동 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 가도록 도움</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>피부와 장의 복합 관리 — 장 건강뿐만 아니라 피부 면역력 유지에도 도움을 주어 이너뷰티를 챙길 수 있습니다.</t>
+          <t>장과 피부 면역 동시 보충 — 100억 유산균으로 장 건강과 피부 면역 관리를 동시에 진행함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -6613,18 +6616,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>체지방 감소 및 붓기 관리 — 디톡스 및 체지방 관리에 유용하며 과식 후 뱃살과 붓기를 정돈하는 데 도움을 줍니다.</t>
+          <t>확실한 디톡스 및 붓기 제거 — 과식 후 디톡스나 급진급빠 시 뱃살이 들어가고 라인이 정돈됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>꾸준한 일상 다이어트 케어 — 무리하게 굶지 않고 일상에서 간편하게 보조제로 체중을 관리할 수 있습니다.</t>
+          <t>원활한 속 비움 효과 — 섭취 시 화장실을 잘 가게 되고 묵직했던 속이 개운해짐</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 정제의 크기가 다소 커서 삼킬 때 목넘김이 약간 불편할 수 있습니다.</t>
+          <t>다소 큰 알약 크기 — 정제 사이즈가 좀 더 커서 삼킬 때 다소 부담이 느껴짐</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -6672,12 +6675,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>비타민C와 D 올인원 조합 — 면역에 좋은 비타민C와 햇빛이 부족한 실내인을 위한 비타민D를 한 번에 섭취할 수 있습니다.</t>
+          <t>비타민 C와 D의 올인원 — 면역 관리를 돕는 비타민C와 결핍되기 쉬운 비타민D를 한 번에 복용함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>귀여운 증정품 파우치 기획 — 콜라보 캐릭터 파우치 등이 증정되어 구매 만족도를 높여줍니다.</t>
+          <t>높은 신뢰도와 가성비 — 믿을 수 있는 대표 브랜드 제품으로 꾸준히 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6723,16 +6726,16 @@
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>13672</v>
+        <v>13675</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>다채롭고 맛있는 과일 맛 — 애플민트, 백도, 타트체리 등 맛있는 과일 맛 구미 형태라 맛있게 챙겨 먹을 수 있습니다.</t>
+          <t>빠른 숙면 유도 체감 — 뒤척임 없이 금방 잠들고 새벽에 깨지 않도록 수면의 질을 높임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>자연스러운 수면 유도 — 취침 전 섭취하면 뒤척임이 줄어들고 편안하게 잠들 수 있게 도와줍니다.</t>
+          <t>맛있는 식물성 구미 — 부담 없는 식물성 성분에 달콤한 젤리 맛이라 지속 복용하기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -7105,7 +7108,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14716</v>
+        <v>14719</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>8055</v>
@@ -7129,7 +7132,7 @@
         <v>15338</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>13672</v>
+        <v>13675</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>6735</v>
@@ -7143,53 +7146,52 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 숙면 유도 효과 — 섭취 시 뒤척이지 않고 빠르게 깊은 잠에 들도록 도와줍니다.
-맛있는 구미 제형 — 정제 약 대신 달콤하고 맛있는 젤리 형태로 되어 있어 자기 전 부담 없이 먹기 좋습니다.</t>
+          <t>맛있는 젤리 형태 — 알약이 아닌 달콤한 구미 타입이라 섭취 부담이 없음
+빠르고 깊은 수면 유도 — 취침 전 복용 시 잠에 금방 들고 푹 자는 데 효과적임</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>여성 이너뷰티 종합 케어 — 질유산균 성분으로 아침 공복에 챙겨 먹으며 장과 여성 건강을 한 번에 케어할 수 있습니다.
-간편한 1일 1캡슐 복용 — 하루 한 알만 챙기면 되는 직관적이고 편한 용법을 가집니다.
-풍성한 기획 세트 구성 — 증정품이 포함된 알찬 세트 구성으로 혜택이 좋습니다.</t>
+          <t>하루 한 알 간편 케어 — 아침 공복에 1캡슐로 여성 건강과 장 건강을 관리함
+넉넉한 더블 기획 구성 — 2개월 분량의 알찬 구성으로 넉넉하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>장 건강 및 면역력 강화 — 꾸준한 섭취를 통해 장내 유익균을 늘리고 면역력을 튼튼하게 유지해 줍니다.
-풍성한 1+1 기획 혜택 — 1+1 구성과 사은품 증정으로 가격 대비 높은 만족감을 제공합니다.</t>
+          <t>장 건강 및 면역 케어 — 꾸준히 먹으면 장이 편안해지고 면역 유지에 도움을 줌
+혜자스러운 1+1 기획 — 1+1 더블 구성과 증정품을 함께 얻을 수 있어 가성비 높음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 이중 케어 — 장 유산균 케어와 체지방 관리를 동시에 해결해 주는 합리적인 제품입니다.
-맛있는 요거트 풍미 — 거부감 없는 상큼한 요거트 맛으로 매일 맛있게 섭취할 수 있습니다.
-속 더부룩함 완화 — 섭취 후 배에 가스가 차거나 더부룩한 증상이 줄어들고 속이 편안해집니다.</t>
+          <t>장과 체지방 동시 관리 — 체지방 감소와 장 건강을 함께 챙기는 이중 기능성 제품임
+상큼한 요거트 맛 — 상큼한 요거트 맛이라 하루 한 포씩 맛있게 챙겨 먹기 좋음
+속 편한 뱃살 케어 — 복용 시 아랫배가 가벼워지고 더부룩한 속이 한결 편안해짐</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>배 아픔 없는 원활한 배변 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 갈 수 있도록 돕습니다.
-피부와 장의 복합 관리 — 장 건강뿐만 아니라 피부 면역력 유지에도 도움을 주어 이너뷰티를 챙길 수 있습니다.</t>
+          <t>속 편한 배변 활동 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 가도록 도움
+장과 피부 면역 동시 보충 — 100억 유산균으로 장 건강과 피부 면역 관리를 동시에 진행함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>체지방 감소 및 붓기 관리 — 디톡스 및 체지방 관리에 유용하며 과식 후 뱃살과 붓기를 정돈하는 데 도움을 줍니다.
-꾸준한 일상 다이어트 케어 — 무리하게 굶지 않고 일상에서 간편하게 보조제로 체중을 관리할 수 있습니다.</t>
+          <t>확실한 디톡스 및 붓기 제거 — 과식 후 디톡스나 급진급빠 시 뱃살이 들어가고 라인이 정돈됨
+원활한 속 비움 효과 — 섭취 시 화장실을 잘 가게 되고 묵직했던 속이 개운해짐</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>비타민C와 D 올인원 조합 — 면역에 좋은 비타민C와 햇빛이 부족한 실내인을 위한 비타민D를 한 번에 섭취할 수 있습니다.
-귀여운 증정품 파우치 기획 — 콜라보 캐릭터 파우치 등이 증정되어 구매 만족도를 높여줍니다.</t>
+          <t>비타민 C와 D의 올인원 — 면역 관리를 돕는 비타민C와 결핍되기 쉬운 비타민D를 한 번에 복용함
+높은 신뢰도와 가성비 — 믿을 수 있는 대표 브랜드 제품으로 꾸준히 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>다채롭고 맛있는 과일 맛 — 애플민트, 백도, 타트체리 등 맛있는 과일 맛 구미 형태라 맛있게 챙겨 먹을 수 있습니다.
-자연스러운 수면 유도 — 취침 전 섭취하면 뒤척임이 줄어들고 편안하게 잠들 수 있게 도와줍니다.</t>
+          <t>빠른 숙면 유도 체감 — 뒤척임 없이 금방 잠들고 새벽에 깨지 않도록 수면의 질을 높임
+맛있는 식물성 구미 — 부담 없는 식물성 성분에 달콤한 젤리 맛이라 지속 복용하기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
@@ -7200,11 +7202,7 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>취침 전 재양치 필요성 — 젤리 제형 특성상 취침 전 섭취 후 양치를 다시 해야 하는 번거로움이 있습니다.</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
@@ -7212,7 +7210,7 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 정제의 크기가 다소 커서 삼킬 때 목넘김이 약간 불편할 수 있습니다.</t>
+          <t>다소 큰 알약 크기 — 정제 사이즈가 좀 더 커서 삼킬 때 다소 부담이 느껴짐</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -7360,7 +7358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7398,7 +7396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7408,10 +7406,10 @@
         <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -7420,20 +7418,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -7446,16 +7444,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -7464,7 +7462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7474,19 +7472,19 @@
         <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7499,60 +7497,60 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7574,7 +7572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7584,12 +7582,56 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -1170,14 +1170,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1242,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1292,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,232 +1425,232 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>편리한 섭취와 휴대성 — 액상과 정제 조합으로 먹기 쉽고 외출 시 휴대하기 용이함</t>
+          <t>고급스러운 제품 패키지 — 패키지가 고급스럽고 단정하여 선물용으로 전달하기에 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 선물 패키지 — 패키지가 고급스러워 지인이나 부모님 선물용으로 적합함</t>
+          <t>체감되는 피로 회복 효과 — 피로감이 줄어들고 컨디션 및 활력이 회복되는 느낌을 받음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 섭취 후 피로감이 줄어들고 컨디션 유지 및 활력 보충에 도움 됨</t>
+          <t>편리한 휴대와 올인원 섭취 — 가볍고 휴대성이 좋으며 액상과 정제를 한 번에 챙길 수 있음</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용이나 활용도가 떨어짐</t>
+          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용 활용도가 떨어짐</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2663,22 +2663,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 망고피치 맛 — 비타민 특유의 쓴맛이나 냄새가 없고 망고피치 맛으로 맛있게 섭취 가능함</t>
+          <t>거부감 없는 망고피치 맛 — 쓴맛이나 특유의 향이 없어 망고피치 맛 액상을 부담 없이 마실 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 올인원 제형 — 액상과 정제가 같이 들어 있어 물 없이도 장소 구분 없이 먹기 편함</t>
+          <t>목넘김 편한 작은 알약 — 알약 크기가 작아 물 없이 액상과 함께 편하게 삼킬 수 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>우수한 활력 보충 효과 — 피로할 때 먹으면 에너지가 충전되고 체력 보충에 도움 됨</t>
+          <t>신속한 체력 보충 효과 — 피로할 때 섭취 시 활력이 생기고 피로가 빠르게 회복됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>상대적으로 연한 맛과 효과 — 독일산 비타민 제품에 비해 섭취감이 다소 연하고 약하게 느껴짐</t>
+          <t>알약 크기의 체감 개인차 — 알약을 잘 넘기지 못하는 경우 다소 크게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2726,17 +2726,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 체감 — 몸이 피곤하거나 나른할 때 섭취하면 빠르게 기운이 나고 효과적임</t>
+          <t>고급스러운 패키지 디자인 — 상자 및 구성 패키지가 깔끔하고 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 기프트 패키지 — 상자 포장이 묵직하고 깔끔하며 고급스러워 선물용으로 아주 훌륭함</t>
+          <t>탁월한 피로 회복 체감 — 피곤하고 나른할 때 섭취 시 힘이 나고 컨디션이 올라감</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>편리한 휴대성 및 복용 — 개별 포장되어 갖고 다니기 편하고 피곤할 때 마시기 유용함</t>
+          <t>간편한 휴대 및 섭취법 — 휴대하기 편하고 피곤할 때마다 간편하게 마시기 좋음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 과일 맛 젤리 — 쓴맛 없이 달콤한 과일 맛 구미 형태라 간식처럼 즐겁게 먹기 좋음</t>
+          <t>물 없이 먹는 구미 제형 — 젤리 형태라 물 없이도 어디서나 간식처럼 쉽게 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>물 필요 없는 편리함 — 물 없이 씹어서 간편하게 복용할 수 있어 영양제 챙겨 먹기 편함</t>
+          <t>달콤상큼한 과일 풍미 — 비타민 특유의 냄새나 쓴맛 없이 달콤하고 식감이 쫀득함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>예쁜 선물용 패키지 — 포장 디자인이 예쁘고 알찬 구성이라 연령대 상관없이 선물하기 적합함</t>
+          <t>남녀노소 높은 만족도 — 어른과 아이 모두 부담 없이 즐길 수 있고 포장 디자인도 예쁨</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>적게 느껴지는 하루 권장량 — 맛에 비해 하루 섭취 권장량이 2개로 제한되어 아쉬움이 남음</t>
+          <t>아쉬운 하루 권장 섭취량 — 맛이 좋아 하루 2개라는 권장 섭취량이 아쉽게 느껴짐</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2848,17 +2848,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 섭취 후 피로가 풀어지고 기력 회복 효과가 직관적으로 체감됨</t>
+          <t>위생적인 1회 개별 포장 — 1회분씩 깔끔하게 개별 포장되어 있어 위생적이고 휴대가 용이함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>쉬운 알약 목넘김 — 정제 크기가 크지 않아 목넘김 부담 없이 액상과 함께 섭취 가능함</t>
+          <t>부담 없는 알약 목넘김 — 알약 크기가 크지 않아서 삼킬 때 목넘김이 나쁘지 않음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>위생적인 개별 포장 — 1회분씩 개별 포장되어 있어 위생적이고 들고 다니기 편함</t>
+          <t>신속한 피로 회복 체감 — 섭취 후 피로 회복 및 에너지 충전 효과를 신속하게 체감함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2903,23 +2903,19 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있고 쉬운 복용법 — 맛이 좋고 먹기 편해 데일리로 지속해서 챙겨 먹기 좋음</t>
+          <t>맛있고 간편한 liquid 제형 — 맛이 우수하고 가방에 휴대하여 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 휴대성 — 가방에 넣고 다니기 좋은 사이즈로 외출 시에도 챙기기 용이함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>체력 보충 및 피로 해소 — 몸이 피곤하고 체력이 떨어질 때 먹으면 컨디션 관리에 도움 됨</t>
-        </is>
-      </c>
+          <t>확실한 피로 개선 체감 — 피로감이 풀리고 몸의 컨디션이 한결 편안해짐</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2966,18 +2962,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>강력한 컨디션 회복 — 체력이 바닥났을 때 먹으면 피로감이 줄고 활력이 돋아남</t>
+          <t>상큼한 진한 오렌지 맛 — 진하고 상큼한 오렌지 맛 액상이라 거부감 없이 마시기 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>진하고 상큼한 오렌지맛 — 진한 오렌지 맛 액상과 정제 조합으로 거부감 없이 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>확실한 체력 증진 효과 — 체력이 떨어졌을 때 피로감을 낮추고 컨디션을 올려줌</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>우수한 가방 속 휴대성 — 컴팩트한 크기로 가방에 넣어 다니며 챙겨 먹기 편함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>부담스러운 가격대 — 제품의 가격이 다소 비싸 직접 상시 구매하기에는 부담이 큼</t>
+          <t>직접 구매 시 가격 부담 — 제품의 성능은 우수하나 가격대가 높게 느껴짐</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>신선하고 재미있는 제형 — 버튼을 눌러 분말을 액상에 섞어 마시는 방식으로 섭취 재미가 있음</t>
+          <t>직접 섞어 마시는 재미 — 버튼을 눌러 분말을 액상에 섞는 방식이라 섭취하는 재미가 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 음료 맛 — 쓰지 않고 음료수처럼 상큼하고 맛있어 부담 없이 복용 가능함</t>
+          <t>고급스러운 포장 케이스 — 패키지가 고급스럽고 디자인이 알차서 선물하기에 적합함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지와 케이스가 예쁘고 알차서 받는 사람의 만족도가 높음</t>
+          <t>상큼하고 맛있는 음료 맛 — 쓴맛 없이 음료처럼 상큼하고 맛있어서 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3084,17 +3084,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛 — 쓴맛이나 비린 맛 없이 상큼한 레몬향으로 호불호 없이 섭취 가능함</t>
+          <t>상큼한 레몬향 풍미 — 비타민 특유의 쓴맛 없이 레몬향이 나 부담 없이 섭취함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>올인원 일체형 제형 — 한 병에 액상과 정제가 같이 들어 있어 별도의 물 없이 간편하게 먹음</t>
+          <t>올인원 샷 형태의 편의성 — 액상과 알약이 함께 들어 있어 물 없이 한번에 보충 가능함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증진 — 바쁜 일상이나 피곤할 때 먹으면 덜 지치고 컨디션 유지에 도움 됨</t>
+          <t>개별 포장으로 편리한 휴대 — 하나씩 개별 포장되어 가방에 넣고 다니며 챙겨 먹기 유용함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 제공 — 남성용과 여성용이 세분화되어 있어 맞춤형 영양 케어가 가능함</t>
+          <t>성별 맞춤 옵션 제공 — 남성용과 여성용 옵션 선택이 가능하여 영양 관리에 유용함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>피로감 감소 효과 — 하루 하나씩 섭취 시 피로함이 덜 느껴지고 활력 증진에 도움 됨</t>
+          <t>보관이 쉬운 분리 구성 — 소박스로 나뉘어 포장되어 있어 보관 및 개별 관리가 편리함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 패키지 구성과 박스 포장이 고급스러워 직장 동료 선물로 적합함</t>
+          <t>체감되는 피로 완화 — 피로감이 줄어들고 일상 활력을 케어하는 효과가 느껴짐</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3249,22 +3249,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>우수한 가성비 구성 — 저렴한 가격대에 알찬 수량으로 구성되어 경제적임</t>
+          <t>뛰어난 구성과 가성비 — 부담 없는 가격에 수량이 넉넉하고 다양한 구성으로 만족도가 높음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>질리지 않는 촉촉함 — 퍽퍽함이 적고 자극적이지 않은 맛과 다양한 메뉴로 질리지 않음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>간편한 조리법 — 전자레인지 조리로 간편하게 데워 먹을 수 있어 식단 관리에 용이함</t>
-        </is>
-      </c>
+          <t>부드럽고 촉촉한 식감 — 뻑뻑함이 적고 양념이 과하지 않아 매일 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 배송 시 제품이 배송 과정에서 모두 녹아 도착하는 문제가 발생함</t>
+          <t>배송 시 해동 발생 문제 — 배송 도중 제품이 해동되어 도착하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3308,21 +3304,21 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>럭셔리한 플리츠백 포장 — 가방 형태의 포장이 매우 예쁘고 활용성이 높아 선물용으로 최고임</t>
+          <t>활용성 높은 럭셔리 포장 — 가방으로 활용할 수 있는 플리츠백 포장이 매우 고급스러움</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>콜라겐과 비오틴 복합 — 콜라겐과 비오틴을 따로 먹을 필요 없이 한 병으로 해결 가능함</t>
+          <t>콜라겐과 비오틴 동시 보충 — 콜라겐과 비오틴을 따로 챙기지 않고 한 번에 섭취 가능함</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>상큼한 오렌지맛 액상 — 오렌지 맛 액상 형태라 거부감 없이 편하게 마실 수 있음</t>
+          <t>부담 없는 오렌지 맛 — 상큼한 오렌지 맛 액상 타입이라 목넘김이 편하고 맛있음</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3371,22 +3367,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 전자레인지 조리 후에도 육즙이 남아 있어 퍽퍽하지 않고 촉촉함</t>
+          <t>촉촉하고 부드러운 육질 — 전자레인지 조리 후에도 퍽퍽하지 않고 촉촉함이 남아있음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다양한 종류와 구성 — 닭가슴살, 소세지, 큐브 등 구성이 다채로워 식단 시 질리지 않음</t>
+          <t>질리지 않는 다양한 맛 — 여러 맛과 형태가 섞여 있어 지속적인 식단 관리에 유용함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>유용한 보냉백 증정 — 도시락을 싸 다니기 좋은 보냉 파우치가 함께 증정되어 편리함</t>
+          <t>유용한 증정 보냉백 — 증정품인 보냉백이 귀엽고 도시락을 휴대할 때 쓰기 좋음</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>증정품 디자인 불일치 — 방송에서 안내된 디자인과 다른 보냉백이 배송되어 아쉬움</t>
+          <t>예고와 다른 사은품 배송 — 방송 안내와 다른 디자인의 보냉백이 배송되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3434,17 +3430,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>비린 맛없는 달콤한 맛 — 단백질 음료 특유의 텁텁함 없이 진한 초코우유처럼 맛이 좋음</t>
+          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린내나 텁텁함 없이 음료수처럼 맛있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 성분 — 제로 슈가 및 락토프리 제품으로 빈속에 마셔도 속이 편안함</t>
+          <t>속 편한 락토프리 제로슈가 — 제로슈가 및 락토프리 제품으로 공복 복용 시에도 속이 편안함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>운동 후 단백질 충전 — 운동 직후 단백질을 빠르게 보충하기에 적합하고 간편함</t>
+          <t>운동 후 간편한 단백 보충 — 낮은 칼로리로 운동 후 간편하게 단백질을 챙기기 적합함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3493,17 +3489,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고소한 군고구마 풍미 — 효소 특유의 냄새 없이 군고구마 향이 나 맛있게 먹을 수 있음</t>
+          <t>풍성하고 알찬 사은품 — 다양한 추가 사은품이 포함되어 구성 만족도가 높음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>푸짐한 추가 사은품 — 견과류바와 다양한 효소가 사은품으로 푸짐하게 제공됨</t>
+          <t>고소한 군고구마 풍미 — 효소 특유의 냄새 대신 군고구마 향이 나 고소하고 맛있음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 섭취 후 더부룩함이 줄어들고 배변 활동을 원활하게 도와줌</t>
+          <t>편안한 소화와 배변 개선 — 속 더부룩함이 줄어들고 화장실 이용이 원활해짐</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3548,21 +3544,21 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>무색·무취·무맛의 편안함 — 특별한 맛이나 향이 없어 입에 털어먹거나 물에 타기 수월함</t>
+          <t>부담 없는 무색무취무맛 — 맛과 냄새가 없어 물에 타거나 입에 털어 넣기 편리함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>고운 입자와 빠른 용해 — 입자가 고와서 물에 잘 녹고 흡수가 빠르게 느껴짐</t>
+          <t>고운 입자의 뛰어난 용해성 — 입자가 고와서 물에 잘 녹고 신속하게 복용할 수 있음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>운동 퍼포먼스 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 큰 도움을 줌</t>
+          <t>운동 수행 능력 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 실질적 도움이 됨</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3611,17 +3607,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>고함량 아르기닌 성분 — 1포당 6,200mg의 고함량 아르기닌이 들어 있어 효과적임</t>
+          <t>높은 아르기닌 함유량 — 1포당 6,200mg의 고함량 아르기닌을 제공하여 활력 보충에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>상큼한 베리 맛스틱 — 상큼한 맛으로 그냥 짜 먹거나 물에 타 마시기 편리함</t>
+          <t>새콤상큼한 베리 맛 — 맛이 상큼하고 달콤하여 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>확실한 활력 개선 체감 — 피로감이 줄어들고 하루를 활기차게 보내는 데 도옴이 됨</t>
+          <t>편리한 스틱형 섭취 — 바로 짜 먹거나 물에 타 마실 수 있는 스틱 형태라 편리함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3670,17 +3666,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>맛있는 레몬 맛 액상 — 역하지 않고 상큼한 레몬 맛이라 영양제를 잘 못 먹는 사람도 쉬움</t>
+          <t>역하지 않은 레몬 맛 — 상큼한 레몬 맛 액상이라 역함 없이 맛있게 마실 수 있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 스틱 포장 — 스틱 형태라 외출 시 챙겨 다니기 쉽고 복용이 편리함</t>
+          <t>액상 스틱의 높은 휴대성 — 물에 잘 녹는 액상 스틱이라 외출 시 챙기기 용이함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>피로 회복 지원 — 복용 시 피로 해소에 도움을 주고 운동할 때 힘이 나는 느낌을 줌</t>
+          <t>체감되는 피로 회복 — 아침 공복 및 운동 전 섭취 시 몸이 가벼워지고 피로가 줄어듦</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3729,7 +3725,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>우수한 숙취 해소 — 섭취 시 숙취 해소 효과가 매우 뛰어나 만족스러움</t>
+          <t>탁월한 숙취 해소 효과 — 섭취 후 숙취를 해소하는 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -4071,7 +4067,7 @@
         <v>8687</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>773</v>
@@ -4094,71 +4090,71 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>편리한 섭취와 휴대성 — 액상과 정제 조합으로 먹기 쉽고 외출 시 휴대하기 용이함
-고급스러운 선물 패키지 — 패키지가 고급스러워 지인이나 부모님 선물용으로 적합함
-피로 회복 및 활력 증진 — 섭취 후 피로감이 줄어들고 컨디션 유지 및 활력 보충에 도움 됨</t>
+          <t>고급스러운 제품 패키지 — 패키지가 고급스럽고 단정하여 선물용으로 전달하기에 적합함
+체감되는 피로 회복 효과 — 피로감이 줄어들고 컨디션 및 활력이 회복되는 느낌을 받음
+편리한 휴대와 올인원 섭취 — 가볍고 휴대성이 좋으며 액상과 정제를 한 번에 챙길 수 있음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 망고피치 맛 — 비타민 특유의 쓴맛이나 냄새가 없고 망고피치 맛으로 맛있게 섭취 가능함
-간편한 올인원 제형 — 액상과 정제가 같이 들어 있어 물 없이도 장소 구분 없이 먹기 편함
-우수한 활력 보충 효과 — 피로할 때 먹으면 에너지가 충전되고 체력 보충에 도움 됨</t>
+          <t>거부감 없는 망고피치 맛 — 쓴맛이나 특유의 향이 없어 망고피치 맛 액상을 부담 없이 마실 수 있음
+목넘김 편한 작은 알약 — 알약 크기가 작아 물 없이 액상과 함께 편하게 삼킬 수 있음
+신속한 체력 보충 효과 — 피로할 때 섭취 시 활력이 생기고 피로가 빠르게 회복됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 체감 — 몸이 피곤하거나 나른할 때 섭취하면 빠르게 기운이 나고 효과적임
-고급스러운 기프트 패키지 — 상자 포장이 묵직하고 깔끔하며 고급스러워 선물용으로 아주 훌륭함
-편리한 휴대성 및 복용 — 개별 포장되어 갖고 다니기 편하고 피곤할 때 마시기 유용함</t>
+          <t>고급스러운 패키지 디자인 — 상자 및 구성 패키지가 깔끔하고 고급스러워 선물용으로 제격임
+탁월한 피로 회복 체감 — 피곤하고 나른할 때 섭취 시 힘이 나고 컨디션이 올라감
+간편한 휴대 및 섭취법 — 휴대하기 편하고 피곤할 때마다 간편하게 마시기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 과일 맛 젤리 — 쓴맛 없이 달콤한 과일 맛 구미 형태라 간식처럼 즐겁게 먹기 좋음
-물 필요 없는 편리함 — 물 없이 씹어서 간편하게 복용할 수 있어 영양제 챙겨 먹기 편함
-예쁜 선물용 패키지 — 포장 디자인이 예쁘고 알찬 구성이라 연령대 상관없이 선물하기 적합함</t>
+          <t>물 없이 먹는 구미 제형 — 젤리 형태라 물 없이도 어디서나 간식처럼 쉽게 섭취 가능함
+달콤상큼한 과일 풍미 — 비타민 특유의 냄새나 쓴맛 없이 달콤하고 식감이 쫀득함
+남녀노소 높은 만족도 — 어른과 아이 모두 부담 없이 즐길 수 있고 포장 디자인도 예쁨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 섭취 후 피로가 풀어지고 기력 회복 효과가 직관적으로 체감됨
-쉬운 알약 목넘김 — 정제 크기가 크지 않아 목넘김 부담 없이 액상과 함께 섭취 가능함
-위생적인 개별 포장 — 1회분씩 개별 포장되어 있어 위생적이고 들고 다니기 편함</t>
+          <t>위생적인 1회 개별 포장 — 1회분씩 깔끔하게 개별 포장되어 있어 위생적이고 휴대가 용이함
+부담 없는 알약 목넘김 — 알약 크기가 크지 않아서 삼킬 때 목넘김이 나쁘지 않음
+신속한 피로 회복 체감 — 섭취 후 피로 회복 및 에너지 충전 효과를 신속하게 체감함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 쉬운 복용법 — 맛이 좋고 먹기 편해 데일리로 지속해서 챙겨 먹기 좋음
-간편한 휴대성 — 가방에 넣고 다니기 좋은 사이즈로 외출 시에도 챙기기 용이함
-체력 보충 및 피로 해소 — 몸이 피곤하고 체력이 떨어질 때 먹으면 컨디션 관리에 도움 됨</t>
+          <t>맛있고 간편한 liquid 제형 — 맛이 우수하고 가방에 휴대하여 편하게 마실 수 있음
+확실한 피로 개선 체감 — 피로감이 풀리고 몸의 컨디션이 한결 편안해짐</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>강력한 컨디션 회복 — 체력이 바닥났을 때 먹으면 피로감이 줄고 활력이 돋아남
-진하고 상큼한 오렌지맛 — 진한 오렌지 맛 액상과 정제 조합으로 거부감 없이 맛있게 먹기 좋음</t>
+          <t>상큼한 진한 오렌지 맛 — 진하고 상큼한 오렌지 맛 액상이라 거부감 없이 마시기 좋음
+확실한 체력 증진 효과 — 체력이 떨어졌을 때 피로감을 낮추고 컨디션을 올려줌
+우수한 가방 속 휴대성 — 컴팩트한 크기로 가방에 넣어 다니며 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>신선하고 재미있는 제형 — 버튼을 눌러 분말을 액상에 섞어 마시는 방식으로 섭취 재미가 있음
-상큼하고 맛있는 음료 맛 — 쓰지 않고 음료수처럼 상큼하고 맛있어 부담 없이 복용 가능함
-고급스러운 포장 디자인 — 패키지와 케이스가 예쁘고 알차서 받는 사람의 만족도가 높음</t>
+          <t>직접 섞어 마시는 재미 — 버튼을 눌러 분말을 액상에 섞는 방식이라 섭취하는 재미가 있음
+고급스러운 포장 케이스 — 패키지가 고급스럽고 디자인이 알차서 선물하기에 적합함
+상큼하고 맛있는 음료 맛 — 쓴맛 없이 음료처럼 상큼하고 맛있어서 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛 — 쓴맛이나 비린 맛 없이 상큼한 레몬향으로 호불호 없이 섭취 가능함
-올인원 일체형 제형 — 한 병에 액상과 정제가 같이 들어 있어 별도의 물 없이 간편하게 먹음
-피로 해소 및 활력 증진 — 바쁜 일상이나 피곤할 때 먹으면 덜 지치고 컨디션 유지에 도움 됨</t>
+          <t>상큼한 레몬향 풍미 — 비타민 특유의 쓴맛 없이 레몬향이 나 부담 없이 섭취함
+올인원 샷 형태의 편의성 — 액상과 알약이 함께 들어 있어 물 없이 한번에 보충 가능함
+개별 포장으로 편리한 휴대 — 하나씩 개별 포장되어 가방에 넣고 다니며 챙겨 먹기 유용함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 제공 — 남성용과 여성용이 세분화되어 있어 맞춤형 영양 케어가 가능함
-피로감 감소 효과 — 하루 하나씩 섭취 시 피로함이 덜 느껴지고 활력 증진에 도움 됨
-고급스러운 선물용 포장 — 패키지 구성과 박스 포장이 고급스러워 직장 동료 선물로 적합함</t>
+          <t>성별 맞춤 옵션 제공 — 남성용과 여성용 옵션 선택이 가능하여 영양 관리에 유용함
+보관이 쉬운 분리 구성 — 소박스로 나뉘어 포장되어 있어 보관 및 개별 관리가 편리함
+체감되는 피로 완화 — 피로감이 줄어들고 일상 활력을 케어하는 효과가 느껴짐</t>
         </is>
       </c>
     </row>
@@ -4170,25 +4166,25 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용이나 활용도가 떨어짐</t>
+          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용 활용도가 떨어짐</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>상대적으로 연한 맛과 효과 — 독일산 비타민 제품에 비해 섭취감이 다소 연하고 약하게 느껴짐</t>
+          <t>알약 크기의 체감 개인차 — 알약을 잘 넘기지 못하는 경우 다소 크게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>적게 느껴지는 하루 권장량 — 맛에 비해 하루 섭취 권장량이 2개로 제한되어 아쉬움이 남음</t>
+          <t>아쉬운 하루 권장 섭취량 — 맛이 좋아 하루 2개라는 권장 섭취량이 아쉽게 느껴짐</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격대 — 제품의 가격이 다소 비싸 직접 상시 구매하기에는 부담이 큼</t>
+          <t>직접 구매 시 가격 부담 — 제품의 성능은 우수하나 가격대가 높게 느껴짐</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -4604,7 +4600,7 @@
         <v>49</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>142</v>
@@ -4616,7 +4612,7 @@
         <v>1653</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>247</v>
@@ -4637,63 +4633,62 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 구성 — 저렴한 가격대에 알찬 수량으로 구성되어 경제적임
-질리지 않는 촉촉함 — 퍽퍽함이 적고 자극적이지 않은 맛과 다양한 메뉴로 질리지 않음
-간편한 조리법 — 전자레인지 조리로 간편하게 데워 먹을 수 있어 식단 관리에 용이함</t>
+          <t>뛰어난 구성과 가성비 — 부담 없는 가격에 수량이 넉넉하고 다양한 구성으로 만족도가 높음
+부드럽고 촉촉한 식감 — 뻑뻑함이 적고 양념이 과하지 않아 매일 먹기 좋음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>럭셔리한 플리츠백 포장 — 가방 형태의 포장이 매우 예쁘고 활용성이 높아 선물용으로 최고임
-콜라겐과 비오틴 복합 — 콜라겐과 비오틴을 따로 먹을 필요 없이 한 병으로 해결 가능함
-상큼한 오렌지맛 액상 — 오렌지 맛 액상 형태라 거부감 없이 편하게 마실 수 있음</t>
+          <t>활용성 높은 럭셔리 포장 — 가방으로 활용할 수 있는 플리츠백 포장이 매우 고급스러움
+콜라겐과 비오틴 동시 보충 — 콜라겐과 비오틴을 따로 챙기지 않고 한 번에 섭취 가능함
+부담 없는 오렌지 맛 — 상큼한 오렌지 맛 액상 타입이라 목넘김이 편하고 맛있음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 전자레인지 조리 후에도 육즙이 남아 있어 퍽퍽하지 않고 촉촉함
-다양한 종류와 구성 — 닭가슴살, 소세지, 큐브 등 구성이 다채로워 식단 시 질리지 않음
-유용한 보냉백 증정 — 도시락을 싸 다니기 좋은 보냉 파우치가 함께 증정되어 편리함</t>
+          <t>촉촉하고 부드러운 육질 — 전자레인지 조리 후에도 퍽퍽하지 않고 촉촉함이 남아있음
+질리지 않는 다양한 맛 — 여러 맛과 형태가 섞여 있어 지속적인 식단 관리에 유용함
+유용한 증정 보냉백 — 증정품인 보냉백이 귀엽고 도시락을 휴대할 때 쓰기 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛없는 달콤한 맛 — 단백질 음료 특유의 텁텁함 없이 진한 초코우유처럼 맛이 좋음
-속 편한 락토프리 성분 — 제로 슈가 및 락토프리 제품으로 빈속에 마셔도 속이 편안함
-운동 후 단백질 충전 — 운동 직후 단백질을 빠르게 보충하기에 적합하고 간편함</t>
+          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린내나 텁텁함 없이 음료수처럼 맛있음
+속 편한 락토프리 제로슈가 — 제로슈가 및 락토프리 제품으로 공복 복용 시에도 속이 편안함
+운동 후 간편한 단백 보충 — 낮은 칼로리로 운동 후 간편하게 단백질을 챙기기 적합함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고소한 군고구마 풍미 — 효소 특유의 냄새 없이 군고구마 향이 나 맛있게 먹을 수 있음
-푸짐한 추가 사은품 — 견과류바와 다양한 효소가 사은품으로 푸짐하게 제공됨
-속 편한 소화 개선 — 섭취 후 더부룩함이 줄어들고 배변 활동을 원활하게 도와줌</t>
+          <t>풍성하고 알찬 사은품 — 다양한 추가 사은품이 포함되어 구성 만족도가 높음
+고소한 군고구마 풍미 — 효소 특유의 냄새 대신 군고구마 향이 나 고소하고 맛있음
+편안한 소화와 배변 개선 — 속 더부룩함이 줄어들고 화장실 이용이 원활해짐</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>무색·무취·무맛의 편안함 — 특별한 맛이나 향이 없어 입에 털어먹거나 물에 타기 수월함
-고운 입자와 빠른 용해 — 입자가 고와서 물에 잘 녹고 흡수가 빠르게 느껴짐
-운동 퍼포먼스 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 큰 도움을 줌</t>
+          <t>부담 없는 무색무취무맛 — 맛과 냄새가 없어 물에 타거나 입에 털어 넣기 편리함
+고운 입자의 뛰어난 용해성 — 입자가 고와서 물에 잘 녹고 신속하게 복용할 수 있음
+운동 수행 능력 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 실질적 도움이 됨</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>고함량 아르기닌 성분 — 1포당 6,200mg의 고함량 아르기닌이 들어 있어 효과적임
-상큼한 베리 맛스틱 — 상큼한 맛으로 그냥 짜 먹거나 물에 타 마시기 편리함
-확실한 활력 개선 체감 — 피로감이 줄어들고 하루를 활기차게 보내는 데 도옴이 됨</t>
+          <t>높은 아르기닌 함유량 — 1포당 6,200mg의 고함량 아르기닌을 제공하여 활력 보충에 도움 됨
+새콤상큼한 베리 맛 — 맛이 상큼하고 달콤하여 거부감 없이 섭취 가능함
+편리한 스틱형 섭취 — 바로 짜 먹거나 물에 타 마실 수 있는 스틱 형태라 편리함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 레몬 맛 액상 — 역하지 않고 상큼한 레몬 맛이라 영양제를 잘 못 먹는 사람도 쉬움
-간편한 스틱 포장 — 스틱 형태라 외출 시 챙겨 다니기 쉽고 복용이 편리함
-피로 회복 지원 — 복용 시 피로 해소에 도움을 주고 운동할 때 힘이 나는 느낌을 줌</t>
+          <t>역하지 않은 레몬 맛 — 상큼한 레몬 맛 액상이라 역함 없이 맛있게 마실 수 있음
+액상 스틱의 높은 휴대성 — 물에 잘 녹는 액상 스틱이라 외출 시 챙기기 용이함
+체감되는 피로 회복 — 아침 공복 및 운동 전 섭취 시 몸이 가벼워지고 피로가 줄어듦</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>우수한 숙취 해소 — 섭취 시 숙취 해소 효과가 매우 뛰어나 만족스러움</t>
+          <t>탁월한 숙취 해소 효과 — 섭취 후 숙취를 해소하는 효과가 뛰어남</t>
         </is>
       </c>
     </row>
@@ -4706,13 +4701,13 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 배송 시 제품이 배송 과정에서 모두 녹아 도착하는 문제가 발생함</t>
+          <t>배송 시 해동 발생 문제 — 배송 도중 제품이 해동되어 도착하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>증정품 디자인 불일치 — 방송에서 안내된 디자인과 다른 보냉백이 배송되어 아쉬움</t>
+          <t>예고와 다른 사은품 배송 — 방송 안내와 다른 디자인의 보냉백이 배송되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -4965,7 +4960,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4973,62 +4968,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3324</v>
+        <v>676</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>최고의 가성비 — 5,000원이라는 저렴한 가격으로 한 달 치 비타민을 챙길 수 있음</t>
+          <t>운동 시 에너지를 제공 — 러닝이나 운동 전에 먹으면 지치지 않고 힘이 유지됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>알찬 영양 성분 배합 — 한국인 맞춤형으로 비타민 12종과 미네랄 7종이 포함됨</t>
+          <t>맛과 휴대성의 유용함 — 맛이 좋고 가볍게 챙겨 먹기 좋은 스틱 형태로 구성됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>상대적으로 낮은 함량 — 저렴한 가격 특성상 약국 제품에 비해 영양 성분 함량이 적을 수 있음</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>살짝 큰 알약 크기 — 사람에 따라 정제 알약의 크기가 약간 크게 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5036,48 +5023,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581091&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260601/30NEHOm4dIOnmUVwUKLJ591581091_00_0030NEHOm4dIOnmUVwUKLJ.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>5851</v>
+        <v>459</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>수면 및 근육 완화 체감 — 눈 떨림 및 다리 쥐 증상이 개선되고 숙면을 취하는 데 큰 도움 됨</t>
+          <t>뛰어난 가격 대비 성능 — 약국 대비 부담 없는 가격으로 고함량 비타민B를 구매 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 3,000원에 마그네슘 권장량을 채울 수 있어 가성비가 훌륭함</t>
+          <t>피로 개선 및 구내염 완화 — 복용 후 피로감이 줄고 혓바늘이 줄어드는 효과를 봄</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>속 편한 섭취감 — 복용 시 속 쓰림 없이 편안하게 지속해서 챙겨 먹기 좋음</t>
+          <t>편리한 휴대 및 복용 — 포장이 간편하여 상시 휴대하며 복용하기 좋음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -5087,7 +5074,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5095,7 +5082,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5105,39 +5092,39 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>4461</v>
+        <v>6141</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>작은 정제와 편한 목넘김 — 알약 크기가 작아서 물과 함께 삼키기가 매우 수월함</t>
+          <t>검증된 제약사의 가성비 — 유명 브랜드 제품을 저렴하게 구매할 수 있어 만족도가 높음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>식전 혈당 관리 용이 — 식전 복용으로 간단하게 혈당 스파이크 관리에 도움을 줌</t>
+          <t>혈압 및 활력 케어 효과 — 100mg의 코큐텐 함량으로 혈압 조절과 활력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>미흡한 체감 효과 — 개인차에 따라 식후 졸음이나 혈당 조절 측면의 직접 체감이 부족함</t>
+          <t>야간 복용 시 수면 영향 — 저녁 식후 복용할 경우 활력 증가로 수면에 방해가 될 수 있음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -5146,7 +5133,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5154,12 +5141,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5169,43 +5156,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>6137</v>
+        <v>6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>고함량 대비 뛰어난 가성비 — 하루 권장량 100mg을 저렴한 가격으로 챙길 수 있어 만족스러움</t>
+          <t>고급스러운 외관 디자인 — 패키지 케이스가 은은하게 반짝여 선물용으로도 손색없음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>활력 및 피로 개선 — 꾸준한 복용 시 몸이 가벼워지고 일상 활력 증진에 도옴을 줌</t>
+          <t>합리적이고 착한 가격 — 품질 대비 가격이 저렴하여 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>저녁 복용 시 수면 영향 — 저녁 식후에 복용할 경우 사람에 따라 잠들기 어려울 수 있음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5213,7 +5196,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5223,44 +5206,52 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3422</v>
+        <v>3797</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>동일 성분 대비 갓성비 — 유명 브랜드 제품과 동일한 함량을 5,000원에 구매 가능함</t>
+          <t>삼키기 쉬운 작은 캡슐 — 캡슐 크기가 작고 부드러워 목넘김이 용이함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>체지방 관리 및 부담 해소 — 기름진 음식이나 탄수화물 섭취 후 부담을 줄여주는 데 유용함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>눈의 피로 및 건조함 완화 — 컴퓨터나 스마트폰 사용 후 느껴지는 눈의 뻑뻑함과 피로가 줄어듦</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>부담 없는 가성비 한 달 분량 — 루테인 권장량을 3천원대의 저렴한 가격으로 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>단일 루테인 위주의 성분 — 지아잔틴이나 아스타잔틴 성분은 별도로 함유되어 있지 않음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5268,12 +5259,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5283,36 +5274,40 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3273</v>
+        <v>1168</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>칼마디 황금 비율 조합 — 칼슘과 마그네슘의 2:1 비율 및 비타민D 복합 구성으로 흡수에 좋음</t>
+          <t>신속한 전해질 및 수분 충전 — 땀을 많이 흘린 후 음용 시 수분과 전해질이 빠르게 보충됨</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3종 결합 가성비 — 뼈 건강 필수 영양소 3가지를 5천원에 한 번에 먹을 수 있음</t>
+          <t>은은한 자몽 향의 편의성 — 자몽 향이 은은하게 퍼져 맹물보다 편하게 물을 많이 마실 수 있음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>간편한 뼈 관절 관리 — 여러 개를 따로 챙길 필요 없이 한 알로 해결되어 용이함</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>붓기 완화 및 대사 도움 — 칼륨과 식이섬유 배합으로 얼굴 붓기 제거 및 순환에 유용함</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>시중 이온음료 대비 옅은 맛 — 기존 포카리스웨트 등 음료에 비해 맛이 다소 밍밍하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5327,53 +5322,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2396</v>
+        <v>4467</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>우수한 배변 활동 지원 — 마신 후 화장실을 잘 가게 되어 속이 가벼워지고 편안해짐</t>
+          <t>작은 크기로 편한 목넘김 — 알약 크기가 작아서 복용할 때 삼키기 편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>커피 대용으로 적합 — 찬물에 잘 녹고 아메리카노와 유사하여 부담 없이 마시기 좋음</t>
+          <t>식전 복용 시 혈당 케어 — 식사 전 복용하면 식후 혈당 스파이크를 잡는 데 도움이 됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>편리한 스틱 포장 — 개별 스틱 포장이라 외출이나 회사에서 챙겨 마시기 편함</t>
+          <t>부담 없는 가성비 가격 — 저렴한 가격으로 식후 혈당 관리 영양제를 시도할 수 있음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>소용량 및 씁쓸한 맛 — 1포 용량이 적어 2포를 타야 진해지며 사람에 따라 다소 씁쓸함</t>
+          <t>체감 효과의 개인차 — 개인에 따라 식후 졸음 개선이나 효과를 즉각 체감하기 어려움</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5382,7 +5377,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5390,12 +5385,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5405,43 +5400,47 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>1060</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고급스러운 기프트 포장 — 패키지가 고급스러워 명절이나 부모님 선물용으로 추천할 만함</t>
+          <t>올리브오일과 레몬의 조합 — 오일 캡슐과 레몬즙을 개별 포장하여 공복에 한 번에 먹기 편함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 쓴맛 — 홍삼 특유의 강한 쓴맛이 적어 부담 없이 먹을 수 있음</t>
+          <t>원활한 배변 및 속 편함 — 아침 공복 복용 시 장 건강과 배변 활동에 유용한 효과를 봄</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>휴대성 및 복용 편의 — 개별 환 포장으로 들고 다니기 좋고 복용이 간편함</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>휴대가 용이한 포장 용기 — 병 패키징이 야무지고 개별 포장되어 출근 시 챙겨가기 용이함</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>강한 신맛에 대한 호불호 — 동봉된 레몬즙의 신맛이 시큼하여 잘 못 먹는 경우 부담될 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5449,53 +5448,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>6059</v>
+        <v>2396</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>비린내 없는 깔끔함 — 섭취 후 생선 비린내가 오르지 않아 거부감 없이 복용 가능함</t>
+          <t>깔끔한 커피 대용 맛 — 씁쓸함이 적고 깔끔하여 부담 없이 아메리카노 대용으로 마시기 좋음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>안구 건조 개선 효과 — 꾸준히 복용 시 눈의 뻑뻑함과 건조함 완화에 도움이 됨</t>
+          <t>원활한 배변 활동 촉진 — 꾸준히 마시면 배변 활동이 원활해지고 몸이 가벼워지는 느낌을 받음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>rTG 오메가3 가성비 — rTG 형태 오메가3를 5,000원에 부담 없이 지속 구매 가능함</t>
+          <t>찬물에도 잘 녹는 편의성 — 스틱 타입이라 휴대가 편리하고 찬물에도 쉽게 잘 녹음</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 큰 알약 및 잦은 품절 — 캡슐 크기가 커 삼키기 어려울 수 있으며 품절이 자주 발생함</t>
+          <t>다소 옅은 커피 맛과 농도 — 1포 용량이 적어 진한 진도감을 원할 경우 2포 이상 타야 함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5512,12 +5511,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5527,33 +5526,33 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3564</v>
+        <v>1501</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>속 더부룩함 없는 복용감 — 타사 제품 대비 섭취 후 속 더부룩함이나 불편함이 적음</t>
+          <t>100% 유기농 레몬 원액 — 설탕이 들어가지 않은 순수 유기농 레몬이라 안심하고 복용함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>간 피로 개선 체감 — 꾸준히 복용 시 피로감이 줄어들고 컨디션 유지에 도움 됨</t>
+          <t>떫지 않은 상쾌한 풍미 — 떫은 맛없이 상큼하여 물이나 탄산수에 타 마시면 상쾌함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>비타민B 복합 가성비 — 밀크씨슬과 비타민B군을 저렴한 가격으로 한 번에 보충함</t>
+          <t>개별 포장의 가성비 — 1포씩 개별 포장되어 외출 시 휴대하기 편하고 가격도 저렴함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -5671,47 +5670,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5728,52 +5727,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
     </row>
@@ -5785,52 +5784,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 루테인 30정 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5849,7 @@
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5859,13 +5858,13 @@
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5878,34 +5877,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3324</v>
+        <v>676</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5851</v>
+        <v>459</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4461</v>
+        <v>6141</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6137</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3422</v>
+        <v>3797</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3273</v>
+        <v>1168</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>4467</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1060</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>2396</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>6059</v>
-      </c>
       <c r="L7" s="3" t="n">
-        <v>3564</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5916,105 +5915,109 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>최고의 가성비 — 5,000원이라는 저렴한 가격으로 한 달 치 비타민을 챙길 수 있음
-알찬 영양 성분 배합 — 한국인 맞춤형으로 비타민 12종과 미네랄 7종이 포함됨</t>
+          <t>운동 시 에너지를 제공 — 러닝이나 운동 전에 먹으면 지치지 않고 힘이 유지됨
+맛과 휴대성의 유용함 — 맛이 좋고 가볍게 챙겨 먹기 좋은 스틱 형태로 구성됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>수면 및 근육 완화 체감 — 눈 떨림 및 다리 쥐 증상이 개선되고 숙면을 취하는 데 큰 도움 됨
-부담 없는 저렴한 가격 — 3,000원에 마그네슘 권장량을 채울 수 있어 가성비가 훌륭함
-속 편한 섭취감 — 복용 시 속 쓰림 없이 편안하게 지속해서 챙겨 먹기 좋음</t>
+          <t>뛰어난 가격 대비 성능 — 약국 대비 부담 없는 가격으로 고함량 비타민B를 구매 가능함
+피로 개선 및 구내염 완화 — 복용 후 피로감이 줄고 혓바늘이 줄어드는 효과를 봄
+편리한 휴대 및 복용 — 포장이 간편하여 상시 휴대하며 복용하기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>작은 정제와 편한 목넘김 — 알약 크기가 작아서 물과 함께 삼키기가 매우 수월함
-식전 혈당 관리 용이 — 식전 복용으로 간단하게 혈당 스파이크 관리에 도움을 줌</t>
+          <t>검증된 제약사의 가성비 — 유명 브랜드 제품을 저렴하게 구매할 수 있어 만족도가 높음
+혈압 및 활력 케어 효과 — 100mg의 코큐텐 함량으로 혈압 조절과 활력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>고함량 대비 뛰어난 가성비 — 하루 권장량 100mg을 저렴한 가격으로 챙길 수 있어 만족스러움
-활력 및 피로 개선 — 꾸준한 복용 시 몸이 가벼워지고 일상 활력 증진에 도옴을 줌</t>
+          <t>고급스러운 외관 디자인 — 패키지 케이스가 은은하게 반짝여 선물용으로도 손색없음
+합리적이고 착한 가격 — 품질 대비 가격이 저렴하여 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>동일 성분 대비 갓성비 — 유명 브랜드 제품과 동일한 함량을 5,000원에 구매 가능함
-체지방 관리 및 부담 해소 — 기름진 음식이나 탄수화물 섭취 후 부담을 줄여주는 데 유용함</t>
+          <t>삼키기 쉬운 작은 캡슐 — 캡슐 크기가 작고 부드러워 목넘김이 용이함
+눈의 피로 및 건조함 완화 — 컴퓨터나 스마트폰 사용 후 느껴지는 눈의 뻑뻑함과 피로가 줄어듦
+부담 없는 가성비 한 달 분량 — 루테인 권장량을 3천원대의 저렴한 가격으로 챙길 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>칼마디 황금 비율 조합 — 칼슘과 마그네슘의 2:1 비율 및 비타민D 복합 구성으로 흡수에 좋음
-3종 결합 가성비 — 뼈 건강 필수 영양소 3가지를 5천원에 한 번에 먹을 수 있음
-간편한 뼈 관절 관리 — 여러 개를 따로 챙길 필요 없이 한 알로 해결되어 용이함</t>
+          <t>신속한 전해질 및 수분 충전 — 땀을 많이 흘린 후 음용 시 수분과 전해질이 빠르게 보충됨
+은은한 자몽 향의 편의성 — 자몽 향이 은은하게 퍼져 맹물보다 편하게 물을 많이 마실 수 있음
+붓기 완화 및 대사 도움 — 칼륨과 식이섬유 배합으로 얼굴 붓기 제거 및 순환에 유용함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>우수한 배변 활동 지원 — 마신 후 화장실을 잘 가게 되어 속이 가벼워지고 편안해짐
-커피 대용으로 적합 — 찬물에 잘 녹고 아메리카노와 유사하여 부담 없이 마시기 좋음
-편리한 스틱 포장 — 개별 스틱 포장이라 외출이나 회사에서 챙겨 마시기 편함</t>
+          <t>작은 크기로 편한 목넘김 — 알약 크기가 작아서 복용할 때 삼키기 편함
+식전 복용 시 혈당 케어 — 식사 전 복용하면 식후 혈당 스파이크를 잡는 데 도움이 됨
+부담 없는 가성비 가격 — 저렴한 가격으로 식후 혈당 관리 영양제를 시도할 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 기프트 포장 — 패키지가 고급스러워 명절이나 부모님 선물용으로 추천할 만함
-부담 없는 쓴맛 — 홍삼 특유의 강한 쓴맛이 적어 부담 없이 먹을 수 있음
-휴대성 및 복용 편의 — 개별 환 포장으로 들고 다니기 좋고 복용이 간편함</t>
+          <t>올리브오일과 레몬의 조합 — 오일 캡슐과 레몬즙을 개별 포장하여 공복에 한 번에 먹기 편함
+원활한 배변 및 속 편함 — 아침 공복 복용 시 장 건강과 배변 활동에 유용한 효과를 봄
+휴대가 용이한 포장 용기 — 병 패키징이 야무지고 개별 포장되어 출근 시 챙겨가기 용이함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>비린내 없는 깔끔함 — 섭취 후 생선 비린내가 오르지 않아 거부감 없이 복용 가능함
-안구 건조 개선 효과 — 꾸준히 복용 시 눈의 뻑뻑함과 건조함 완화에 도움이 됨
-rTG 오메가3 가성비 — rTG 형태 오메가3를 5,000원에 부담 없이 지속 구매 가능함</t>
+          <t>깔끔한 커피 대용 맛 — 씁쓸함이 적고 깔끔하여 부담 없이 아메리카노 대용으로 마시기 좋음
+원활한 배변 활동 촉진 — 꾸준히 마시면 배변 활동이 원활해지고 몸이 가벼워지는 느낌을 받음
+찬물에도 잘 녹는 편의성 — 스틱 타입이라 휴대가 편리하고 찬물에도 쉽게 잘 녹음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>속 더부룩함 없는 복용감 — 타사 제품 대비 섭취 후 속 더부룩함이나 불편함이 적음
-간 피로 개선 체감 — 꾸준히 복용 시 피로감이 줄어들고 컨디션 유지에 도움 됨
-비타민B 복합 가성비 — 밀크씨슬과 비타민B군을 저렴한 가격으로 한 번에 보충함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>100% 유기농 레몬 원액 — 설탕이 들어가지 않은 순수 유기농 레몬이라 안심하고 복용함
+떫지 않은 상쾌한 풍미 — 떫은 맛없이 상큼하여 물이나 탄산수에 타 마시면 상쾌함
+개별 포장의 가성비 — 1포씩 개별 포장되어 외출 시 휴대하기 편하고 가격도 저렴함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>상대적으로 낮은 함량 — 저렴한 가격 특성상 약국 제품에 비해 영양 성분 함량이 적을 수 있음
-살짝 큰 알약 크기 — 사람에 따라 정제 알약의 크기가 약간 크게 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>미흡한 체감 효과 — 개인차에 따라 식후 졸음이나 혈당 조절 측면의 직접 체감이 부족함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>저녁 복용 시 수면 영향 — 저녁 식후에 복용할 경우 사람에 따라 잠들기 어려울 수 있음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>야간 복용 시 수면 영향 — 저녁 식후 복용할 경우 활력 증가로 수면에 방해가 될 수 있음</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>단일 루테인 위주의 성분 — 지아잔틴이나 아스타잔틴 성분은 별도로 함유되어 있지 않음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>시중 이온음료 대비 옅은 맛 — 기존 포카리스웨트 등 음료에 비해 맛이 다소 밍밍하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>소용량 및 씁쓸한 맛 — 1포 용량이 적어 2포를 타야 진해지며 사람에 따라 다소 씁쓸함</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>체감 효과의 개인차 — 개인에 따라 식후 졸음 개선이나 효과를 즉각 체감하기 어려움</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛에 대한 호불호 — 동봉된 레몬즙의 신맛이 시큼하여 잘 못 먹는 경우 부담될 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 및 잦은 품절 — 캡슐 크기가 커 삼키기 어려울 수 있으며 품절이 자주 발생함</t>
+          <t>다소 옅은 커피 맛과 농도 — 1포 용량이 적어 진한 진도감을 원할 경우 2포 이상 타야 함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -6027,47 +6030,47 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6251,7 +6254,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6259,43 +6262,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>14719</v>
+        <v>8056</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 알약이 아닌 달콤한 구미 타입이라 섭취 부담이 없음</t>
+          <t>2개월 대용량 기획 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>빠르고 깊은 수면 유도 — 취침 전 복용 시 잠에 금방 들고 푹 자는 데 효과적임</t>
+          <t>하루 한 알의 간편한 케어 — 하루 한 캡슐을 물과 함께 먹으면 되어 매일의 루틴으로 용이함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -6306,7 +6309,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6314,43 +6317,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>8055</v>
+        <v>14723</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>하루 한 알 간편 케어 — 아침 공복에 1캡슐로 여성 건강과 장 건강을 관리함</t>
+          <t>부담 없는 구미 형태 — 알약 대신 젤리 형태로 되어 있어 맛있고 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>넉넉한 더블 기획 구성 — 2개월 분량의 알찬 구성으로 넉넉하게 챙겨 먹기 좋음</t>
+          <t>수면 유도 및 숙면 도움 — 식물성 멜라토닌 성분으로 뒤척임 없이 깊은 잠에 들도록 도움</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -6361,7 +6364,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6369,43 +6372,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>24087</v>
+        <v>457</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>장 건강 및 면역 케어 — 꾸준히 먹으면 장이 편안해지고 면역 유지에 도움을 줌</t>
+          <t>장 건강과 체지방 관리 — 체지방 감소와 장 건강을 동시에 관리하는 이중기능성 제품임</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>혜자스러운 1+1 기획 — 1+1 더블 구성과 증정품을 함께 얻을 수 있어 가성비 높음</t>
+          <t>맛있는 요거트 풍미 — 상큼한 요거트 맛이라 하루 한 포씩 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -6416,7 +6419,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6424,50 +6427,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>457</v>
+        <v>24090</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>장과 체지방 동시 관리 — 체지방 감소와 장 건강을 함께 챙기는 이중 기능성 제품임</t>
+          <t>1+1 기획의 알찬 혜택 — 1+1 기획 구성과 증정품 제공으로 가성비 높게 구매 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>상큼한 요거트 맛 — 상큼한 요거트 맛이라 하루 한 포씩 맛있게 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>속 편한 뱃살 케어 — 복용 시 아랫배가 가벼워지고 더부룩한 속이 한결 편안해짐</t>
-        </is>
-      </c>
+          <t>장 건강 및 면역 케어 — 공복 복용으로 장 환경을 개선하고 면역력을 관리하는 데 적합함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6475,7 +6474,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6483,54 +6482,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000002944&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0000/A00000000294413ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>12309</v>
+        <v>21297</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>속 편한 배변 활동 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 가도록 도움</t>
+          <t>고함량 비타민C 섭취 — 1000mg 고함량 구성으로 피로를 줄이고 컨디션을 끌어올려 줌</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>장과 피부 면역 동시 보충 — 100억 유산균으로 장 건강과 피부 면역 관리를 동시에 진행함</t>
+          <t>높은 브랜드 신뢰성 — 대한민국 대표 비타민 브랜드 제품으로 안심하고 구매함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>섭취 시 강한 신맛 — 고함량 비타민C 특성상 신맛이 강하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6538,37 +6541,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>솔티스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000234147&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023414702ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>106</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>15342</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>비타민 C와 D의 결합 — 비타민C와 비타민D를 한 번에 복용 가능하여 관리가 효율적임</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>면역 및 건강 유지 효과 — 실내 생활에 부족한 비타민D와 면역 케어 비타민C를 동시에 보충함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6577,7 +6588,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6585,58 +6596,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563462ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>26614</v>
+        <v>17520</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>확실한 디톡스 및 붓기 제거 — 과식 후 디톡스나 급진급빠 시 뱃살이 들어가고 라인이 정돈됨</t>
+          <t>부담 없는 저렴한 가성비 — 커피 한 잔 가격 수준의 저렴함으로 지속적인 구매가 용이함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>원활한 속 비움 효과 — 섭취 시 화장실을 잘 가게 되고 묵직했던 속이 개운해짐</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 정제 사이즈가 좀 더 커서 삼킬 때 다소 부담이 느껴짐</t>
-        </is>
-      </c>
+          <t>비린내 없는 부드러운 삼킴 — 캡슐 크기가 적당하고 비린내가 느껴지지 않아 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>위생적인 개별 낱개 포장 — 개별 포장되어 있어 들고 다니기 쉽고 보관이 위생적임</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6644,43 +6655,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>15338</v>
+        <v>12312</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>비타민 C와 D의 올인원 — 면역 관리를 돕는 비타민C와 결핍되기 쉬운 비타민D를 한 번에 복용함</t>
+          <t>복통 없는 배변 개선 — 배 아픔 없이 화장실을 원활하고 상쾌하게 가도록 도와줌</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>높은 신뢰도와 가성비 — 믿을 수 있는 대표 브랜드 제품으로 꾸준히 챙겨 먹기 적합함</t>
+          <t>피부와 장의 동시 케어 — 장 건강과 더불어 피부 면역을 관리하는 데 도움을 줌</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6726,16 +6737,16 @@
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>13675</v>
+        <v>13678</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>빠른 숙면 유도 체감 — 뒤척임 없이 금방 잠들고 새벽에 깨지 않도록 수면의 질을 높임</t>
+          <t>맛있는 구미 형태의 제형 — 상큼하고 맛있는 과일 맛 젤리 타입이라 간식처럼 먹기 좋음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>맛있는 식물성 구미 — 부담 없는 식물성 성분에 달콤한 젤리 맛이라 지속 복용하기 편함</t>
+          <t>수면 질 개선 및 숙면 — 새벽에 깨지 않고 빠른 수면에 들도록 돕는 효과가 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -6746,7 +6757,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6754,37 +6765,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[올영단독] 정관장 에브리타임 세븐베리/배/한라봉 플레이버 7포 단독기획</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15,600원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225001&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022500124ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>6735</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>2065</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>신속한 배변 반응 및 변비 완화 — 섭취 후 빠르게 신호가 오며 만성 변비 개선에 뛰어남</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>체지방 및 아랫배 관리 — 지속 복용 시 체지방 감량과 아랫배 관리 느낌을 받음</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6901,52 +6920,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
     </row>
@@ -6958,52 +6977,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>바이오코어유산균</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>솔티스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
         </is>
       </c>
     </row>
@@ -7015,44 +7034,44 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
@@ -7060,7 +7079,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 정관장 에브리타임 세븐베리/배/한라봉 플레이버 7포 단독기획</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
     </row>
@@ -7071,34 +7090,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.9</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="7">
@@ -7108,34 +7127,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14719</v>
+        <v>8056</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8055</v>
+        <v>14723</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>24087</v>
+        <v>457</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>457</v>
+        <v>24090</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12309</v>
+        <v>21297</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>106</v>
+        <v>15342</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>26614</v>
+        <v>17520</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>15338</v>
+        <v>12312</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>13675</v>
+        <v>13678</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6735</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7146,55 +7165,65 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 알약이 아닌 달콤한 구미 타입이라 섭취 부담이 없음
-빠르고 깊은 수면 유도 — 취침 전 복용 시 잠에 금방 들고 푹 자는 데 효과적임</t>
+          <t>2개월 대용량 기획 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉하게 섭취할 수 있음
+하루 한 알의 간편한 케어 — 하루 한 캡슐을 물과 함께 먹으면 되어 매일의 루틴으로 용이함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>하루 한 알 간편 케어 — 아침 공복에 1캡슐로 여성 건강과 장 건강을 관리함
-넉넉한 더블 기획 구성 — 2개월 분량의 알찬 구성으로 넉넉하게 챙겨 먹기 좋음</t>
+          <t>부담 없는 구미 형태 — 알약 대신 젤리 형태로 되어 있어 맛있고 부담 없이 먹을 수 있음
+수면 유도 및 숙면 도움 — 식물성 멜라토닌 성분으로 뒤척임 없이 깊은 잠에 들도록 도움</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>장 건강 및 면역 케어 — 꾸준히 먹으면 장이 편안해지고 면역 유지에 도움을 줌
-혜자스러운 1+1 기획 — 1+1 더블 구성과 증정품을 함께 얻을 수 있어 가성비 높음</t>
+          <t>장 건강과 체지방 관리 — 체지방 감소와 장 건강을 동시에 관리하는 이중기능성 제품임
+맛있는 요거트 풍미 — 상큼한 요거트 맛이라 하루 한 포씩 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>장과 체지방 동시 관리 — 체지방 감소와 장 건강을 함께 챙기는 이중 기능성 제품임
-상큼한 요거트 맛 — 상큼한 요거트 맛이라 하루 한 포씩 맛있게 챙겨 먹기 좋음
-속 편한 뱃살 케어 — 복용 시 아랫배가 가벼워지고 더부룩한 속이 한결 편안해짐</t>
+          <t>1+1 기획의 알찬 혜택 — 1+1 기획 구성과 증정품 제공으로 가성비 높게 구매 가능함
+장 건강 및 면역 케어 — 공복 복용으로 장 환경을 개선하고 면역력을 관리하는 데 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>속 편한 배변 활동 — 복통이나 가스 차는 증상 없이 부드럽게 화장실을 가도록 도움
-장과 피부 면역 동시 보충 — 100억 유산균으로 장 건강과 피부 면역 관리를 동시에 진행함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
+          <t>고함량 비타민C 섭취 — 1000mg 고함량 구성으로 피로를 줄이고 컨디션을 끌어올려 줌
+높은 브랜드 신뢰성 — 대한민국 대표 비타민 브랜드 제품으로 안심하고 구매함</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>비타민 C와 D의 결합 — 비타민C와 비타민D를 한 번에 복용 가능하여 관리가 효율적임
+면역 및 건강 유지 효과 — 실내 생활에 부족한 비타민D와 면역 케어 비타민C를 동시에 보충함</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>확실한 디톡스 및 붓기 제거 — 과식 후 디톡스나 급진급빠 시 뱃살이 들어가고 라인이 정돈됨
-원활한 속 비움 효과 — 섭취 시 화장실을 잘 가게 되고 묵직했던 속이 개운해짐</t>
+          <t>부담 없는 저렴한 가성비 — 커피 한 잔 가격 수준의 저렴함으로 지속적인 구매가 용이함
+비린내 없는 부드러운 삼킴 — 캡슐 크기가 적당하고 비린내가 느껴지지 않아 먹기 편함
+위생적인 개별 낱개 포장 — 개별 포장되어 있어 들고 다니기 쉽고 보관이 위생적임</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>비타민 C와 D의 올인원 — 면역 관리를 돕는 비타민C와 결핍되기 쉬운 비타민D를 한 번에 복용함
-높은 신뢰도와 가성비 — 믿을 수 있는 대표 브랜드 제품으로 꾸준히 챙겨 먹기 적합함</t>
+          <t>복통 없는 배변 개선 — 배 아픔 없이 화장실을 원활하고 상쾌하게 가도록 도와줌
+피부와 장의 동시 케어 — 장 건강과 더불어 피부 면역을 관리하는 데 도움을 줌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>빠른 숙면 유도 체감 — 뒤척임 없이 금방 잠들고 새벽에 깨지 않도록 수면의 질을 높임
-맛있는 식물성 구미 — 부담 없는 식물성 성분에 달콤한 젤리 맛이라 지속 복용하기 편함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>맛있는 구미 형태의 제형 — 상큼하고 맛있는 과일 맛 젤리 타입이라 간식처럼 먹기 좋음
+수면 질 개선 및 숙면 — 새벽에 깨지 않고 빠른 수면에 들도록 돕는 효과가 있음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>신속한 배변 반응 및 변비 완화 — 섭취 후 빠르게 신호가 오며 만성 변비 개선에 뛰어남
+체지방 및 아랫배 관리 — 지속 복용 시 체지방 감량과 아랫배 관리 느낌을 받음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7206,13 +7235,13 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>섭취 시 강한 신맛 — 고함량 비타민C 특성상 신맛이 강하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 정제 사이즈가 좀 더 커서 삼킬 때 다소 부담이 느껴짐</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
@@ -7225,44 +7254,44 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>15,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>13,950원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>17,400원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>8,900원</t>
@@ -7270,7 +7299,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>15,600원</t>
+          <t>18,900원</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7396,20 +7425,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -7418,20 +7447,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -7444,16 +7473,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -7462,23 +7491,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7506,7 +7535,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7516,10 +7545,10 @@
         <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7528,7 +7557,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7550,7 +7579,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7560,10 +7589,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7572,7 +7601,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7585,53 +7614,9 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -2600,22 +2600,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>고급스러운 제품 패키지 — 패키지가 고급스럽고 단정하여 선물용으로 전달하기에 적합함</t>
+          <t>간편한 섭취와 맛있는 풍미 — 액상과 정제로 구성되어 간편하게 먹을 수 있으며 맛이 양호함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 효과 — 피로감이 줄어들고 컨디션 및 활력이 회복되는 느낌을 받음</t>
+          <t>체력 증진 및 피로 회복 — 회식 다음 날이나 육아, 업무로 지쳤을 때 활력을 도둠</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>편리한 휴대와 올인원 섭취 — 가볍고 휴대성이 좋으며 액상과 정제를 한 번에 챙길 수 있음</t>
+          <t>선물용으로 높은 만족도 — 받는 사람의 건강을 챙겨줄 수 있어 선물용으로 반응이 좋음</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용 활용도가 떨어짐</t>
+          <t>배송 지연 및 사은품 누락 — 배송 처리가 느리고 안내된 사은품이 동봉되지 않음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2663,24 +2663,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>거부감 없는 망고피치 맛 — 쓴맛이나 특유의 향이 없어 망고피치 맛 액상을 부담 없이 마실 수 있음</t>
+          <t>물 없는 간편한 섭취 — 상단 정제와 하단 액상을 물 없이 한 번에 복용할 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>목넘김 편한 작은 알약 — 알약 크기가 작아 물 없이 액상과 함께 편하게 삼킬 수 있음</t>
+          <t>확실한 피로 회복 체감 — 매일 한 병씩 복용 시 피로가 풀리고 기운이 나는 효과가 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>신속한 체력 보충 효과 — 피로할 때 섭취 시 활력이 생기고 피로가 빠르게 회복됨</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>알약 크기의 체감 개인차 — 알약을 잘 넘기지 못하는 경우 다소 크게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>우수한 가성비와 선물 활용성 — 남녀노소 누구에게나 선물하기 좋으며 가성비가 뛰어남</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2726,20 +2722,24 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 상자 및 구성 패키지가 깔끔하고 고급스러워 선물용으로 제격임</t>
+          <t>우수한 피로 개선 효과 — 하루 종일 일해도 아침에 가뿐하며 피로감이 줄어듦</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>탁월한 피로 회복 체감 — 피곤하고 나른할 때 섭취 시 힘이 나고 컨디션이 올라감</t>
+          <t>고급스러운 포장과 구성 — 포장 상태가 고급스러워 생일이나 응원 선물로 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>간편한 휴대 및 섭취법 — 휴대하기 편하고 피곤할 때마다 간편하게 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>부담 없는 섭취 방식 — 맛이 좋고 먹기 편해 꾸준히 챙겨 먹기 적합함</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>당뇨 환자의 섭취 주의 — 당 성분 함유로 인해 당뇨 질환자의 복용 시 주의가 필요함</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2785,25 +2785,29 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>물 없이 먹는 구미 제형 — 젤리 형태라 물 없이도 어디서나 간식처럼 쉽게 섭취 가능함</t>
+          <t>맛있는 젤리 제형 — 상큼한 맛과 식감으로 부담 없는 건강 간식처럼 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>달콤상큼한 과일 풍미 — 비타민 특유의 냄새나 쓴맛 없이 달콤하고 식감이 쫀득함</t>
+          <t>귀여운 포장과 굿즈 증정 — 선물 포장이 귀엽고 함께 증정되는 키캡 만족도가 높음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>남녀노소 높은 만족도 — 어른과 아이 모두 부담 없이 즐길 수 있고 포장 디자인도 예쁨</t>
+          <t>일상 속 활력 충전 — 지친 몸에 영양을 공급하여 기분 전환과 활력에 도움 됨</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>아쉬운 하루 권장 섭취량 — 맛이 좋아 하루 2개라는 권장 섭취량이 아쉽게 느껴짐</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>다소 단단한 젤리 식감 — 젤리가 완전히 말랑하지 않아 식감에 대한 아쉬움이 있음</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>키캡 굿즈 로고 표기 — 동봉된 키캡 뒷면에 브랜드 로고가 표기되어 아쉬움</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -2848,17 +2852,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>위생적인 1회 개별 포장 — 1회분씩 깔끔하게 개별 포장되어 있어 위생적이고 휴대가 용이함</t>
+          <t>높은 휴대성과 편의성 — 가방에 쏙 들어가는 크기라 외출 시에도 챙겨 마시기 편함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>부담 없는 알약 목넘김 — 알약 크기가 크지 않아서 삼킬 때 목넘김이 나쁘지 않음</t>
+          <t>빠른 체력 회복 체감 — 피로감이 심할 때 먹으면 체력이 보충되는 느낌을 받음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>신속한 피로 회복 체감 — 섭취 후 피로 회복 및 에너지 충전 효과를 신속하게 체감함</t>
+          <t>합리적인 가격과 빠른 배송 — 배송이 신속하며 부담 없는 가격대로 구매할 수 있음</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2907,15 +2911,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있고 간편한 liquid 제형 — 맛이 우수하고 가방에 휴대하여 편하게 마실 수 있음</t>
+          <t>넉넉한 30병 구성 — 수량이 넉넉하여 출근이나 운동 시 오래 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 체감 — 피로감이 풀리고 몸의 컨디션이 한결 편안해짐</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>거부감 없는 맛과 향 — 향과 맛에 부담이 없어 아이들도 거부감 없이 잘 마심</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>선물용 쇼핑백 증정 — 쇼핑백이 함께 포함되어 생일이나 명절 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2962,24 +2970,20 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>상큼한 진한 오렌지 맛 — 진하고 상큼한 오렌지 맛 액상이라 거부감 없이 마시기 좋음</t>
+          <t>신속한 체력 회복 도움 — 수술 후 회복기나 피로가 누적되었을 때 기운을 북돋아 줌</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>확실한 체력 증진 효과 — 체력이 떨어졌을 때 피로감을 낮추고 컨디션을 올려줌</t>
+          <t>부담 없는 선물용 영양제 — 지인이나 친구에게 부담 없이 건강을 선물하기 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>우수한 가방 속 휴대성 — 컴팩트한 크기로 가방에 넣어 다니며 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>직접 구매 시 가격 부담 — 제품의 성능은 우수하나 가격대가 높게 느껴짐</t>
-        </is>
-      </c>
+          <t>신속한 배송 서비스 — 주문 후 배송이 빠르고 안전하게 도착함</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -3025,17 +3029,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>직접 섞어 마시는 재미 — 버튼을 눌러 분말을 액상에 섞는 방식이라 섭취하는 재미가 있음</t>
+          <t>신선한 액상 분말 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시므로 신선함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>고급스러운 포장 케이스 — 패키지가 고급스럽고 디자인이 알차서 선물하기에 적합함</t>
+          <t>고급스러운 포장 디자인 — 패키지가 예쁘고 고급스러워 축하 및 응원 선물로 뛰어남</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 음료 맛 — 쓴맛 없이 음료처럼 상큼하고 맛있어서 편하게 마실 수 있음</t>
+          <t>맛있는 영양 보충 — 음료처럼 맛이 좋아 하루 한 병씩 부담 없이 비타민을 챙김</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3084,20 +3088,24 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>상큼한 레몬향 풍미 — 비타민 특유의 쓴맛 없이 레몬향이 나 부담 없이 섭취함</t>
+          <t>빠른 피로 회복 효과 — 액상 제형으로 피로할 때 마시면 부스터처럼 즉각 피로가 풀림</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>올인원 샷 형태의 편의성 — 액상과 알약이 함께 들어 있어 물 없이 한번에 보충 가능함</t>
+          <t>안정적인 패키지 포장 — 내부 홈에 앰플이 딱 고정되어 안전하게 배송됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>개별 포장으로 편리한 휴대 — 하나씩 개별 포장되어 가방에 넣고 다니며 챙겨 먹기 유용함</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>간편한 일상 영양 섭취 — 하루 한 개씩 개별 휴대하며 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>적은 수량 구성 — 1박스 5입 구성이라 지속 복용 시 수량이 부족하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3143,17 +3151,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 제공 — 남성용과 여성용 옵션 선택이 가능하여 영양 관리에 유용함</t>
+          <t>한 번에 챙기는 멀티 케어 — 필요한 영양소를 한 번에 케어할 수 있어 피로함이 줄어듦</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>보관이 쉬운 분리 구성 — 소박스로 나뉘어 포장되어 있어 보관 및 개별 관리가 편리함</t>
+          <t>우수한 포장과 디자인 — 깔끔한 선물 포장과 디자인으로 정성스러움이 전달됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>체감되는 피로 완화 — 피로감이 줄어들고 일상 활력을 케어하는 효과가 느껴짐</t>
+          <t>편리한 휴대성 — 하루에 하나씩 가방에 넣어 다니며 복용하기 용이함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3249,18 +3257,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>뛰어난 구성과 가성비 — 부담 없는 가격에 수량이 넉넉하고 다양한 구성으로 만족도가 높음</t>
+          <t>뛰어난 가성비 구성 — 24개입 구성을 매우 합리적인 가격으로 구매 가능함</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 뻑뻑함이 적고 양념이 과하지 않아 매일 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>다양한 맛과 부드러운 식감 — 뻑뻑함이 적고 맛이 다채로워 매일 먹어도 질리지 않음</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>전자레인지 간편 조리 — 전자레인지로 빠르게 조리할 수 있어 다이어트 식단에 적합함</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 시 해동 발생 문제 — 배송 도중 제품이 해동되어 도착하는 아쉬움이 있음</t>
+          <t>배송 시 제품 해동 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3308,20 +3320,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>활용성 높은 럭셔리 포장 — 가방으로 활용할 수 있는 플리츠백 포장이 매우 고급스러움</t>
+          <t>고급스러운 에디션 포장 — 은은한 핑크 포장과 패키지가 고급스러워 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>콜라겐과 비오틴 동시 보충 — 콜라겐과 비오틴을 따로 챙기지 않고 한 번에 섭취 가능함</t>
+          <t>피부 상태 개선 체감 — 꾸준히 복용 시 피부가 맑아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>부담 없는 오렌지 맛 — 상큼한 오렌지 맛 액상 타입이라 목넘김이 편하고 맛있음</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>추가 앰플 및 샘플 증정 — 추가 앰플 증정 및 샘플 구성이 알차 만족스러움</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>단기 복용 시 효과 미체감 — 복용 초반에는 즉각적인 효과를 확인하기 어려움</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3367,25 +3383,29 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 전자레인지 조리 후에도 퍽퍽하지 않고 촉촉함이 남아있음</t>
+          <t>다채로운 맛과 뛰어난 풍미 — 다양한 맛으로 구성되어 골라 먹기 좋고 맛이 우수함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 여러 맛과 형태가 섞여 있어 지속적인 식단 관리에 유용함</t>
+          <t>저렴한 한 달 식단 패키지 — 30팩 구성을 저렴하게 구매할 수 있어 가격 만족도가 높음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>유용한 증정 보냉백 — 증정품인 보냉백이 귀엽고 도시락을 휴대할 때 쓰기 좋음</t>
+          <t>사은품 보냉백의 활용성 — 증정되는 보냉백으로 도시락 휴대가 용이함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>예고와 다른 사은품 배송 — 방송 안내와 다른 디자인의 보냉백이 배송되어 아쉬움이 남음</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>배송 중 해동 발생 — 여름철 배송 시 내용물이 많이 녹아서 전달됨</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>증정 사은품 누락 우려 — 보냉백 등의 증정품이 동봉되지 않거나 배송이 지연됨</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
@@ -3430,17 +3450,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린내나 텁텁함 없이 음료수처럼 맛있음</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함과 비린 맛이 없어 마시기 편함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 제로슈가 — 제로슈가 및 락토프리 제품으로 공복 복용 시에도 속이 편안함</t>
+          <t>속 편한 분리유청 성분 — 마신 뒤 더부룩함이나 속 불편함 없이 깔끔하게 소화됨</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>운동 후 간편한 단백 보충 — 낮은 칼로리로 운동 후 간편하게 단백질을 챙기기 적합함</t>
+          <t>간편한 운동 후 단백질 보충 — 슬림한 패키지로 휴대성이 좋고 당과 칼로리 부담이 적음</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3489,17 +3509,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>풍성하고 알찬 사은품 — 다양한 추가 사은품이 포함되어 구성 만족도가 높음</t>
+          <t>식후 더부룩함 개선 — 고기나 밀가루 섭취 후 복용 시 답답한 속이 한결 편안해짐</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>고소한 군고구마 풍미 — 효소 특유의 냄새 대신 군고구마 향이 나 고소하고 맛있음</t>
+          <t>배변 활동 원활 — 꾸준히 복용하면 매일 원활한 배변 활동에 도움 됨</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>편안한 소화와 배변 개선 — 속 더부룩함이 줄어들고 화장실 이용이 원활해짐</t>
+          <t>고소한 군고구마 맛 — 거부감 없는 고소한 군고구마 맛으로 편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3548,17 +3568,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>부담 없는 무색무취무맛 — 맛과 냄새가 없어 물에 타거나 입에 털어 넣기 편리함</t>
+          <t>운동 수행 능력 향상 — 꾸준히 먹으면 득근 및 세트 수행에 도움을 받음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>고운 입자의 뛰어난 용해성 — 입자가 고와서 물에 잘 녹고 신속하게 복용할 수 있음</t>
+          <t>음료와의 용해성 및 편의성 — 물이나 음료에 잘 타서 부담 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 실질적 도움이 됨</t>
+          <t>귀여운 키링 증정 — 제품과 함께 제공되는 키링 사은품의 만족도가 높음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3607,17 +3627,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>높은 아르기닌 함유량 — 1포당 6,200mg의 고함량 아르기닌을 제공하여 활력 보충에 도움 됨</t>
+          <t>6,200mg 초고함량 활력 — 고함량 아르기닌으로 섭취 후 피로 회복과 활력이 뛰어남</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>새콤상큼한 베리 맛 — 맛이 상큼하고 달콤하여 거부감 없이 섭취 가능함</t>
+          <t>선물용 패키지 구성 — 고급스러운 포장과 쇼핑백, 추가 증정 5포로 선물에 적합함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>편리한 스틱형 섭취 — 바로 짜 먹거나 물에 타 마실 수 있는 스틱 형태라 편리함</t>
+          <t>휴대하기 편한 스틱 제형 — 개별 포장된 액상 스틱으로 언제 어디서나 1포씩 먹기 편함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3666,17 +3686,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>역하지 않은 레몬 맛 — 상큼한 레몬 맛 액상이라 역함 없이 맛있게 마실 수 있음</t>
+          <t>상큼한 레몬맛 액상 — 레몬맛 액상 제형이라 물에 타서 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>액상 스틱의 높은 휴대성 — 물에 잘 녹는 액상 스틱이라 외출 시 챙기기 용이함</t>
+          <t>운동 전후 및 아침 활력 — 아침 공복이나 운동 시 복용하면 하루 시작이 가벼워짐</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 아침 공복 및 운동 전 섭취 시 몸이 가벼워지고 피로가 줄어듦</t>
+          <t>응원 선물로 우수함 — 웨이트 트레이닝을 하거나 피로한 지인 선물로 만족도가 높음</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3725,7 +3745,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 섭취 후 숙취를 해소하는 효과가 뛰어남</t>
+          <t>탁월한 숙취 해소 효과 — 음주 후 섭취 시 숙취 해소 효능이 매우 우수함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -4090,75 +4110,76 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 제품 패키지 — 패키지가 고급스럽고 단정하여 선물용으로 전달하기에 적합함
-체감되는 피로 회복 효과 — 피로감이 줄어들고 컨디션 및 활력이 회복되는 느낌을 받음
-편리한 휴대와 올인원 섭취 — 가볍고 휴대성이 좋으며 액상과 정제를 한 번에 챙길 수 있음</t>
+          <t>간편한 섭취와 맛있는 풍미 — 액상과 정제로 구성되어 간편하게 먹을 수 있으며 맛이 양호함
+체력 증진 및 피로 회복 — 회식 다음 날이나 육아, 업무로 지쳤을 때 활력을 도둠
+선물용으로 높은 만족도 — 받는 사람의 건강을 챙겨줄 수 있어 선물용으로 반응이 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 망고피치 맛 — 쓴맛이나 특유의 향이 없어 망고피치 맛 액상을 부담 없이 마실 수 있음
-목넘김 편한 작은 알약 — 알약 크기가 작아 물 없이 액상과 함께 편하게 삼킬 수 있음
-신속한 체력 보충 효과 — 피로할 때 섭취 시 활력이 생기고 피로가 빠르게 회복됨</t>
+          <t>물 없는 간편한 섭취 — 상단 정제와 하단 액상을 물 없이 한 번에 복용할 수 있음
+확실한 피로 회복 체감 — 매일 한 병씩 복용 시 피로가 풀리고 기운이 나는 효과가 있음
+우수한 가성비와 선물 활용성 — 남녀노소 누구에게나 선물하기 좋으며 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 상자 및 구성 패키지가 깔끔하고 고급스러워 선물용으로 제격임
-탁월한 피로 회복 체감 — 피곤하고 나른할 때 섭취 시 힘이 나고 컨디션이 올라감
-간편한 휴대 및 섭취법 — 휴대하기 편하고 피곤할 때마다 간편하게 마시기 좋음</t>
+          <t>우수한 피로 개선 효과 — 하루 종일 일해도 아침에 가뿐하며 피로감이 줄어듦
+고급스러운 포장과 구성 — 포장 상태가 고급스러워 생일이나 응원 선물로 적합함
+부담 없는 섭취 방식 — 맛이 좋고 먹기 편해 꾸준히 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 먹는 구미 제형 — 젤리 형태라 물 없이도 어디서나 간식처럼 쉽게 섭취 가능함
-달콤상큼한 과일 풍미 — 비타민 특유의 냄새나 쓴맛 없이 달콤하고 식감이 쫀득함
-남녀노소 높은 만족도 — 어른과 아이 모두 부담 없이 즐길 수 있고 포장 디자인도 예쁨</t>
+          <t>맛있는 젤리 제형 — 상큼한 맛과 식감으로 부담 없는 건강 간식처럼 먹기 좋음
+귀여운 포장과 굿즈 증정 — 선물 포장이 귀엽고 함께 증정되는 키캡 만족도가 높음
+일상 속 활력 충전 — 지친 몸에 영양을 공급하여 기분 전환과 활력에 도움 됨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>위생적인 1회 개별 포장 — 1회분씩 깔끔하게 개별 포장되어 있어 위생적이고 휴대가 용이함
-부담 없는 알약 목넘김 — 알약 크기가 크지 않아서 삼킬 때 목넘김이 나쁘지 않음
-신속한 피로 회복 체감 — 섭취 후 피로 회복 및 에너지 충전 효과를 신속하게 체감함</t>
+          <t>높은 휴대성과 편의성 — 가방에 쏙 들어가는 크기라 외출 시에도 챙겨 마시기 편함
+빠른 체력 회복 체감 — 피로감이 심할 때 먹으면 체력이 보충되는 느낌을 받음
+합리적인 가격과 빠른 배송 — 배송이 신속하며 부담 없는 가격대로 구매할 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 간편한 liquid 제형 — 맛이 우수하고 가방에 휴대하여 편하게 마실 수 있음
-확실한 피로 개선 체감 — 피로감이 풀리고 몸의 컨디션이 한결 편안해짐</t>
+          <t>넉넉한 30병 구성 — 수량이 넉넉하여 출근이나 운동 시 오래 챙겨 먹기 좋음
+거부감 없는 맛과 향 — 향과 맛에 부담이 없어 아이들도 거부감 없이 잘 마심
+선물용 쇼핑백 증정 — 쇼핑백이 함께 포함되어 생일이나 명절 선물용으로 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 진한 오렌지 맛 — 진하고 상큼한 오렌지 맛 액상이라 거부감 없이 마시기 좋음
-확실한 체력 증진 효과 — 체력이 떨어졌을 때 피로감을 낮추고 컨디션을 올려줌
-우수한 가방 속 휴대성 — 컴팩트한 크기로 가방에 넣어 다니며 챙겨 먹기 편함</t>
+          <t>신속한 체력 회복 도움 — 수술 후 회복기나 피로가 누적되었을 때 기운을 북돋아 줌
+부담 없는 선물용 영양제 — 지인이나 친구에게 부담 없이 건강을 선물하기 좋음
+신속한 배송 서비스 — 주문 후 배송이 빠르고 안전하게 도착함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>직접 섞어 마시는 재미 — 버튼을 눌러 분말을 액상에 섞는 방식이라 섭취하는 재미가 있음
-고급스러운 포장 케이스 — 패키지가 고급스럽고 디자인이 알차서 선물하기에 적합함
-상큼하고 맛있는 음료 맛 — 쓴맛 없이 음료처럼 상큼하고 맛있어서 편하게 마실 수 있음</t>
+          <t>신선한 액상 분말 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시므로 신선함
+고급스러운 포장 디자인 — 패키지가 예쁘고 고급스러워 축하 및 응원 선물로 뛰어남
+맛있는 영양 보충 — 음료처럼 맛이 좋아 하루 한 병씩 부담 없이 비타민을 챙김</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬향 풍미 — 비타민 특유의 쓴맛 없이 레몬향이 나 부담 없이 섭취함
-올인원 샷 형태의 편의성 — 액상과 알약이 함께 들어 있어 물 없이 한번에 보충 가능함
-개별 포장으로 편리한 휴대 — 하나씩 개별 포장되어 가방에 넣고 다니며 챙겨 먹기 유용함</t>
+          <t>빠른 피로 회복 효과 — 액상 제형으로 피로할 때 마시면 부스터처럼 즉각 피로가 풀림
+안정적인 패키지 포장 — 내부 홈에 앰플이 딱 고정되어 안전하게 배송됨
+간편한 일상 영양 섭취 — 하루 한 개씩 개별 휴대하며 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 제공 — 남성용과 여성용 옵션 선택이 가능하여 영양 관리에 유용함
-보관이 쉬운 분리 구성 — 소박스로 나뉘어 포장되어 있어 보관 및 개별 관리가 편리함
-체감되는 피로 완화 — 피로감이 줄어들고 일상 활력을 케어하는 효과가 느껴짐</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>한 번에 챙기는 멀티 케어 — 필요한 영양소를 한 번에 케어할 수 있어 피로함이 줄어듦
+우수한 포장과 디자인 — 깔끔한 선물 포장과 디자인으로 정성스러움이 전달됨
+편리한 휴대성 — 하루에 하나씩 가방에 넣어 다니며 복용하기 용이함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4166,29 +4187,30 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 부직포 포장 재질 — 부직포 포장의 이음새가 벌어지고 재활용 활용도가 떨어짐</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기의 체감 개인차 — 알약을 잘 넘기지 못하는 경우 다소 크게 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>배송 지연 및 사은품 누락 — 배송 처리가 느리고 안내된 사은품이 동봉되지 않음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>당뇨 환자의 섭취 주의 — 당 성분 함유로 인해 당뇨 질환자의 복용 시 주의가 필요함</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 하루 권장 섭취량 — 맛이 좋아 하루 2개라는 권장 섭취량이 아쉽게 느껴짐</t>
+          <t>다소 단단한 젤리 식감 — 젤리가 완전히 말랑하지 않아 식감에 대한 아쉬움이 있음
+키캡 굿즈 로고 표기 — 동봉된 키캡 뒷면에 브랜드 로고가 표기되어 아쉬움</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>직접 구매 시 가격 부담 — 제품의 성능은 우수하나 가격대가 높게 느껴짐</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>적은 수량 구성 — 1박스 5입 구성이라 지속 복용 시 수량이 부족하게 느껴짐</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4633,66 +4655,67 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 구성과 가성비 — 부담 없는 가격에 수량이 넉넉하고 다양한 구성으로 만족도가 높음
-부드럽고 촉촉한 식감 — 뻑뻑함이 적고 양념이 과하지 않아 매일 먹기 좋음</t>
+          <t>뛰어난 가성비 구성 — 24개입 구성을 매우 합리적인 가격으로 구매 가능함
+다양한 맛과 부드러운 식감 — 뻑뻑함이 적고 맛이 다채로워 매일 먹어도 질리지 않음
+전자레인지 간편 조리 — 전자레인지로 빠르게 조리할 수 있어 다이어트 식단에 적합함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>활용성 높은 럭셔리 포장 — 가방으로 활용할 수 있는 플리츠백 포장이 매우 고급스러움
-콜라겐과 비오틴 동시 보충 — 콜라겐과 비오틴을 따로 챙기지 않고 한 번에 섭취 가능함
-부담 없는 오렌지 맛 — 상큼한 오렌지 맛 액상 타입이라 목넘김이 편하고 맛있음</t>
+          <t>고급스러운 에디션 포장 — 은은한 핑크 포장과 패키지가 고급스러워 선물용으로 훌륭함
+피부 상태 개선 체감 — 꾸준히 복용 시 피부가 맑아지는 느낌을 받음
+추가 앰플 및 샘플 증정 — 추가 앰플 증정 및 샘플 구성이 알차 만족스러움</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 전자레인지 조리 후에도 퍽퍽하지 않고 촉촉함이 남아있음
-질리지 않는 다양한 맛 — 여러 맛과 형태가 섞여 있어 지속적인 식단 관리에 유용함
-유용한 증정 보냉백 — 증정품인 보냉백이 귀엽고 도시락을 휴대할 때 쓰기 좋음</t>
+          <t>다채로운 맛과 뛰어난 풍미 — 다양한 맛으로 구성되어 골라 먹기 좋고 맛이 우수함
+저렴한 한 달 식단 패키지 — 30팩 구성을 저렴하게 구매할 수 있어 가격 만족도가 높음
+사은품 보냉백의 활용성 — 증정되는 보냉백으로 도시락 휴대가 용이함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린내나 텁텁함 없이 음료수처럼 맛있음
-속 편한 락토프리 제로슈가 — 제로슈가 및 락토프리 제품으로 공복 복용 시에도 속이 편안함
-운동 후 간편한 단백 보충 — 낮은 칼로리로 운동 후 간편하게 단백질을 챙기기 적합함</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함과 비린 맛이 없어 마시기 편함
+속 편한 분리유청 성분 — 마신 뒤 더부룩함이나 속 불편함 없이 깔끔하게 소화됨
+간편한 운동 후 단백질 보충 — 슬림한 패키지로 휴대성이 좋고 당과 칼로리 부담이 적음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>풍성하고 알찬 사은품 — 다양한 추가 사은품이 포함되어 구성 만족도가 높음
-고소한 군고구마 풍미 — 효소 특유의 냄새 대신 군고구마 향이 나 고소하고 맛있음
-편안한 소화와 배변 개선 — 속 더부룩함이 줄어들고 화장실 이용이 원활해짐</t>
+          <t>식후 더부룩함 개선 — 고기나 밀가루 섭취 후 복용 시 답답한 속이 한결 편안해짐
+배변 활동 원활 — 꾸준히 복용하면 매일 원활한 배변 활동에 도움 됨
+고소한 군고구마 맛 — 거부감 없는 고소한 군고구마 맛으로 편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 무색무취무맛 — 맛과 냄새가 없어 물에 타거나 입에 털어 넣기 편리함
-고운 입자의 뛰어난 용해성 — 입자가 고와서 물에 잘 녹고 신속하게 복용할 수 있음
-운동 수행 능력 향상 — 섭취 시 펌핑감과 운동 효율을 높이는 데 실질적 도움이 됨</t>
+          <t>운동 수행 능력 향상 — 꾸준히 먹으면 득근 및 세트 수행에 도움을 받음
+음료와의 용해성 및 편의성 — 물이나 음료에 잘 타서 부담 없이 간편하게 섭취 가능함
+귀여운 키링 증정 — 제품과 함께 제공되는 키링 사은품의 만족도가 높음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>높은 아르기닌 함유량 — 1포당 6,200mg의 고함량 아르기닌을 제공하여 활력 보충에 도움 됨
-새콤상큼한 베리 맛 — 맛이 상큼하고 달콤하여 거부감 없이 섭취 가능함
-편리한 스틱형 섭취 — 바로 짜 먹거나 물에 타 마실 수 있는 스틱 형태라 편리함</t>
+          <t>6,200mg 초고함량 활력 — 고함량 아르기닌으로 섭취 후 피로 회복과 활력이 뛰어남
+선물용 패키지 구성 — 고급스러운 포장과 쇼핑백, 추가 증정 5포로 선물에 적합함
+휴대하기 편한 스틱 제형 — 개별 포장된 액상 스틱으로 언제 어디서나 1포씩 먹기 편함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>역하지 않은 레몬 맛 — 상큼한 레몬 맛 액상이라 역함 없이 맛있게 마실 수 있음
-액상 스틱의 높은 휴대성 — 물에 잘 녹는 액상 스틱이라 외출 시 챙기기 용이함
-체감되는 피로 회복 — 아침 공복 및 운동 전 섭취 시 몸이 가벼워지고 피로가 줄어듦</t>
+          <t>상큼한 레몬맛 액상 — 레몬맛 액상 제형이라 물에 타서 부담 없이 섭취 가능함
+운동 전후 및 아침 활력 — 아침 공복이나 운동 시 복용하면 하루 시작이 가벼워짐
+응원 선물로 우수함 — 웨이트 트레이닝을 하거나 피로한 지인 선물로 만족도가 높음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 섭취 후 숙취를 해소하는 효과가 뛰어남</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>탁월한 숙취 해소 효과 — 음주 후 섭취 시 숙취 해소 효능이 매우 우수함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4701,13 +4724,18 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 해동 발생 문제 — 배송 도중 제품이 해동되어 도착하는 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+          <t>배송 시 제품 해동 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>단기 복용 시 효과 미체감 — 복용 초반에는 즉각적인 효과를 확인하기 어려움</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>예고와 다른 사은품 배송 — 방송 안내와 다른 디자인의 보냉백이 배송되어 아쉬움이 남음</t>
+          <t>배송 중 해동 발생 — 여름철 배송 시 내용물이 많이 녹아서 전달됨
+증정 사은품 누락 우려 — 보냉백 등의 증정품이 동봉되지 않거나 배송이 지연됨</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -4999,12 +5027,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>운동 시 에너지를 제공 — 러닝이나 운동 전에 먹으면 지치지 않고 힘이 유지됨</t>
+          <t>우수한 체력 보충 — 운동이나 라이딩, 야외 활동 시 피로 회복에 효과적임</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>맛과 휴대성의 유용함 — 맛이 좋고 가볍게 챙겨 먹기 좋은 스틱 형태로 구성됨</t>
+          <t>착한 가성비 — 다이소 판매 제품으로 저렴한 가격에 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -5054,20 +5082,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 약국 대비 부담 없는 가격으로 고함량 비타민B를 구매 가능함</t>
+          <t>부담 없는 가격의 비타민 — 저렴한 가격으로 필수 영양소인 비타민B를 챙길 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>피로 개선 및 구내염 완화 — 복용 후 피로감이 줄고 혓바늘이 줄어드는 효과를 봄</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>편리한 휴대 및 복용 — 포장이 간편하여 상시 휴대하며 복용하기 좋음</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>높은 재구매 만족도 — 지속적으로 꾸준히 재구매하여 섭취할 정도로 만족함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>효과 체감의 개인차 — 섭취 후 피로 개선 등의 신체적 효과를 크게 느끼지 못함</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5113,20 +5141,16 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>검증된 제약사의 가성비 — 유명 브랜드 제품을 저렴하게 구매할 수 있어 만족도가 높음</t>
+          <t>뛰어난 가성비와 성분 — 저렴한 가격 대비 코큐텐 함량과 품질이 뛰어남</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>혈압 및 활력 케어 효과 — 100mg의 코큐텐 함량으로 혈압 조절과 활력 유지에 도움 됨</t>
+          <t>간편한 복용과 빠른 배송 — 복용하기 편하며 주문 후 배송이 빠름</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>야간 복용 시 수면 영향 — 저녁 식후 복용할 경우 활력 증가로 수면에 방해가 될 수 있음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5172,12 +5196,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>고급스러운 외관 디자인 — 패키지 케이스가 은은하게 반짝여 선물용으로도 손색없음</t>
+          <t>고급스러운 패키지 디자인 — 은은하게 반짝이는 고급스러운 포장으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>합리적이고 착한 가격 — 품질 대비 가격이 저렴하여 부담 없이 구매 가능함</t>
+          <t>합리적인 구매 가격 — 침향환을 부담 없는 합리적인 가격대로 구매 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5227,22 +5251,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 작은 캡슐 — 캡슐 크기가 작고 부드러워 목넘김이 용이함</t>
+          <t>작은 알약 크기 — 정제 크기가 작아서 목넘김이 편하고 삼키기 쉬움</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>눈의 피로 및 건조함 완화 — 컴퓨터나 스마트폰 사용 후 느껴지는 눈의 뻑뻑함과 피로가 줄어듦</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>부담 없는 가성비 한 달 분량 — 루테인 권장량을 3천원대의 저렴한 가격으로 챙길 수 있음</t>
-        </is>
-      </c>
+          <t>부담 없는 가성비 — 컴퓨터 작업으로 피로한 눈 관리를 저렴하게 시작할 수 있음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>단일 루테인 위주의 성분 — 지아잔틴이나 아스타잔틴 성분은 별도로 함유되어 있지 않음</t>
+          <t>단기 복용 시 미미한 효과 — 복용 초반에는 눈 피로 개선 효과가 눈에 띄지 않음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -5290,24 +5310,20 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>신속한 전해질 및 수분 충전 — 땀을 많이 흘린 후 음용 시 수분과 전해질이 빠르게 보충됨</t>
+          <t>맛있는 이온음료 맛 — 포카리스웨트와 유사한 맛이 나 탄산음료 대신 마시기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>은은한 자몽 향의 편의성 — 자몽 향이 은은하게 퍼져 맹물보다 편하게 물을 많이 마실 수 있음</t>
+          <t>간편한 물 섭취 방식 — 분말을 물에 타서 간단하게 음용할 수 있음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>붓기 완화 및 대사 도움 — 칼륨과 식이섬유 배합으로 얼굴 붓기 제거 및 순환에 유용함</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>시중 이온음료 대비 옅은 맛 — 기존 포카리스웨트 등 음료에 비해 맛이 다소 밍밍하게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>나트륨 배출 및 붓기 관리 — 짜게 먹는 습관이 있거나 자주 붓는 경우 관리하기 유용함</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5353,22 +5369,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>작은 크기로 편한 목넘김 — 알약 크기가 작아서 복용할 때 삼키기 편함</t>
+          <t>편안한 목넘김 — 알약 크기가 크지 않아 섭취하기에 부담이 없음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>식전 복용 시 혈당 케어 — 식사 전 복용하면 식후 혈당 스파이크를 잡는 데 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>부담 없는 가성비 가격 — 저렴한 가격으로 식후 혈당 관리 영양제를 시도할 수 있음</t>
-        </is>
-      </c>
+          <t>식후 혈당 가성비 관리 — 식후 혈당 관리를 저렴한 가격으로 꾸준히 하기 적합함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>체감 효과의 개인차 — 개인에 따라 식후 졸음 개선이나 효과를 즉각 체감하기 어려움</t>
+          <t>체감 효능 미흡 — 섭취 후 신체 변화나 효능이 크게 느껴지지 않음</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5416,22 +5428,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>올리브오일과 레몬의 조합 — 오일 캡슐과 레몬즙을 개별 포장하여 공복에 한 번에 먹기 편함</t>
+          <t>간편한 포장 및 복용 — 올리브오일과 레몬 조합을 낱개로 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>원활한 배변 및 속 편함 — 아침 공복 복용 시 장 건강과 배변 활동에 유용한 효과를 봄</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>휴대가 용이한 포장 용기 — 병 패키징이 야무지고 개별 포장되어 출근 시 챙겨가기 용이함</t>
-        </is>
-      </c>
+          <t>저렴한 유행 제품 체험 — 유행하는 오일 레몬 조합을 저렴한 가격에 경험 가능함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>강한 신맛에 대한 호불호 — 동봉된 레몬즙의 신맛이 시큼하여 잘 못 먹는 경우 부담될 수 있음</t>
+          <t>효과 체감의 부족 — 섭취 후 신체적인 변화나 효과를 체감하기 어려움</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -5479,22 +5487,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>깔끔한 커피 대용 맛 — 씁쓸함이 적고 깔끔하여 부담 없이 아메리카노 대용으로 마시기 좋음</t>
+          <t>압도적인 가성비 — 10포 구성을 매우 저렴한 가격으로 구매할 수 있음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 촉진 — 꾸준히 마시면 배변 활동이 원활해지고 몸이 가벼워지는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>찬물에도 잘 녹는 편의성 — 스틱 타입이라 휴대가 편리하고 찬물에도 쉽게 잘 녹음</t>
-        </is>
-      </c>
+          <t>연하고 구수한 맛 — 보리차나 연한 커피 맛이 나 운동 중 마시기 좋음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 옅은 커피 맛과 농도 — 1포 용량이 적어 진한 진도감을 원할 경우 2포 이상 타야 함</t>
+          <t>오프라인 판매 중단 아쉬움 — 오프라인 매장에서 구매하기 어려워진 점이 아쉬움</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5542,19 +5546,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>100% 유기농 레몬 원액 — 설탕이 들어가지 않은 순수 유기농 레몬이라 안심하고 복용함</t>
+          <t>상큼하고 풍부한 맛 — 상큼한 레몬 맛으로 물에 타서 수시로 마시기 유용함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>떫지 않은 상쾌한 풍미 — 떫은 맛없이 상큼하여 물이나 탄산수에 타 마시면 상쾌함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>개별 포장의 가성비 — 1포씩 개별 포장되어 외출 시 휴대하기 편하고 가격도 저렴함</t>
-        </is>
-      </c>
+          <t>저렴한 구매 가격 — 유기농 레몬즙을 저렴한 가격에 가성비 있게 구매함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -5915,69 +5915,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>운동 시 에너지를 제공 — 러닝이나 운동 전에 먹으면 지치지 않고 힘이 유지됨
-맛과 휴대성의 유용함 — 맛이 좋고 가볍게 챙겨 먹기 좋은 스틱 형태로 구성됨</t>
+          <t>우수한 체력 보충 — 운동이나 라이딩, 야외 활동 시 피로 회복에 효과적임
+착한 가성비 — 다이소 판매 제품으로 저렴한 가격에 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 약국 대비 부담 없는 가격으로 고함량 비타민B를 구매 가능함
-피로 개선 및 구내염 완화 — 복용 후 피로감이 줄고 혓바늘이 줄어드는 효과를 봄
-편리한 휴대 및 복용 — 포장이 간편하여 상시 휴대하며 복용하기 좋음</t>
+          <t>부담 없는 가격의 비타민 — 저렴한 가격으로 필수 영양소인 비타민B를 챙길 수 있음
+높은 재구매 만족도 — 지속적으로 꾸준히 재구매하여 섭취할 정도로 만족함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>검증된 제약사의 가성비 — 유명 브랜드 제품을 저렴하게 구매할 수 있어 만족도가 높음
-혈압 및 활력 케어 효과 — 100mg의 코큐텐 함량으로 혈압 조절과 활력 유지에 도움 됨</t>
+          <t>뛰어난 가성비와 성분 — 저렴한 가격 대비 코큐텐 함량과 품질이 뛰어남
+간편한 복용과 빠른 배송 — 복용하기 편하며 주문 후 배송이 빠름</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 외관 디자인 — 패키지 케이스가 은은하게 반짝여 선물용으로도 손색없음
-합리적이고 착한 가격 — 품질 대비 가격이 저렴하여 부담 없이 구매 가능함</t>
+          <t>고급스러운 패키지 디자인 — 은은하게 반짝이는 고급스러운 포장으로 선물용에 적합함
+합리적인 구매 가격 — 침향환을 부담 없는 합리적인 가격대로 구매 가능함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 작은 캡슐 — 캡슐 크기가 작고 부드러워 목넘김이 용이함
-눈의 피로 및 건조함 완화 — 컴퓨터나 스마트폰 사용 후 느껴지는 눈의 뻑뻑함과 피로가 줄어듦
-부담 없는 가성비 한 달 분량 — 루테인 권장량을 3천원대의 저렴한 가격으로 챙길 수 있음</t>
+          <t>작은 알약 크기 — 정제 크기가 작아서 목넘김이 편하고 삼키기 쉬움
+부담 없는 가성비 — 컴퓨터 작업으로 피로한 눈 관리를 저렴하게 시작할 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>신속한 전해질 및 수분 충전 — 땀을 많이 흘린 후 음용 시 수분과 전해질이 빠르게 보충됨
-은은한 자몽 향의 편의성 — 자몽 향이 은은하게 퍼져 맹물보다 편하게 물을 많이 마실 수 있음
-붓기 완화 및 대사 도움 — 칼륨과 식이섬유 배합으로 얼굴 붓기 제거 및 순환에 유용함</t>
+          <t>맛있는 이온음료 맛 — 포카리스웨트와 유사한 맛이 나 탄산음료 대신 마시기 좋음
+간편한 물 섭취 방식 — 분말을 물에 타서 간단하게 음용할 수 있음
+나트륨 배출 및 붓기 관리 — 짜게 먹는 습관이 있거나 자주 붓는 경우 관리하기 유용함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>작은 크기로 편한 목넘김 — 알약 크기가 작아서 복용할 때 삼키기 편함
-식전 복용 시 혈당 케어 — 식사 전 복용하면 식후 혈당 스파이크를 잡는 데 도움이 됨
-부담 없는 가성비 가격 — 저렴한 가격으로 식후 혈당 관리 영양제를 시도할 수 있음</t>
+          <t>편안한 목넘김 — 알약 크기가 크지 않아 섭취하기에 부담이 없음
+식후 혈당 가성비 관리 — 식후 혈당 관리를 저렴한 가격으로 꾸준히 하기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>올리브오일과 레몬의 조합 — 오일 캡슐과 레몬즙을 개별 포장하여 공복에 한 번에 먹기 편함
-원활한 배변 및 속 편함 — 아침 공복 복용 시 장 건강과 배변 활동에 유용한 효과를 봄
-휴대가 용이한 포장 용기 — 병 패키징이 야무지고 개별 포장되어 출근 시 챙겨가기 용이함</t>
+          <t>간편한 포장 및 복용 — 올리브오일과 레몬 조합을 낱개로 간편하게 먹을 수 있음
+저렴한 유행 제품 체험 — 유행하는 오일 레몬 조합을 저렴한 가격에 경험 가능함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>깔끔한 커피 대용 맛 — 씁쓸함이 적고 깔끔하여 부담 없이 아메리카노 대용으로 마시기 좋음
-원활한 배변 활동 촉진 — 꾸준히 마시면 배변 활동이 원활해지고 몸이 가벼워지는 느낌을 받음
-찬물에도 잘 녹는 편의성 — 스틱 타입이라 휴대가 편리하고 찬물에도 쉽게 잘 녹음</t>
+          <t>압도적인 가성비 — 10포 구성을 매우 저렴한 가격으로 구매할 수 있음
+연하고 구수한 맛 — 보리차나 연한 커피 맛이 나 운동 중 마시기 좋음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>100% 유기농 레몬 원액 — 설탕이 들어가지 않은 순수 유기농 레몬이라 안심하고 복용함
-떫지 않은 상쾌한 풍미 — 떫은 맛없이 상큼하여 물이나 탄산수에 타 마시면 상쾌함
-개별 포장의 가성비 — 1포씩 개별 포장되어 외출 시 휴대하기 편하고 가격도 저렴함</t>
+          <t>상큼하고 풍부한 맛 — 상큼한 레몬 맛으로 물에 타서 수시로 마시기 유용함
+저렴한 구매 가격 — 유기농 레몬즙을 저렴한 가격에 가성비 있게 구매함</t>
         </is>
       </c>
     </row>
@@ -5988,36 +5982,32 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>야간 복용 시 수면 영향 — 저녁 식후 복용할 경우 활력 증가로 수면에 방해가 될 수 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>효과 체감의 개인차 — 섭취 후 피로 개선 등의 신체적 효과를 크게 느끼지 못함</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>단일 루테인 위주의 성분 — 지아잔틴이나 아스타잔틴 성분은 별도로 함유되어 있지 않음</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>시중 이온음료 대비 옅은 맛 — 기존 포카리스웨트 등 음료에 비해 맛이 다소 밍밍하게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>단기 복용 시 미미한 효과 — 복용 초반에는 눈 피로 개선 효과가 눈에 띄지 않음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과의 개인차 — 개인에 따라 식후 졸음 개선이나 효과를 즉각 체감하기 어려움</t>
+          <t>체감 효능 미흡 — 섭취 후 신체 변화나 효능이 크게 느껴지지 않음</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛에 대한 호불호 — 동봉된 레몬즙의 신맛이 시큼하여 잘 못 먹는 경우 부담될 수 있음</t>
+          <t>효과 체감의 부족 — 섭취 후 신체적인 변화나 효과를 체감하기 어려움</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 옅은 커피 맛과 농도 — 1포 용량이 적어 진한 진도감을 원할 경우 2포 이상 타야 함</t>
+          <t>오프라인 판매 중단 아쉬움 — 오프라인 매장에서 구매하기 어려워진 점이 아쉬움</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -6293,12 +6283,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2개월 대용량 기획 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉하게 섭취할 수 있음</t>
+          <t>1일 1캡슐 간편 케어 — 하루 한 알 섭취로 여성 건강 및 장 건강을 관리함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>하루 한 알의 간편한 케어 — 하루 한 캡슐을 물과 함께 먹으면 되어 매일의 루틴으로 용이함</t>
+          <t>알찬 기획 및 증정품 — 2개월분 용량에 포토카드 등 증정 혜택 만족도가 높음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -6348,16 +6338,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>부담 없는 구미 형태 — 알약 대신 젤리 형태로 되어 있어 맛있고 부담 없이 먹을 수 있음</t>
+          <t>맛있는 구미 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간편하게 먹기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>수면 유도 및 숙면 도움 — 식물성 멜라토닌 성분으로 뒤척임 없이 깊은 잠에 들도록 도움</t>
+          <t>빠른 입면과 숙면 도움 — 자기 전 복용 시 잠이 잘 들고 숙면을 취할 수 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>취침 전 재양치 번거로움 — 자기 직전 젤리 섭취 후 양치를 다시 해야 하는 불편함이 있음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -6403,12 +6397,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>장 건강과 체지방 관리 — 체지방 감소와 장 건강을 동시에 관리하는 이중기능성 제품임</t>
+          <t>체지방과 장 건강 동시 케어 — 체지방 감소와 장 케어를 함께 할 수 있는 이중 기능성 제품임</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>맛있는 요거트 풍미 — 상큼한 요거트 맛이라 하루 한 포씩 부담 없이 먹기 좋음</t>
+          <t>상큼한 요거트 맛 — 맛있는 요거트 맛으로 하루 한 포씩 즐겁게 챙겨 먹음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -6458,12 +6452,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1+1 기획의 알찬 혜택 — 1+1 기획 구성과 증정품 제공으로 가성비 높게 구매 가능함</t>
+          <t>풍성한 1+1 기획 구성 — 더블 기획으로 2달 동안 넉넉하게 복용할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>장 건강 및 면역 케어 — 공복 복용으로 장 환경을 개선하고 면역력을 관리하는 데 적합함</t>
+          <t>아침 공복 장 건강 케어 — 아침 빈속에 섭취하여 장 면역과 장 건강을 유지함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6513,18 +6507,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>고함량 비타민C 섭취 — 1000mg 고함량 구성으로 피로를 줄이고 컨디션을 끌어올려 줌</t>
+          <t>고함량 비타민C 보충 — 고함량 섭취를 통해 피로감을 줄이고 컨디션을 유지함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>높은 브랜드 신뢰성 — 대한민국 대표 비타민 브랜드 제품으로 안심하고 구매함</t>
+          <t>4개월분 대용량 가성비 — 넉넉한 용량으로 오랫동안 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>섭취 시 강한 신맛 — 고함량 비타민C 특성상 신맛이 강하게 느껴질 수 있음</t>
+          <t>강한 신맛과 수분 필요 — 알약의 신맛이 강하며 섭취 시 충분한 물 마심이 필요함</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -6572,12 +6566,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>비타민 C와 D의 결합 — 비타민C와 비타민D를 한 번에 복용 가능하여 관리가 효율적임</t>
+          <t>비타민 C와 D 올인원 — 항산화 비타민C와 실내 생활 필수 비타민D를 한 번에 섭취함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>면역 및 건강 유지 효과 — 실내 생활에 부족한 비타민D와 면역 케어 비타민C를 동시에 보충함</t>
+          <t>귀여운 산리오 파우치 증정 — 마이멜로디 파우치가 동봉되어 소장 가치가 높음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -6623,21 +6617,21 @@
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>17520</v>
+        <v>17521</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가성비 — 커피 한 잔 가격 수준의 저렴함으로 지속적인 구매가 용이함</t>
+          <t>압도적인 가성비 — 타사 제품 대비 가격이 매우 저렴하여 부담이 적음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>비린내 없는 부드러운 삼킴 — 캡슐 크기가 적당하고 비린내가 느껴지지 않아 먹기 편함</t>
+          <t>비린내 없는 편안함 — 오메가3 특유의 비린내가 적고 캡슐 크기가 적당함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>위생적인 개별 낱개 포장 — 개별 포장되어 있어 들고 다니기 쉽고 보관이 위생적임</t>
+          <t>위생적인 PTP 개별 포장 — 개별 포장되어 있어 휴대와 보관이 유용함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -6686,12 +6680,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>복통 없는 배변 개선 — 배 아픔 없이 화장실을 원활하고 상쾌하게 가도록 도와줌</t>
+          <t>속 편한 배변 활동 도움 — 복통이나 가스 차는 현상 없이 편안하게 화장실을 감</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>피부와 장의 동시 케어 — 장 건강과 더불어 피부 면역을 관리하는 데 도움을 줌</t>
+          <t>귀여운 산리오 러기지택 — 산리오 콜라보 굿즈 증정으로 기획 만족도가 높음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6741,16 +6735,20 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>맛있는 구미 형태의 제형 — 상큼하고 맛있는 과일 맛 젤리 타입이라 간식처럼 먹기 좋음</t>
+          <t>확실한 수면 유도 효과 — 자기 전 복용 시 새벽에 깨지 않고 빠르게 잠에 듦</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>수면 질 개선 및 숙면 — 새벽에 깨지 않고 빠른 수면에 들도록 돕는 효과가 있음</t>
+          <t>식물성 성분의 맛있는 구미 — 식물성 멜라토닌 성분이며 상큼한 과일 맛 젤리로 먹기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>취침 전 양치 재실행 번거로움 — 잠들기 전 젤리를 먹은 뒤 양치를 다시 해야 하는 불편함이 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -6796,12 +6794,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>신속한 배변 반응 및 변비 완화 — 섭취 후 빠르게 신호가 오며 만성 변비 개선에 뛰어남</t>
+          <t>빠른 숙변 해소 및 장 상쾌함 — 복용 후 신호가 빠르게 와서 만성 변비 해소에 효과적임</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>체지방 및 아랫배 관리 — 지속 복용 시 체지방 감량과 아랫배 관리 느낌을 받음</t>
+          <t>귀여운 콜라보 굿즈 — 산리오 캐릭터 카라비너 증정으로 소장 욕구를 높임</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -7145,7 +7143,7 @@
         <v>15342</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>17520</v>
+        <v>17521</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>12312</v>
@@ -7165,63 +7163,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2개월 대용량 기획 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉하게 섭취할 수 있음
-하루 한 알의 간편한 케어 — 하루 한 캡슐을 물과 함께 먹으면 되어 매일의 루틴으로 용이함</t>
+          <t>1일 1캡슐 간편 케어 — 하루 한 알 섭취로 여성 건강 및 장 건강을 관리함
+알찬 기획 및 증정품 — 2개월분 용량에 포토카드 등 증정 혜택 만족도가 높음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 구미 형태 — 알약 대신 젤리 형태로 되어 있어 맛있고 부담 없이 먹을 수 있음
-수면 유도 및 숙면 도움 — 식물성 멜라토닌 성분으로 뒤척임 없이 깊은 잠에 들도록 도움</t>
+          <t>맛있는 구미 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간편하게 먹기 좋음
+빠른 입면과 숙면 도움 — 자기 전 복용 시 잠이 잘 들고 숙면을 취할 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>장 건강과 체지방 관리 — 체지방 감소와 장 건강을 동시에 관리하는 이중기능성 제품임
-맛있는 요거트 풍미 — 상큼한 요거트 맛이라 하루 한 포씩 부담 없이 먹기 좋음</t>
+          <t>체지방과 장 건강 동시 케어 — 체지방 감소와 장 케어를 함께 할 수 있는 이중 기능성 제품임
+상큼한 요거트 맛 — 맛있는 요거트 맛으로 하루 한 포씩 즐겁게 챙겨 먹음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>1+1 기획의 알찬 혜택 — 1+1 기획 구성과 증정품 제공으로 가성비 높게 구매 가능함
-장 건강 및 면역 케어 — 공복 복용으로 장 환경을 개선하고 면역력을 관리하는 데 적합함</t>
+          <t>풍성한 1+1 기획 구성 — 더블 기획으로 2달 동안 넉넉하게 복용할 수 있음
+아침 공복 장 건강 케어 — 아침 빈속에 섭취하여 장 면역과 장 건강을 유지함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 섭취 — 1000mg 고함량 구성으로 피로를 줄이고 컨디션을 끌어올려 줌
-높은 브랜드 신뢰성 — 대한민국 대표 비타민 브랜드 제품으로 안심하고 구매함</t>
+          <t>고함량 비타민C 보충 — 고함량 섭취를 통해 피로감을 줄이고 컨디션을 유지함
+4개월분 대용량 가성비 — 넉넉한 용량으로 오랫동안 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>비타민 C와 D의 결합 — 비타민C와 비타민D를 한 번에 복용 가능하여 관리가 효율적임
-면역 및 건강 유지 효과 — 실내 생활에 부족한 비타민D와 면역 케어 비타민C를 동시에 보충함</t>
+          <t>비타민 C와 D 올인원 — 항산화 비타민C와 실내 생활 필수 비타민D를 한 번에 섭취함
+귀여운 산리오 파우치 증정 — 마이멜로디 파우치가 동봉되어 소장 가치가 높음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가성비 — 커피 한 잔 가격 수준의 저렴함으로 지속적인 구매가 용이함
-비린내 없는 부드러운 삼킴 — 캡슐 크기가 적당하고 비린내가 느껴지지 않아 먹기 편함
-위생적인 개별 낱개 포장 — 개별 포장되어 있어 들고 다니기 쉽고 보관이 위생적임</t>
+          <t>압도적인 가성비 — 타사 제품 대비 가격이 매우 저렴하여 부담이 적음
+비린내 없는 편안함 — 오메가3 특유의 비린내가 적고 캡슐 크기가 적당함
+위생적인 PTP 개별 포장 — 개별 포장되어 있어 휴대와 보관이 유용함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>복통 없는 배변 개선 — 배 아픔 없이 화장실을 원활하고 상쾌하게 가도록 도와줌
-피부와 장의 동시 케어 — 장 건강과 더불어 피부 면역을 관리하는 데 도움을 줌</t>
+          <t>속 편한 배변 활동 도움 — 복통이나 가스 차는 현상 없이 편안하게 화장실을 감
+귀여운 산리오 러기지택 — 산리오 콜라보 굿즈 증정으로 기획 만족도가 높음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 형태의 제형 — 상큼하고 맛있는 과일 맛 젤리 타입이라 간식처럼 먹기 좋음
-수면 질 개선 및 숙면 — 새벽에 깨지 않고 빠른 수면에 들도록 돕는 효과가 있음</t>
+          <t>확실한 수면 유도 효과 — 자기 전 복용 시 새벽에 깨지 않고 빠르게 잠에 듦
+식물성 성분의 맛있는 구미 — 식물성 멜라토닌 성분이며 상큼한 과일 맛 젤리로 먹기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>신속한 배변 반응 및 변비 완화 — 섭취 후 빠르게 신호가 오며 만성 변비 개선에 뛰어남
-체지방 및 아랫배 관리 — 지속 복용 시 체지방 감량과 아랫배 관리 느낌을 받음</t>
+          <t>빠른 숙변 해소 및 장 상쾌함 — 복용 후 신호가 빠르게 와서 만성 변비 해소에 효과적임
+귀여운 콜라보 굿즈 — 산리오 캐릭터 카라비너 증정으로 소장 욕구를 높임</t>
         </is>
       </c>
     </row>
@@ -7232,18 +7230,26 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 재양치 번거로움 — 자기 직전 젤리 섭취 후 양치를 다시 해야 하는 불편함이 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>섭취 시 강한 신맛 — 고함량 비타민C 특성상 신맛이 강하게 느껴질 수 있음</t>
+          <t>강한 신맛과 수분 필요 — 알약의 신맛이 강하며 섭취 시 충분한 물 마심이 필요함</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 양치 재실행 번거로움 — 잠들기 전 젤리를 먹은 뒤 양치를 다시 해야 하는 불편함이 있음</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7491,7 +7497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7513,7 +7519,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7579,7 +7585,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7589,10 +7595,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7601,7 +7607,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7611,10 +7617,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>

--- a/data/daily/2026-09/2026-09-09.xlsx
+++ b/data/daily/2026-09/2026-09-09.xlsx
@@ -1195,14 +1195,89 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1292,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,135 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,207 +1450,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>간편한 섭취와 맛있는 풍미 — 액상과 정제로 구성되어 간편하게 먹을 수 있으며 맛이 양호함</t>
+          <t>활력 증진 및 체력 회복 — 육아나 피로 누적 시 빠른 체력 충전에 도움 됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 회복 — 회식 다음 날이나 육아, 업무로 지쳤을 때 활력을 도둠</t>
+          <t>선물용으로 높은 만족도 — 받는 사람의 기분을 좋게 만드는 우수한 선물임</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 받는 사람의 건강을 챙겨줄 수 있어 선물용으로 반응이 좋음</t>
+          <t>맛있고 간편한 복용법 — 맛이 우수하고 간편하게 섭취하기 편함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>배송 지연 및 사은품 누락 — 배송 처리가 느리고 안내된 사은품이 동봉되지 않음</t>
+          <t>배송 지연 및 사은품 누락 — 배송 속도가 느리고 사은품이 함께 오지 않음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2659,21 +2659,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15335</v>
+        <v>15337</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>물 없는 간편한 섭취 — 상단 정제와 하단 액상을 물 없이 한 번에 복용할 수 있음</t>
+          <t>물 없이 간편한 섭취 — 액상과 알약 일체형으로 물 없이 바로 복용 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 매일 한 병씩 복용 시 피로가 풀리고 기운이 나는 효과가 있음</t>
+          <t>빠른 피로 회복 효과 — 복용 후 에너지가 충전되고 활력이 생김</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>우수한 가성비와 선물 활용성 — 남녀노소 누구에게나 선물하기 좋으며 가성비가 뛰어남</t>
+          <t>선물용 우수한 가성비 — 가격 대비 알찬 구성으로 선물하기에 좋음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2722,22 +2722,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>우수한 피로 개선 효과 — 하루 종일 일해도 아침에 가뿐하며 피로감이 줄어듦</t>
+          <t>아침 피로 개선 효과 — 복용 후 피로감이 줄고 아침에 몸이 가벼워짐</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 구성 — 포장 상태가 고급스러워 생일이나 응원 선물로 적합함</t>
+          <t>고급스러운 패키지 포장 — 포장 상태가 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>부담 없는 섭취 방식 — 맛이 좋고 먹기 편해 꾸준히 챙겨 먹기 적합함</t>
+          <t>편리하고 맛있는 복용 — 맛이 좋아 거부감 없이 편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>당뇨 환자의 섭취 주의 — 당 성분 함유로 인해 당뇨 질환자의 복용 시 주의가 필요함</t>
+          <t>당뇨 환자의 복용 제약 — 당 성분이나 특성상 당뇨 환자가 직접 섭취하기 어려움</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2785,29 +2785,21 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 상큼한 맛과 식감으로 부담 없는 건강 간식처럼 먹기 좋음</t>
+          <t>맛있는 젤리 제형 — 맛과 식감이 좋아 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>귀여운 포장과 굿즈 증정 — 선물 포장이 귀엽고 함께 증정되는 키캡 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>일상 속 활력 충전 — 지친 몸에 영양을 공급하여 기분 전환과 활력에 도움 됨</t>
-        </is>
-      </c>
+          <t>센스 있는 사은품 구성 — 키캡 등 귀여운 굿즈가 동봉되어 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>다소 단단한 젤리 식감 — 젤리가 완전히 말랑하지 않아 식감에 대한 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>키캡 굿즈 로고 표기 — 동봉된 키캡 뒷면에 브랜드 로고가 표기되어 아쉬움</t>
-        </is>
-      </c>
+          <t>다소 딱딱한 젤리 식감 — 젤리가 조금 더 말랑했으면 하는 아쉬움이 있음</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -2848,21 +2840,21 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>8687</v>
+        <v>8688</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>높은 휴대성과 편의성 — 가방에 쏙 들어가는 크기라 외출 시에도 챙겨 마시기 편함</t>
+          <t>우수한 휴대성과 편의성 — 가방에 쏙 들어가는 크기로 외출 시 휴대하기 용이함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>빠른 체력 회복 체감 — 피로감이 심할 때 먹으면 체력이 보충되는 느낌을 받음</t>
+          <t>합리적 가격과 빠른 배송 — 가격이 저렴하고 배송이 빠름</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>합리적인 가격과 빠른 배송 — 배송이 신속하며 부담 없는 가격대로 구매할 수 있음</t>
+          <t>피로 회복 및 기운 충전 — 지치고 힘들 때 복용하면 체력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2907,21 +2899,21 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>넉넉한 30병 구성 — 수량이 넉넉하여 출근이나 운동 시 오래 챙겨 먹기 좋음</t>
+          <t>휴대하기 용이한 용기 — 낱개 포장으로 간편하게 들고 다니며 마시기 편함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>거부감 없는 맛과 향 — 향과 맛에 부담이 없어 아이들도 거부감 없이 잘 마심</t>
+          <t>거부감 없는 맛과 향 — 청소년도 잘 먹을 정도로 향과 맛이 무난함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 증정 — 쇼핑백이 함께 포함되어 생일이나 명절 선물용으로 적합함</t>
+          <t>넉넉한 30병 구성 — 수량이 많아 오랫동안 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2966,21 +2958,21 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>신속한 체력 회복 도움 — 수술 후 회복기나 피로가 누적되었을 때 기운을 북돋아 줌</t>
+          <t>예쁜 선물 포장 구성 — 선물용 포장이 정성스럽고 깔끔함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>부담 없는 선물용 영양제 — 지인이나 친구에게 부담 없이 건강을 선물하기 좋음</t>
+          <t>빠른 수술 후 체력 회복 — 체력이 떨어지거나 수술 후 회복 시 도움을 줌</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>신속한 배송 서비스 — 주문 후 배송이 빠르고 안전하게 도착함</t>
+          <t>간편한 복용과 빠른 배송 — 배송이 빠르고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3029,17 +3021,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>신선한 액상 분말 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시므로 신선함</t>
+          <t>신선한 이중 섞음 용기 — 버튼을 눌러 분말과 액상을 직접 섞어 마셔 신선함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지가 예쁘고 고급스러워 축하 및 응원 선물로 뛰어남</t>
+          <t>고급스러운 포장 디자인 — 패키지 포장이 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>맛있는 영양 보충 — 음료처럼 맛이 좋아 하루 한 병씩 부담 없이 비타민을 챙김</t>
+          <t>맛있는 음료 제형 — 음료수처럼 맛이 좋아 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3088,22 +3080,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 액상 제형으로 피로할 때 마시면 부스터처럼 즉각 피로가 풀림</t>
+          <t>빠른 피로 회복 체감 — 액상 제형으로 복용 즉시 피로 회복이 체감됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>안정적인 패키지 포장 — 내부 홈에 앰플이 딱 고정되어 안전하게 배송됨</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>간편한 일상 영양 섭취 — 하루 한 개씩 개별 휴대하며 챙겨 먹기 편함</t>
-        </is>
-      </c>
+          <t>선물하기 좋은 패키지 — 제품 고정이 잘 되어 있고 패키지가 고급스러움</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>적은 수량 구성 — 1박스 5입 구성이라 지속 복용 시 수량이 부족하게 느껴짐</t>
+          <t>다소 비싼 가격대 — 가격이 저렴한 편은 아니라 약간의 부담이 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3151,17 +3139,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 멀티 케어 — 필요한 영양소를 한 번에 케어할 수 있어 피로함이 줄어듦</t>
+          <t>뛰어난 휴대성과 편의성 — 하루 하나씩 챙겨 다니며 복용하기 용이함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 포장과 디자인 — 깔끔한 선물 포장과 디자인으로 정성스러움이 전달됨</t>
+          <t>정성스러운 포장 품질 — 디자인과 포장이 정성스러워 선물의 가치가 높음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 하루에 하나씩 가방에 넣어 다니며 복용하기 용이함</t>
+          <t>올인원 영양 케어 — 필요 영양소를 한 번에 섭취하여 피로감이 줄어듦</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3257,22 +3245,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 구성 — 24개입 구성을 매우 합리적인 가격으로 구매 가능함</t>
+          <t>저렴한 대용량 가성비 — 구성 대비 가격이 매우 저렴함</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>다양한 맛과 부드러운 식감 — 뻑뻑함이 적고 맛이 다채로워 매일 먹어도 질리지 않음</t>
+          <t>물리지 않는 다양한 맛 — 여러 가지 양념 맛으로 매일 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>전자레인지 간편 조리 — 전자레인지로 빠르게 조리할 수 있어 다이어트 식단에 적합함</t>
+          <t>꼼꼼한 포장과 빠른 배송 — 배송이 빠르고 포장 상태가 양호함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
+          <t>배송 중 제품 해동 문제 — 배송 과정에서 제품이 녹아서 도착함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3320,24 +3308,20 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스러운 에디션 포장 — 은은한 핑크 포장과 패키지가 고급스러워 선물용으로 훌륭함</t>
+          <t>고급스러운 선물 포장 — 포장 상태가 매우 예쁘고 고급스러움</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>피부 상태 개선 체감 — 꾸준히 복용 시 피부가 맑아지는 느낌을 받음</t>
+          <t>피부 개선 및 체감 효과 — 꾸준히 먹으면 피부가 맑아지는 느낌이 듦</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>추가 앰플 및 샘플 증정 — 추가 앰플 증정 및 샘플 구성이 알차 만족스러움</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>단기 복용 시 효과 미체감 — 복용 초반에는 즉각적인 효과를 확인하기 어려움</t>
-        </is>
-      </c>
+          <t>알찬 증정품 구성 — 추가 앰플과 샘플 증정이 있어 만족스러움</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3383,29 +3367,21 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>다채로운 맛과 뛰어난 풍미 — 다양한 맛으로 구성되어 골라 먹기 좋고 맛이 우수함</t>
+          <t>우수한 구성과 가성비 — 30팩 대용량 수량에 보냉백까지 사은품으로 제공됨</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>저렴한 한 달 식단 패키지 — 30팩 구성을 저렴하게 구매할 수 있어 가격 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>사은품 보냉백의 활용성 — 증정되는 보냉백으로 도시락 휴대가 용이함</t>
-        </is>
-      </c>
+          <t>골라 먹는 다양한 맛 — 종류가 다채롭고 맛있어서 식단 관리에 유용함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 여름철 배송 시 내용물이 많이 녹아서 전달됨</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>증정 사은품 누락 우려 — 보냉백 등의 증정품이 동봉되지 않거나 배송이 지연됨</t>
-        </is>
-      </c>
+          <t>제품 해동 배송 상태 — 배송 중 닭가슴살이 녹아서 오는 경우가 있음</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
@@ -3450,17 +3426,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함과 비린 맛이 없어 마시기 편함</t>
+          <t>비린 맛 없는 부드러움 — 단백질 음료 특유의 텁텁함과 비린 맛이 없음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>속 편한 분리유청 성분 — 마신 뒤 더부룩함이나 속 불편함 없이 깔끔하게 소화됨</t>
+          <t>속 편한 저당 영양 설계 — 당 함량이 낮고 마신 후 속 더부룩함이 없음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>간편한 운동 후 단백질 보충 — 슬림한 패키지로 휴대성이 좋고 당과 칼로리 부담이 적음</t>
+          <t>편리한 휴대용 패키지 — 슬림한 용기로 들고 다니며 간식 대용으로 먹기 좋음</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3509,17 +3485,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>식후 더부룩함 개선 — 고기나 밀가루 섭취 후 복용 시 답답한 속이 한결 편안해짐</t>
+          <t>고소한 군고구마 풍미 — 맛이 고소하고 부담스럽지 않음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>배변 활동 원활 — 꾸준히 복용하면 매일 원활한 배변 활동에 도움 됨</t>
+          <t>더부룩함 및 배변 개선 — 식후 속 답답함이 줄고 배변 활동에 도움 됨</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 거부감 없는 고소한 군고구마 맛으로 편하게 먹을 수 있음</t>
+          <t>풍성한 이벤트 사은품 — 가격 할인이 크고 사은품 혜택이 많음</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3564,21 +3540,21 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 꾸준히 먹으면 득근 및 세트 수행에 도움을 받음</t>
+          <t>운동 수행 능력 향상 — 운동 시 세트를 더 채울 수 있고 체감 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>음료와의 용해성 및 편의성 — 물이나 음료에 잘 타서 부담 없이 간편하게 섭취 가능함</t>
+          <t>물에 잘 녹는 복용 편의 — 물이나 음료에 섞어 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>귀여운 키링 증정 — 제품과 함께 제공되는 키링 사은품의 만족도가 높음</t>
+          <t>귀여운 증정 키링 — 동봉된 키링 사은품의 만족도가 높음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3627,17 +3603,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6,200mg 초고함량 활력 — 고함량 아르기닌으로 섭취 후 피로 회복과 활력이 뛰어남</t>
+          <t>초고함량 빠른 활력 충전 — 6,200mg 함량으로 운동 퍼포먼스 및 체력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>선물용 패키지 구성 — 고급스러운 포장과 쇼핑백, 추가 증정 5포로 선물에 적합함</t>
+          <t>고급스러운 포장과 구성 — 전용 쇼핑백과 추가 증정이 있어 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>휴대하기 편한 스틱 제형 — 개별 포장된 액상 스틱으로 언제 어디서나 1포씩 먹기 편함</t>
+          <t>간편한 1포 개별 포장 — 휴대성이 좋아 언제 어디서나 섭취하기 편함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3686,19 +3662,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 레몬맛 액상 제형이라 물에 타서 부담 없이 섭취 가능함</t>
+          <t>상큼한 레몬맛 액상 제형 — 레몬맛이라 부담 없고 물에 타서 마시기 편함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>운동 전후 및 아침 활력 — 아침 공복이나 운동 시 복용하면 하루 시작이 가벼워짐</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>응원 선물로 우수함 — 웨이트 트레이닝을 하거나 피로한 지인 선물로 만족도가 높음</t>
-        </is>
-      </c>
+          <t>공복 복용 시 피로 개선 — 아침 공복에 먹으면 하루 시작이 가벼워짐</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3745,7 +3717,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 음주 후 섭취 시 숙취 해소 효능이 매우 우수함</t>
+          <t>확실한 숙취 해소 효과 — 음주 후 복용 시 숙취 완화 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -4075,7 +4047,7 @@
         <v>15998</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15335</v>
+        <v>15337</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3342</v>
@@ -4084,13 +4056,13 @@
         <v>6449</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8687</v>
+        <v>8688</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1618</v>
@@ -4110,76 +4082,74 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>간편한 섭취와 맛있는 풍미 — 액상과 정제로 구성되어 간편하게 먹을 수 있으며 맛이 양호함
-체력 증진 및 피로 회복 — 회식 다음 날이나 육아, 업무로 지쳤을 때 활력을 도둠
-선물용으로 높은 만족도 — 받는 사람의 건강을 챙겨줄 수 있어 선물용으로 반응이 좋음</t>
+          <t>활력 증진 및 체력 회복 — 육아나 피로 누적 시 빠른 체력 충전에 도움 됨
+선물용으로 높은 만족도 — 받는 사람의 기분을 좋게 만드는 우수한 선물임
+맛있고 간편한 복용법 — 맛이 우수하고 간편하게 섭취하기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>물 없는 간편한 섭취 — 상단 정제와 하단 액상을 물 없이 한 번에 복용할 수 있음
-확실한 피로 회복 체감 — 매일 한 병씩 복용 시 피로가 풀리고 기운이 나는 효과가 있음
-우수한 가성비와 선물 활용성 — 남녀노소 누구에게나 선물하기 좋으며 가성비가 뛰어남</t>
+          <t>물 없이 간편한 섭취 — 액상과 알약 일체형으로 물 없이 바로 복용 가능함
+빠른 피로 회복 효과 — 복용 후 에너지가 충전되고 활력이 생김
+선물용 우수한 가성비 — 가격 대비 알찬 구성으로 선물하기에 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 개선 효과 — 하루 종일 일해도 아침에 가뿐하며 피로감이 줄어듦
-고급스러운 포장과 구성 — 포장 상태가 고급스러워 생일이나 응원 선물로 적합함
-부담 없는 섭취 방식 — 맛이 좋고 먹기 편해 꾸준히 챙겨 먹기 적합함</t>
+          <t>아침 피로 개선 효과 — 복용 후 피로감이 줄고 아침에 몸이 가벼워짐
+고급스러운 패키지 포장 — 포장 상태가 고급스러워 선물용으로 적합함
+편리하고 맛있는 복용 — 맛이 좋아 거부감 없이 편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 상큼한 맛과 식감으로 부담 없는 건강 간식처럼 먹기 좋음
-귀여운 포장과 굿즈 증정 — 선물 포장이 귀엽고 함께 증정되는 키캡 만족도가 높음
-일상 속 활력 충전 — 지친 몸에 영양을 공급하여 기분 전환과 활력에 도움 됨</t>
+          <t>맛있는 젤리 제형 — 맛과 식감이 좋아 부담 없이 섭취 가능함
+센스 있는 사은품 구성 — 키캡 등 귀여운 굿즈가 동봉되어 만족도가 높음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>높은 휴대성과 편의성 — 가방에 쏙 들어가는 크기라 외출 시에도 챙겨 마시기 편함
-빠른 체력 회복 체감 — 피로감이 심할 때 먹으면 체력이 보충되는 느낌을 받음
-합리적인 가격과 빠른 배송 — 배송이 신속하며 부담 없는 가격대로 구매할 수 있음</t>
+          <t>우수한 휴대성과 편의성 — 가방에 쏙 들어가는 크기로 외출 시 휴대하기 용이함
+합리적 가격과 빠른 배송 — 가격이 저렴하고 배송이 빠름
+피로 회복 및 기운 충전 — 지치고 힘들 때 복용하면 체력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>넉넉한 30병 구성 — 수량이 넉넉하여 출근이나 운동 시 오래 챙겨 먹기 좋음
-거부감 없는 맛과 향 — 향과 맛에 부담이 없어 아이들도 거부감 없이 잘 마심
-선물용 쇼핑백 증정 — 쇼핑백이 함께 포함되어 생일이나 명절 선물용으로 적합함</t>
+          <t>휴대하기 용이한 용기 — 낱개 포장으로 간편하게 들고 다니며 마시기 편함
+거부감 없는 맛과 향 — 청소년도 잘 먹을 정도로 향과 맛이 무난함
+넉넉한 30병 구성 — 수량이 많아 오랫동안 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>신속한 체력 회복 도움 — 수술 후 회복기나 피로가 누적되었을 때 기운을 북돋아 줌
-부담 없는 선물용 영양제 — 지인이나 친구에게 부담 없이 건강을 선물하기 좋음
-신속한 배송 서비스 — 주문 후 배송이 빠르고 안전하게 도착함</t>
+          <t>예쁜 선물 포장 구성 — 선물용 포장이 정성스럽고 깔끔함
+빠른 수술 후 체력 회복 — 체력이 떨어지거나 수술 후 회복 시 도움을 줌
+간편한 복용과 빠른 배송 — 배송이 빠르고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>신선한 액상 분말 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시므로 신선함
-고급스러운 포장 디자인 — 패키지가 예쁘고 고급스러워 축하 및 응원 선물로 뛰어남
-맛있는 영양 보충 — 음료처럼 맛이 좋아 하루 한 병씩 부담 없이 비타민을 챙김</t>
+          <t>신선한 이중 섞음 용기 — 버튼을 눌러 분말과 액상을 직접 섞어 마셔 신선함
+고급스러운 포장 디자인 — 패키지 포장이 고급스러워 선물용으로 제격임
+맛있는 음료 제형 — 음료수처럼 맛이 좋아 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 액상 제형으로 피로할 때 마시면 부스터처럼 즉각 피로가 풀림
-안정적인 패키지 포장 — 내부 홈에 앰플이 딱 고정되어 안전하게 배송됨
-간편한 일상 영양 섭취 — 하루 한 개씩 개별 휴대하며 챙겨 먹기 편함</t>
+          <t>빠른 피로 회복 체감 — 액상 제형으로 복용 즉시 피로 회복이 체감됨
+선물하기 좋은 패키지 — 제품 고정이 잘 되어 있고 패키지가 고급스러움</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 멀티 케어 — 필요한 영양소를 한 번에 케어할 수 있어 피로함이 줄어듦
-우수한 포장과 디자인 — 깔끔한 선물 포장과 디자인으로 정성스러움이 전달됨
-편리한 휴대성 — 하루에 하나씩 가방에 넣어 다니며 복용하기 용이함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>뛰어난 휴대성과 편의성 — 하루 하나씩 챙겨 다니며 복용하기 용이함
+정성스러운 포장 품질 — 디자인과 포장이 정성스러워 선물의 가치가 높음
+올인원 영양 케어 — 필요 영양소를 한 번에 섭취하여 피로감이 줄어듦</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4187,19 +4157,18 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>배송 지연 및 사은품 누락 — 배송 처리가 느리고 안내된 사은품이 동봉되지 않음</t>
+          <t>배송 지연 및 사은품 누락 — 배송 속도가 느리고 사은품이 함께 오지 않음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>당뇨 환자의 섭취 주의 — 당 성분 함유로 인해 당뇨 질환자의 복용 시 주의가 필요함</t>
+          <t>당뇨 환자의 복용 제약 — 당 성분이나 특성상 당뇨 환자가 직접 섭취하기 어려움</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>다소 단단한 젤리 식감 — 젤리가 완전히 말랑하지 않아 식감에 대한 아쉬움이 있음
-키캡 굿즈 로고 표기 — 동봉된 키캡 뒷면에 브랜드 로고가 표기되어 아쉬움</t>
+          <t>다소 딱딱한 젤리 식감 — 젤리가 조금 더 말랑했으면 하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4208,7 +4177,7 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>적은 수량 구성 — 1박스 5입 구성이라 지속 복용 시 수량이 부족하게 느껴짐</t>
+          <t>다소 비싼 가격대 — 가격이 저렴한 편은 아니라 약간의 부담이 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4634,7 +4603,7 @@
         <v>1653</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>247</v>
@@ -4655,67 +4624,65 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 구성 — 24개입 구성을 매우 합리적인 가격으로 구매 가능함
-다양한 맛과 부드러운 식감 — 뻑뻑함이 적고 맛이 다채로워 매일 먹어도 질리지 않음
-전자레인지 간편 조리 — 전자레인지로 빠르게 조리할 수 있어 다이어트 식단에 적합함</t>
+          <t>저렴한 대용량 가성비 — 구성 대비 가격이 매우 저렴함
+물리지 않는 다양한 맛 — 여러 가지 양념 맛으로 매일 먹기 좋음
+꼼꼼한 포장과 빠른 배송 — 배송이 빠르고 포장 상태가 양호함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 에디션 포장 — 은은한 핑크 포장과 패키지가 고급스러워 선물용으로 훌륭함
-피부 상태 개선 체감 — 꾸준히 복용 시 피부가 맑아지는 느낌을 받음
-추가 앰플 및 샘플 증정 — 추가 앰플 증정 및 샘플 구성이 알차 만족스러움</t>
+          <t>고급스러운 선물 포장 — 포장 상태가 매우 예쁘고 고급스러움
+피부 개선 및 체감 효과 — 꾸준히 먹으면 피부가 맑아지는 느낌이 듦
+알찬 증정품 구성 — 추가 앰플과 샘플 증정이 있어 만족스러움</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 맛과 뛰어난 풍미 — 다양한 맛으로 구성되어 골라 먹기 좋고 맛이 우수함
-저렴한 한 달 식단 패키지 — 30팩 구성을 저렴하게 구매할 수 있어 가격 만족도가 높음
-사은품 보냉백의 활용성 — 증정되는 보냉백으로 도시락 휴대가 용이함</t>
+          <t>우수한 구성과 가성비 — 30팩 대용량 수량에 보냉백까지 사은품으로 제공됨
+골라 먹는 다양한 맛 — 종류가 다채롭고 맛있어서 식단 관리에 유용함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함과 비린 맛이 없어 마시기 편함
-속 편한 분리유청 성분 — 마신 뒤 더부룩함이나 속 불편함 없이 깔끔하게 소화됨
-간편한 운동 후 단백질 보충 — 슬림한 패키지로 휴대성이 좋고 당과 칼로리 부담이 적음</t>
+          <t>비린 맛 없는 부드러움 — 단백질 음료 특유의 텁텁함과 비린 맛이 없음
+속 편한 저당 영양 설계 — 당 함량이 낮고 마신 후 속 더부룩함이 없음
+편리한 휴대용 패키지 — 슬림한 용기로 들고 다니며 간식 대용으로 먹기 좋음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>식후 더부룩함 개선 — 고기나 밀가루 섭취 후 복용 시 답답한 속이 한결 편안해짐
-배변 활동 원활 — 꾸준히 복용하면 매일 원활한 배변 활동에 도움 됨
-고소한 군고구마 맛 — 거부감 없는 고소한 군고구마 맛으로 편하게 먹을 수 있음</t>
+          <t>고소한 군고구마 풍미 — 맛이 고소하고 부담스럽지 않음
+더부룩함 및 배변 개선 — 식후 속 답답함이 줄고 배변 활동에 도움 됨
+풍성한 이벤트 사은품 — 가격 할인이 크고 사은품 혜택이 많음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 꾸준히 먹으면 득근 및 세트 수행에 도움을 받음
-음료와의 용해성 및 편의성 — 물이나 음료에 잘 타서 부담 없이 간편하게 섭취 가능함
-귀여운 키링 증정 — 제품과 함께 제공되는 키링 사은품의 만족도가 높음</t>
+          <t>운동 수행 능력 향상 — 운동 시 세트를 더 채울 수 있고 체감 효과가 뛰어남
+물에 잘 녹는 복용 편의 — 물이나 음료에 섞어 부담 없이 섭취 가능함
+귀여운 증정 키링 — 동봉된 키링 사은품의 만족도가 높음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>6,200mg 초고함량 활력 — 고함량 아르기닌으로 섭취 후 피로 회복과 활력이 뛰어남
-선물용 패키지 구성 — 고급스러운 포장과 쇼핑백, 추가 증정 5포로 선물에 적합함
-휴대하기 편한 스틱 제형 — 개별 포장된 액상 스틱으로 언제 어디서나 1포씩 먹기 편함</t>
+          <t>초고함량 빠른 활력 충전 — 6,200mg 함량으로 운동 퍼포먼스 및 체력 증진에 도움 됨
+고급스러운 포장과 구성 — 전용 쇼핑백과 추가 증정이 있어 선물용으로 훌륭함
+간편한 1포 개별 포장 — 휴대성이 좋아 언제 어디서나 섭취하기 편함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 레몬맛 액상 제형이라 물에 타서 부담 없이 섭취 가능함
-운동 전후 및 아침 활력 — 아침 공복이나 운동 시 복용하면 하루 시작이 가벼워짐
-응원 선물로 우수함 — 웨이트 트레이닝을 하거나 피로한 지인 선물로 만족도가 높음</t>
+          <t>상큼한 레몬맛 액상 제형 — 레몬맛이라 부담 없고 물에 타서 마시기 편함
+공복 복용 시 피로 개선 — 아침 공복에 먹으면 하루 시작이 가벼워짐</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 음주 후 섭취 시 숙취 해소 효능이 매우 우수함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>확실한 숙취 해소 효과 — 음주 후 복용 시 숙취 완화 효과가 뛰어남</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4724,18 +4691,13 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>단기 복용 시 효과 미체감 — 복용 초반에는 즉각적인 효과를 확인하기 어려움</t>
-        </is>
-      </c>
+          <t>배송 중 제품 해동 문제 — 배송 과정에서 제품이 녹아서 도착함</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 여름철 배송 시 내용물이 많이 녹아서 전달됨
-증정 사은품 누락 우려 — 보냉백 등의 증정품이 동봉되지 않거나 배송이 지연됨</t>
+          <t>제품 해동 배송 상태 — 배송 중 닭가슴살이 녹아서 오는 경우가 있음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -4988,7 +4950,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4996,43 +4958,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>676</v>
+        <v>1168</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 체력 보충 — 운동이나 라이딩, 야외 활동 시 피로 회복에 효과적임</t>
+          <t>짜게 먹은 후 붓기 관리 — 나트륨 섭취 후 붓기 완화에 유용함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>착한 가성비 — 다이소 판매 제품으로 저렴한 가격에 부담 없이 구매 가능함</t>
+          <t>상쾌한 이온음료 맛 — 포카리 같은 이온음료 맛이 나 탄산 대용으로 좋음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -5043,7 +5005,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5051,51 +5013,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>대웅제약 마그네슘 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581091&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000270&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/30NEHOm4dIOnmUVwUKLJ591581091_00_0030NEHOm4dIOnmUVwUKLJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/rjUOcdF4xff4PIy7VUYT600000270_00_01rjUOcdF4xff4PIy7VUYT.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>651</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>부담 없는 가격의 비타민 — 저렴한 가격으로 필수 영양소인 비타민B를 챙길 수 있음</t>
+          <t>저림 완화와 컨디션 개선 — 복용 후 몸 저림이 줄고 환절기 컨디션 난조 극복에 도움 됨</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>높은 재구매 만족도 — 지속적으로 꾸준히 재구매하여 섭취할 정도로 만족함</t>
+          <t>깔끔한 디자인과 사용성 — 디자인이 깔끔하고 누구나 사용하기 편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>효과 체감의 개인차 — 섭취 후 피로 개선 등의 신체적 효과를 크게 느끼지 못함</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5137,16 +5095,16 @@
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 성분 — 저렴한 가격 대비 코큐텐 함량과 품질이 뛰어남</t>
+          <t>시중 최상급 가성비 — 착한 가격으로 부담 없이 꾸준히 복용 가능함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>간편한 복용과 빠른 배송 — 복용하기 편하며 주문 후 배송이 빠름</t>
+          <t>간편한 복용과 빠른 배송 — 섭취가 간단하고 배송이 빠름</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5157,7 +5115,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5165,43 +5123,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>2774</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 은은하게 반짝이는 고급스러운 포장으로 선물용에 적합함</t>
+          <t>알찬 성분 함량과 가성비 — 성분 함량이 충실하고 가격이 저렴함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>합리적인 구매 가격 — 침향환을 부담 없는 합리적인 가격대로 구매 가능함</t>
+          <t>사용 및 복용의 편의성 — 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5212,7 +5170,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5220,58 +5178,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3797</v>
+        <v>1779</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>작은 알약 크기 — 정제 크기가 작아서 목넘김이 편하고 삼키기 쉬움</t>
+          <t>피로 회복과 활력 충전 — 피곤할 때 먹으면 체력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 컴퓨터 작업으로 피로한 눈 관리를 저렴하게 시작할 수 있음</t>
+          <t>소량 포장의 높은 휴대성 — 가방에 넣어 다니며 챙겨 먹기 부담 없음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>단기 복용 시 미미한 효과 — 복용 초반에는 눈 피로 개선 효과가 눈에 띄지 않음</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5279,12 +5233,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5294,35 +5248,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1168</v>
+        <v>232</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있는 이온음료 맛 — 포카리스웨트와 유사한 맛이 나 탄산음료 대신 마시기 좋음</t>
+          <t>편안한 수면 유도 도움 — 복용 시 수면에 도움을 줌</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 물 섭취 방식 — 분말을 물에 타서 간단하게 음용할 수 있음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>나트륨 배출 및 붓기 관리 — 짜게 먹는 습관이 있거나 자주 붓는 경우 관리하기 유용함</t>
-        </is>
-      </c>
+          <t>부담 없는 저렴한 가격 — 가격이 저렴하여 만족스러움</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -5330,7 +5280,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5338,49 +5288,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4467</v>
+        <v>398</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>편안한 목넘김 — 알약 크기가 크지 않아 섭취하기에 부담이 없음</t>
+          <t>쓰지 않고 달달한 맛 — 거부감 없이 달콤하게 먹기 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>식후 혈당 가성비 관리 — 식후 혈당 관리를 저렴한 가격으로 꾸준히 하기 적합함</t>
+          <t>빠른 배변 반응 효과 — 복용 후 배변 신호가 빠르게 옴</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>체감 효능 미흡 — 섭취 후 신체 변화나 효능이 크게 느껴지지 않음</t>
+          <t>서서히 나타나는 효과 — 생각보다 즉각적인 효과가 약할 수 있음</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5389,7 +5339,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5397,58 +5347,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1060</v>
+        <v>5858</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>간편한 포장 및 복용 — 올리브오일과 레몬 조합을 낱개로 간편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>저렴한 유행 제품 체험 — 유행하는 오일 레몬 조합을 저렴한 가격에 경험 가능함</t>
-        </is>
-      </c>
+          <t>매우 저렴한 합리적 가격 — 가격이 저렴하여 부담 없이 꾸준히 구매 가능함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>효과 체감의 부족 — 섭취 후 신체적인 변화나 효과를 체감하기 어려움</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5456,49 +5398,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2396</v>
+        <v>2262</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 10포 구성을 매우 저렴한 가격으로 구매할 수 있음</t>
+          <t>압도적인 가성비와 구성 — 가격이 매우 싸고 30일분 구성이 알참</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>연하고 구수한 맛 — 보리차나 연한 커피 맛이 나 운동 중 마시기 좋음</t>
+          <t>위생적인 낱개 개별 포장 — 통 방식보다 한 알씩 포장되어 위생적임</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>오프라인 판매 중단 아쉬움 — 오프라인 매장에서 구매하기 어려워진 점이 아쉬움</t>
+          <t>위장 장애 유발 가능성 — 위가 약한 경우 복용 시 주의가 필요함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5507,7 +5449,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5515,43 +5457,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1501</v>
+        <v>3801</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>상큼하고 풍부한 맛 — 상큼한 레몬 맛으로 물에 타서 수시로 마시기 유용함</t>
+          <t>목넘김 쉬운 작은 알약 — 알약 크기가 작아 복용하기 편함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>저렴한 구매 가격 — 유기농 레몬즙을 저렴한 가격에 가성비 있게 구매함</t>
+          <t>저렴한 가격과 눈 케어 — 가격이 착하고 피로한 눈 건강 유지에 도움 됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5670,52 +5612,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5669,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5742,37 +5684,37 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -5784,12 +5726,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>대웅제약 마그네슘 10정 10일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5799,37 +5741,37 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 철분 30정 30일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 루테인 30정 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5791,7 @@
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5858,13 +5800,13 @@
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5877,37 +5819,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>676</v>
+        <v>1168</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>459</v>
+        <v>651</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6</v>
+        <v>2774</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3797</v>
+        <v>1779</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1168</v>
+        <v>232</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4467</v>
+        <v>398</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1060</v>
+        <v>5858</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2396</v>
+        <v>2262</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5915,63 +5857,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 체력 보충 — 운동이나 라이딩, 야외 활동 시 피로 회복에 효과적임
-착한 가성비 — 다이소 판매 제품으로 저렴한 가격에 부담 없이 구매 가능함</t>
+          <t>짜게 먹은 후 붓기 관리 — 나트륨 섭취 후 붓기 완화에 유용함
+상쾌한 이온음료 맛 — 포카리 같은 이온음료 맛이 나 탄산 대용으로 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가격의 비타민 — 저렴한 가격으로 필수 영양소인 비타민B를 챙길 수 있음
-높은 재구매 만족도 — 지속적으로 꾸준히 재구매하여 섭취할 정도로 만족함</t>
+          <t>저림 완화와 컨디션 개선 — 복용 후 몸 저림이 줄고 환절기 컨디션 난조 극복에 도움 됨
+깔끔한 디자인과 사용성 — 디자인이 깔끔하고 누구나 사용하기 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 성분 — 저렴한 가격 대비 코큐텐 함량과 품질이 뛰어남
-간편한 복용과 빠른 배송 — 복용하기 편하며 주문 후 배송이 빠름</t>
+          <t>시중 최상급 가성비 — 착한 가격으로 부담 없이 꾸준히 복용 가능함
+간편한 복용과 빠른 배송 — 섭취가 간단하고 배송이 빠름</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 은은하게 반짝이는 고급스러운 포장으로 선물용에 적합함
-합리적인 구매 가격 — 침향환을 부담 없는 합리적인 가격대로 구매 가능함</t>
+          <t>알찬 성분 함량과 가성비 — 성분 함량이 충실하고 가격이 저렴함
+사용 및 복용의 편의성 — 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>작은 알약 크기 — 정제 크기가 작아서 목넘김이 편하고 삼키기 쉬움
-부담 없는 가성비 — 컴퓨터 작업으로 피로한 눈 관리를 저렴하게 시작할 수 있음</t>
+          <t>피로 회복과 활력 충전 — 피곤할 때 먹으면 체력 유지에 도움 됨
+소량 포장의 높은 휴대성 — 가방에 넣어 다니며 챙겨 먹기 부담 없음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 이온음료 맛 — 포카리스웨트와 유사한 맛이 나 탄산음료 대신 마시기 좋음
-간편한 물 섭취 방식 — 분말을 물에 타서 간단하게 음용할 수 있음
-나트륨 배출 및 붓기 관리 — 짜게 먹는 습관이 있거나 자주 붓는 경우 관리하기 유용함</t>
+          <t>편안한 수면 유도 도움 — 복용 시 수면에 도움을 줌
+부담 없는 저렴한 가격 — 가격이 저렴하여 만족스러움</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>편안한 목넘김 — 알약 크기가 크지 않아 섭취하기에 부담이 없음
-식후 혈당 가성비 관리 — 식후 혈당 관리를 저렴한 가격으로 꾸준히 하기 적합함</t>
+          <t>쓰지 않고 달달한 맛 — 거부감 없이 달콤하게 먹기 좋음
+빠른 배변 반응 효과 — 복용 후 배변 신호가 빠르게 옴</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>간편한 포장 및 복용 — 올리브오일과 레몬 조합을 낱개로 간편하게 먹을 수 있음
-저렴한 유행 제품 체험 — 유행하는 오일 레몬 조합을 저렴한 가격에 경험 가능함</t>
+          <t>매우 저렴한 합리적 가격 — 가격이 저렴하여 부담 없이 꾸준히 구매 가능함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 10포 구성을 매우 저렴한 가격으로 구매할 수 있음
-연하고 구수한 맛 — 보리차나 연한 커피 맛이 나 운동 중 마시기 좋음</t>
+          <t>압도적인 가성비와 구성 — 가격이 매우 싸고 30일분 구성이 알참
+위생적인 낱개 개별 포장 — 통 방식보다 한 알씩 포장되어 위생적임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 풍부한 맛 — 상큼한 레몬 맛으로 물에 타서 수시로 마시기 유용함
-저렴한 구매 가격 — 유기농 레몬즙을 저렴한 가격에 가성비 있게 구매함</t>
+          <t>목넘김 쉬운 작은 알약 — 알약 크기가 작아 복용하기 편함
+저렴한 가격과 눈 케어 — 가격이 착하고 피로한 눈 건강 유지에 도움 됨</t>
         </is>
       </c>
     </row>
@@ -5982,32 +5922,20 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 개인차 — 섭취 후 피로 개선 등의 신체적 효과를 크게 느끼지 못함</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>단기 복용 시 미미한 효과 — 복용 초반에는 눈 피로 개선 효과가 눈에 띄지 않음</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>체감 효능 미흡 — 섭취 후 신체 변화나 효능이 크게 느껴지지 않음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 부족 — 섭취 후 신체적인 변화나 효과를 체감하기 어려움</t>
-        </is>
-      </c>
+          <t>서서히 나타나는 효과 — 생각보다 즉각적인 효과가 약할 수 있음</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>오프라인 판매 중단 아쉬움 — 오프라인 매장에서 구매하기 어려워진 점이 아쉬움</t>
+          <t>위장 장애 유발 가능성 — 위가 약한 경우 복용 시 주의가 필요함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -6020,52 +5948,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6172,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6252,46 +6180,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>8056</v>
+        <v>21962</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1일 1캡슐 간편 케어 — 하루 한 알 섭취로 여성 건강 및 장 건강을 관리함</t>
+          <t>대용량 우수한 가성비 — 600정 구성으로 오랫동안 경제적으로 복용 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>알찬 기획 및 증정품 — 2개월분 용량에 포토카드 등 증정 혜택 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>높은 브랜드 신뢰도 — 영국산 원료 사용 및 오랜 유명 브랜드로 믿을 수 있음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>위생적인 개별 포장 — 개별 포장되어 휴대성이 좋고 복용이 편리함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -6334,31 +6266,27 @@
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>14723</v>
+        <v>14725</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 구미 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간편하게 먹기 좋음</t>
+          <t>확실한 수면 유도 효과 — 복용 후 잠이 확 들고 푹 잘 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>빠른 입면과 숙면 도움 — 자기 전 복용 시 잠이 잘 들고 숙면을 취할 수 있음</t>
+          <t>맛있는 구미 젤리 제형 — 젤리 형태라 거부감 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>취침 전 재양치 번거로움 — 자기 직전 젤리 섭취 후 양치를 다시 해야 하는 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6366,43 +6294,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>457</v>
+        <v>8057</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 동시 케어 — 체지방 감소와 장 케어를 함께 할 수 있는 이중 기능성 제품임</t>
+          <t>질과 장 건강 동시 케어 — 여성 질 건강과 장 건강을 함께 챙길 수 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>상큼한 요거트 맛 — 맛있는 요거트 맛으로 하루 한 포씩 즐겁게 챙겨 먹음</t>
+          <t>하루 한 알 간편 복용 — 1일 1캡슐 복용으로 간편함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -6413,7 +6341,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6421,43 +6349,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>24090</v>
+        <v>15345</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>풍성한 1+1 기획 구성 — 더블 기획으로 2달 동안 넉넉하게 복용할 수 있음</t>
+          <t>비타민C와 D 동시 보충 — 면역과 비타민D를 한 번에 챙길 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>아침 공복 장 건강 케어 — 아침 빈속에 섭취하여 장 면역과 장 건강을 유지함</t>
+          <t>우수한 가성비와 구성품 — 가격 대비 알차고 귀여운 파우치가 증정됨</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6503,31 +6431,27 @@
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>21297</v>
+        <v>21301</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>고함량 비타민C 보충 — 고함량 섭취를 통해 피로감을 줄이고 컨디션을 유지함</t>
+          <t>고함량 피로 회복 체감 — 고함량 비타민C로 컨디션 향상에 도움 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4개월분 대용량 가성비 — 넉넉한 용량으로 오랫동안 부담 없이 챙겨 먹기 좋음</t>
+          <t>부담 없는 세일 가성비 — 할인 시 가격 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>강한 신맛과 수분 필요 — 알약의 신맛이 강하며 섭취 시 충분한 물 마심이 필요함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6535,45 +6459,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>17,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15342</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>비타민 C와 D 올인원 — 항산화 비타민C와 실내 생활 필수 비타민D를 한 번에 섭취함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 파우치 증정 — 마이멜로디 파우치가 동봉되어 소장 가치가 높음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563462ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6582,7 +6494,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6590,50 +6502,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>17521</v>
+        <v>458</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 타사 제품 대비 가격이 매우 저렴하여 부담이 적음</t>
+          <t>체지방과 장 건강 케어 — 체지방 감소와 장 케어를 한 번에 제공함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>비린내 없는 편안함 — 오메가3 특유의 비린내가 적고 캡슐 크기가 적당함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>위생적인 PTP 개별 포장 — 개별 포장되어 있어 휴대와 보관이 유용함</t>
-        </is>
-      </c>
+          <t>상큼한 요거트 맛 제형 — 맛있게 하루 한 포씩 챙기기 좋음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -6649,43 +6557,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>12312</v>
+        <v>2066</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>속 편한 배변 활동 도움 — 복통이나 가스 차는 현상 없이 편안하게 화장실을 감</t>
+          <t>빠르고 시원한 배변 효과 — 복용 후 빠른 시간 내 신호가 와서 속이 시원함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>귀여운 산리오 러기지택 — 산리오 콜라보 굿즈 증정으로 기획 만족도가 높음</t>
+          <t>체지방 감소와 다이어트 — 아랫배 관리 및 다이어트에 도움 됨</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6696,7 +6604,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6704,58 +6612,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218546&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021854629ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>13678</v>
+        <v>24093</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 수면 유도 효과 — 자기 전 복용 시 새벽에 깨지 않고 빠르게 잠에 듦</t>
+          <t>장 건강 및 면역력 강화 — 장이 편안해지고 면역력 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>식물성 성분의 맛있는 구미 — 식물성 멜라토닌 성분이며 상큼한 과일 맛 젤리로 먹기 편함</t>
+          <t>소형 캡슐의 쉬운 목넘김 — 캡슐 크기가 작아 물과 함께 삼키기 쉬움</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>취침 전 양치 재실행 번거로움 — 잠들기 전 젤리를 먹은 뒤 양치를 다시 해야 하는 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6763,43 +6667,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>2065</v>
+        <v>41003</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 숙변 해소 및 장 상쾌함 — 복용 후 신호가 빠르게 와서 만성 변비 해소에 효과적임</t>
+          <t>확실한 피로 회복 체감 — 복용 시 체력 충전 및 피로 개선 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>귀여운 콜라보 굿즈 — 산리오 캐릭터 카라비너 증정으로 소장 욕구를 높임</t>
+          <t>액상형의 높은 복용 편의 — 탄산수 등에 타 마시기 좋고 마시기 편함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -6918,52 +6822,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -6975,52 +6879,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -7032,52 +6936,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 120정 (4개월분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
     </row>
@@ -7094,7 +6998,7 @@
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.9</v>
@@ -7102,20 +7006,18 @@
       <c r="G6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -7125,34 +7027,32 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8056</v>
+        <v>21962</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14723</v>
+        <v>14725</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>457</v>
+        <v>8057</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24090</v>
+        <v>15345</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>21297</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>15342</v>
-      </c>
+        <v>21301</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="n">
-        <v>17521</v>
+        <v>458</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12312</v>
+        <v>2066</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>13678</v>
+        <v>24093</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2065</v>
+        <v>41003</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7163,63 +7063,58 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1일 1캡슐 간편 케어 — 하루 한 알 섭취로 여성 건강 및 장 건강을 관리함
-알찬 기획 및 증정품 — 2개월분 용량에 포토카드 등 증정 혜택 만족도가 높음</t>
+          <t>대용량 우수한 가성비 — 600정 구성으로 오랫동안 경제적으로 복용 가능함
+높은 브랜드 신뢰도 — 영국산 원료 사용 및 오랜 유명 브랜드로 믿을 수 있음
+위생적인 개별 포장 — 개별 포장되어 휴대성이 좋고 복용이 편리함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간편하게 먹기 좋음
-빠른 입면과 숙면 도움 — 자기 전 복용 시 잠이 잘 들고 숙면을 취할 수 있음</t>
+          <t>확실한 수면 유도 효과 — 복용 후 잠이 확 들고 푹 잘 수 있음
+맛있는 구미 젤리 제형 — 젤리 형태라 거부감 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 동시 케어 — 체지방 감소와 장 케어를 함께 할 수 있는 이중 기능성 제품임
-상큼한 요거트 맛 — 맛있는 요거트 맛으로 하루 한 포씩 즐겁게 챙겨 먹음</t>
+          <t>질과 장 건강 동시 케어 — 여성 질 건강과 장 건강을 함께 챙길 수 있음
+하루 한 알 간편 복용 — 1일 1캡슐 복용으로 간편함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>풍성한 1+1 기획 구성 — 더블 기획으로 2달 동안 넉넉하게 복용할 수 있음
-아침 공복 장 건강 케어 — 아침 빈속에 섭취하여 장 면역과 장 건강을 유지함</t>
+          <t>비타민C와 D 동시 보충 — 면역과 비타민D를 한 번에 챙길 수 있음
+우수한 가성비와 구성품 — 가격 대비 알차고 귀여운 파우치가 증정됨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 보충 — 고함량 섭취를 통해 피로감을 줄이고 컨디션을 유지함
-4개월분 대용량 가성비 — 넉넉한 용량으로 오랫동안 부담 없이 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>비타민 C와 D 올인원 — 항산화 비타민C와 실내 생활 필수 비타민D를 한 번에 섭취함
-귀여운 산리오 파우치 증정 — 마이멜로디 파우치가 동봉되어 소장 가치가 높음</t>
-        </is>
-      </c>
+          <t>고함량 피로 회복 체감 — 고함량 비타민C로 컨디션 향상에 도움 됨
+부담 없는 세일 가성비 — 할인 시 가격 부담 없이 구매 가능함</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 타사 제품 대비 가격이 매우 저렴하여 부담이 적음
-비린내 없는 편안함 — 오메가3 특유의 비린내가 적고 캡슐 크기가 적당함
-위생적인 PTP 개별 포장 — 개별 포장되어 있어 휴대와 보관이 유용함</t>
+          <t>체지방과 장 건강 케어 — 체지방 감소와 장 케어를 한 번에 제공함
+상큼한 요거트 맛 제형 — 맛있게 하루 한 포씩 챙기기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>속 편한 배변 활동 도움 — 복통이나 가스 차는 현상 없이 편안하게 화장실을 감
-귀여운 산리오 러기지택 — 산리오 콜라보 굿즈 증정으로 기획 만족도가 높음</t>
+          <t>빠르고 시원한 배변 효과 — 복용 후 빠른 시간 내 신호가 와서 속이 시원함
+체지방 감소와 다이어트 — 아랫배 관리 및 다이어트에 도움 됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 수면 유도 효과 — 자기 전 복용 시 새벽에 깨지 않고 빠르게 잠에 듦
-식물성 성분의 맛있는 구미 — 식물성 멜라토닌 성분이며 상큼한 과일 맛 젤리로 먹기 편함</t>
+          <t>장 건강 및 면역력 강화 — 장이 편안해지고 면역력 관리에 도움 됨
+소형 캡슐의 쉬운 목넘김 — 캡슐 크기가 작아 물과 함께 삼키기 쉬움</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 숙변 해소 및 장 상쾌함 — 복용 후 신호가 빠르게 와서 만성 변비 해소에 효과적임
-귀여운 콜라보 굿즈 — 산리오 캐릭터 카라비너 증정으로 소장 욕구를 높임</t>
+          <t>확실한 피로 회복 체감 — 복용 시 체력 충전 및 피로 개선 효과가 뛰어남
+액상형의 높은 복용 편의 — 탄산수 등에 타 마시기 좋고 마시기 편함</t>
         </is>
       </c>
     </row>
@@ -7230,26 +7125,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>취침 전 재양치 번거로움 — 자기 직전 젤리 섭취 후 양치를 다시 해야 하는 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛과 수분 필요 — 알약의 신맛이 강하며 섭취 시 충분한 물 마심이 필요함</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>취침 전 양치 재실행 번거로움 — 잠들기 전 젤리를 먹은 뒤 양치를 다시 해야 하는 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7260,52 +7143,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>31,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>17,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>39,800원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>13,950원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>8,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>55,900원</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7431,23 +7314,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -7457,16 +7340,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -7475,7 +7358,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7485,35 +7368,35 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7523,10 +7406,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -7535,35 +7418,35 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7585,7 +7468,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7607,7 +7490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7623,6 +7506,50 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
